--- a/03_Outputs/all/03_DS/ds_idx15_vejez.xlsx
+++ b/03_Outputs/all/03_DS/ds_idx15_vejez.xlsx
@@ -403,19 +403,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>1.914875836338045</v>
+        <v>1.914875836338044</v>
       </c>
       <c r="D2">
         <v>-2.348971029611666</v>
       </c>
       <c r="E2">
-        <v>-0.4064627436056068</v>
+        <v>-0.4064627436056047</v>
       </c>
       <c r="F2">
-        <v>-0.5269395412491378</v>
+        <v>-0.5269395412491381</v>
       </c>
       <c r="G2">
-        <v>-0.2191939359627342</v>
+        <v>-0.2191939359627335</v>
       </c>
     </row>
     <row r="3">
@@ -430,19 +430,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>2.738357441447331</v>
+        <v>2.738357441447329</v>
       </c>
       <c r="D3">
-        <v>1.514773735906488</v>
+        <v>1.514773735906487</v>
       </c>
       <c r="E3">
-        <v>-0.7982418132964324</v>
+        <v>-0.7982418132964311</v>
       </c>
       <c r="F3">
-        <v>0.221910375874713</v>
+        <v>0.2219103758747128</v>
       </c>
       <c r="G3">
-        <v>0.169775106411208</v>
+        <v>0.1697751064112071</v>
       </c>
     </row>
     <row r="4">
@@ -457,19 +457,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>1.870076949567597</v>
+        <v>1.870076949567595</v>
       </c>
       <c r="D4">
-        <v>1.183394982467198</v>
+        <v>1.183394982467197</v>
       </c>
       <c r="E4">
-        <v>0.6479417771450302</v>
+        <v>0.6479417771450322</v>
       </c>
       <c r="F4">
-        <v>-0.1945701494363143</v>
+        <v>-0.194570149436314</v>
       </c>
       <c r="G4">
-        <v>0.1143571558618931</v>
+        <v>0.1143571558618939</v>
       </c>
     </row>
     <row r="5">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>1.305571520702836</v>
+        <v>1.305571520702834</v>
       </c>
       <c r="D5">
         <v>1.101983647394617</v>
       </c>
       <c r="E5">
-        <v>-1.202032648636599</v>
+        <v>-1.202032648636598</v>
       </c>
       <c r="F5">
-        <v>-0.168541558929597</v>
+        <v>-0.1685415589295975</v>
       </c>
       <c r="G5">
-        <v>0.1477336156042729</v>
+        <v>0.1477336156042715</v>
       </c>
     </row>
     <row r="6">
@@ -511,19 +511,19 @@
         </is>
       </c>
       <c r="C6">
-        <v>1.352205629359007</v>
+        <v>1.352205629359006</v>
       </c>
       <c r="D6">
         <v>-1.443996762495321</v>
       </c>
       <c r="E6">
-        <v>0.7581611725411134</v>
+        <v>0.7581611725411148</v>
       </c>
       <c r="F6">
-        <v>0.5251095575949131</v>
+        <v>0.5251095575949135</v>
       </c>
       <c r="G6">
-        <v>-0.07250163462953568</v>
+        <v>-0.07250163462953454</v>
       </c>
     </row>
     <row r="7">
@@ -541,16 +541,16 @@
         <v>-1.585092952044973</v>
       </c>
       <c r="D7">
-        <v>0.8269575722680064</v>
+        <v>0.8269575722680066</v>
       </c>
       <c r="E7">
-        <v>0.1679300552036813</v>
+        <v>0.1679300552036828</v>
       </c>
       <c r="F7">
-        <v>-0.1660361200343499</v>
+        <v>-0.1660361200343501</v>
       </c>
       <c r="G7">
-        <v>0.2923220688316567</v>
+        <v>0.2923220688316568</v>
       </c>
     </row>
     <row r="8">
@@ -565,19 +565,19 @@
         </is>
       </c>
       <c r="C8">
-        <v>1.008080523546282</v>
+        <v>1.00808052354628</v>
       </c>
       <c r="D8">
-        <v>0.8408962772568733</v>
+        <v>0.8408962772568725</v>
       </c>
       <c r="E8">
-        <v>-0.01693279457625719</v>
+        <v>-0.01693279457625516</v>
       </c>
       <c r="F8">
-        <v>-0.285879287796274</v>
+        <v>-0.2858792877962741</v>
       </c>
       <c r="G8">
-        <v>-0.06866952353239977</v>
+        <v>-0.06866952353239925</v>
       </c>
     </row>
     <row r="9">
@@ -592,19 +592,19 @@
         </is>
       </c>
       <c r="C9">
-        <v>1.965270305393888</v>
+        <v>1.965270305393886</v>
       </c>
       <c r="D9">
-        <v>-0.5076099086725114</v>
+        <v>-0.5076099086725117</v>
       </c>
       <c r="E9">
-        <v>0.2105391602125808</v>
+        <v>0.210539160212582</v>
       </c>
       <c r="F9">
         <v>1.245853747272181</v>
       </c>
       <c r="G9">
-        <v>-0.3624807080379963</v>
+        <v>-0.3624807080379967</v>
       </c>
     </row>
     <row r="10">
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="C10">
-        <v>-0.3184560164551199</v>
+        <v>-0.3184560164551202</v>
       </c>
       <c r="D10">
         <v>1.213030248454283</v>
       </c>
       <c r="E10">
-        <v>-0.688663321422285</v>
+        <v>-0.6886633214222831</v>
       </c>
       <c r="F10">
-        <v>-0.1188202633439297</v>
+        <v>-0.11882026334393</v>
       </c>
       <c r="G10">
-        <v>-0.1114102332239948</v>
+        <v>-0.1114102332239934</v>
       </c>
     </row>
     <row r="11">
@@ -646,19 +646,19 @@
         </is>
       </c>
       <c r="C11">
-        <v>-3.790814750701412</v>
+        <v>-3.79081475070141</v>
       </c>
       <c r="D11">
-        <v>0.5140726239988518</v>
+        <v>0.5140726239988528</v>
       </c>
       <c r="E11">
-        <v>0.2762433594916027</v>
+        <v>0.2762433594916041</v>
       </c>
       <c r="F11">
-        <v>-0.1080894128842699</v>
+        <v>-0.1080894128842705</v>
       </c>
       <c r="G11">
-        <v>0.06307089285482353</v>
+        <v>0.06307089285482431</v>
       </c>
     </row>
     <row r="12">
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="C12">
-        <v>0.3679178822926703</v>
+        <v>0.3679178822926698</v>
       </c>
       <c r="D12">
-        <v>-0.2551463141913859</v>
+        <v>-0.255146314191386</v>
       </c>
       <c r="E12">
-        <v>0.04828765849698063</v>
+        <v>0.04828765849698247</v>
       </c>
       <c r="F12">
-        <v>0.02010571708270772</v>
+        <v>0.02010571708270762</v>
       </c>
       <c r="G12">
-        <v>-0.2510264936611606</v>
+        <v>-0.2510264936611599</v>
       </c>
     </row>
     <row r="13">
@@ -700,19 +700,19 @@
         </is>
       </c>
       <c r="C13">
-        <v>0.434036070360294</v>
+        <v>0.4340360703602931</v>
       </c>
       <c r="D13">
-        <v>1.645706868896197</v>
+        <v>1.645706868896196</v>
       </c>
       <c r="E13">
-        <v>-1.690118162305269</v>
+        <v>-1.690118162305267</v>
       </c>
       <c r="F13">
-        <v>0.08960378967366819</v>
+        <v>0.08960378967366732</v>
       </c>
       <c r="G13">
-        <v>-0.2443760041475013</v>
+        <v>-0.2443760041474999</v>
       </c>
     </row>
     <row r="14">
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="C14">
-        <v>-4.630291498340205</v>
+        <v>-4.630291498340202</v>
       </c>
       <c r="D14">
-        <v>-2.409716964122747</v>
+        <v>-2.409716964122745</v>
       </c>
       <c r="E14">
-        <v>0.0942607268152644</v>
+        <v>0.09426072681526609</v>
       </c>
       <c r="F14">
-        <v>0.5102834077398806</v>
+        <v>0.5102834077398803</v>
       </c>
       <c r="G14">
-        <v>-0.01582605253602814</v>
+        <v>-0.015826052536025</v>
       </c>
     </row>
     <row r="15">
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="C15">
-        <v>-2.74356725592122</v>
+        <v>-2.743567255921219</v>
       </c>
       <c r="D15">
-        <v>1.455318939878498</v>
+        <v>1.455318939878499</v>
       </c>
       <c r="E15">
-        <v>0.09728582114367237</v>
+        <v>0.09728582114367423</v>
       </c>
       <c r="F15">
-        <v>-0.0426477551396978</v>
+        <v>-0.04264775513969826</v>
       </c>
       <c r="G15">
-        <v>-0.3056558645135002</v>
+        <v>-0.3056558645134989</v>
       </c>
     </row>
     <row r="16">
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="C16">
-        <v>-0.3487869108096043</v>
+        <v>-0.348786910809605</v>
       </c>
       <c r="D16">
         <v>1.950532940292911</v>
       </c>
       <c r="E16">
-        <v>-0.8833733787453411</v>
+        <v>-0.8833733787453393</v>
       </c>
       <c r="F16">
-        <v>-0.1527725983842801</v>
+        <v>-0.1527725983842808</v>
       </c>
       <c r="G16">
-        <v>-0.4187007318829201</v>
+        <v>-0.418700731882921</v>
       </c>
     </row>
     <row r="17">
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C17">
-        <v>5.067592786731092</v>
+        <v>5.067592786731089</v>
       </c>
       <c r="D17">
-        <v>1.6035773843348</v>
+        <v>1.603577384334798</v>
       </c>
       <c r="E17">
-        <v>0.7107500644823275</v>
+        <v>0.7107500644823297</v>
       </c>
       <c r="F17">
-        <v>0.06285159294837686</v>
+        <v>0.06285159294837767</v>
       </c>
       <c r="G17">
-        <v>0.3192723411561033</v>
+        <v>0.3192723411561029</v>
       </c>
     </row>
     <row r="18">
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="C18">
-        <v>2.503806110884883</v>
+        <v>2.503806110884882</v>
       </c>
       <c r="D18">
         <v>-2.570524015901837</v>
       </c>
       <c r="E18">
-        <v>0.4143184338907606</v>
+        <v>0.4143184338907623</v>
       </c>
       <c r="F18">
-        <v>0.4243924344526543</v>
+        <v>0.4243924344526546</v>
       </c>
       <c r="G18">
-        <v>0.08843689434764064</v>
+        <v>0.08843689434764149</v>
       </c>
     </row>
     <row r="19">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="C19">
-        <v>-1.325311810442261</v>
+        <v>-1.32531181044226</v>
       </c>
       <c r="D19">
-        <v>-0.2687492108872094</v>
+        <v>-0.2687492108872086</v>
       </c>
       <c r="E19">
-        <v>-0.3582847893900689</v>
+        <v>-0.3582847893900675</v>
       </c>
       <c r="F19">
-        <v>0.5607063615858959</v>
+        <v>0.5607063615858958</v>
       </c>
       <c r="G19">
-        <v>-0.04555740951739516</v>
+        <v>-0.04555740951739358</v>
       </c>
     </row>
     <row r="20">
@@ -889,19 +889,19 @@
         </is>
       </c>
       <c r="C20">
-        <v>-0.7699977647349882</v>
+        <v>-0.7699977647349876</v>
       </c>
       <c r="D20">
-        <v>-2.285946986308766</v>
+        <v>-2.285946986308765</v>
       </c>
       <c r="E20">
-        <v>-1.037937648167741</v>
+        <v>-1.03793764816774</v>
       </c>
       <c r="F20">
-        <v>-0.1451463983031107</v>
+        <v>-0.145146398303111</v>
       </c>
       <c r="G20">
-        <v>-0.1082106803318545</v>
+        <v>-0.1082106803318544</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="C21">
-        <v>0.0115347237590143</v>
+        <v>0.01153472375901381</v>
       </c>
       <c r="D21">
-        <v>1.621752112202974</v>
+        <v>1.621752112202973</v>
       </c>
       <c r="E21">
-        <v>-0.4635095925622628</v>
+        <v>-0.4635095925622611</v>
       </c>
       <c r="F21">
-        <v>0.01334590434074585</v>
+        <v>0.01334590434074556</v>
       </c>
       <c r="G21">
-        <v>0.3590118670977346</v>
+        <v>0.3590118670977351</v>
       </c>
     </row>
     <row r="22">
@@ -949,13 +949,13 @@
         <v>1.310142830064821</v>
       </c>
       <c r="E22">
-        <v>0.09571097682496581</v>
+        <v>0.0957109768249676</v>
       </c>
       <c r="F22">
-        <v>-0.004583322934613105</v>
+        <v>-0.004583322934613547</v>
       </c>
       <c r="G22">
-        <v>-0.1744815963097512</v>
+        <v>-0.1744815963097501</v>
       </c>
     </row>
     <row r="23">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="C23">
-        <v>1.079422363943431</v>
+        <v>1.079422363943429</v>
       </c>
       <c r="D23">
-        <v>1.336491887752846</v>
+        <v>1.336491887752844</v>
       </c>
       <c r="E23">
-        <v>-0.6060565724531196</v>
+        <v>-0.6060565724531178</v>
       </c>
       <c r="F23">
-        <v>0.1527453915515432</v>
+        <v>0.152745391551543</v>
       </c>
       <c r="G23">
-        <v>-0.08690961817296276</v>
+        <v>-0.08690961817296358</v>
       </c>
     </row>
     <row r="24">
@@ -997,19 +997,19 @@
         </is>
       </c>
       <c r="C24">
-        <v>-3.606285350663209</v>
+        <v>-3.606285350663208</v>
       </c>
       <c r="D24">
-        <v>0.4479065518284503</v>
+        <v>0.4479065518284513</v>
       </c>
       <c r="E24">
-        <v>0.8490734769880717</v>
+        <v>0.8490734769880733</v>
       </c>
       <c r="F24">
-        <v>-0.5533305094345908</v>
+        <v>-0.5533305094345911</v>
       </c>
       <c r="G24">
-        <v>0.2245577330659553</v>
+        <v>0.2245577330659577</v>
       </c>
     </row>
     <row r="25">
@@ -1024,19 +1024,19 @@
         </is>
       </c>
       <c r="C25">
-        <v>-1.283812806304569</v>
+        <v>-1.283812806304568</v>
       </c>
       <c r="D25">
-        <v>-0.3422819474004092</v>
+        <v>-0.3422819474004088</v>
       </c>
       <c r="E25">
-        <v>1.108835409874756</v>
+        <v>1.108835409874759</v>
       </c>
       <c r="F25">
-        <v>-0.4644151146386361</v>
+        <v>-0.4644151146386359</v>
       </c>
       <c r="G25">
-        <v>-0.06900921923066367</v>
+        <v>-0.06900921923066232</v>
       </c>
     </row>
     <row r="26">
@@ -1051,19 +1051,19 @@
         </is>
       </c>
       <c r="C26">
-        <v>-4.296945239307938</v>
+        <v>-4.296945239307936</v>
       </c>
       <c r="D26">
-        <v>0.5089113625963803</v>
+        <v>0.5089113625963815</v>
       </c>
       <c r="E26">
-        <v>0.3048725282272219</v>
+        <v>0.3048725282272239</v>
       </c>
       <c r="F26">
-        <v>-0.3357082198243969</v>
+        <v>-0.3357082198243974</v>
       </c>
       <c r="G26">
-        <v>0.1367557688361934</v>
+        <v>0.1367557688361954</v>
       </c>
     </row>
     <row r="27">
@@ -1084,13 +1084,13 @@
         <v>1.464051523182875</v>
       </c>
       <c r="E27">
-        <v>-0.127539669136624</v>
+        <v>-0.127539669136622</v>
       </c>
       <c r="F27">
-        <v>-0.0218910229946508</v>
+        <v>-0.0218910229946513</v>
       </c>
       <c r="G27">
-        <v>-0.6338251428208626</v>
+        <v>-0.6338251428208617</v>
       </c>
     </row>
     <row r="28">
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="C28">
-        <v>2.238366182301787</v>
+        <v>2.238366182301786</v>
       </c>
       <c r="D28">
-        <v>-2.66727330985138</v>
+        <v>-2.667273309851379</v>
       </c>
       <c r="E28">
-        <v>-1.212116172298366</v>
+        <v>-1.212116172298364</v>
       </c>
       <c r="F28">
         <v>-0.5592698886492637</v>
       </c>
       <c r="G28">
-        <v>0.1846088419834456</v>
+        <v>0.1846088419834459</v>
       </c>
     </row>
     <row r="29">
@@ -1135,16 +1135,16 @@
         <v>-1.298302244592772</v>
       </c>
       <c r="D29">
-        <v>1.004323689895457</v>
+        <v>1.004323689895456</v>
       </c>
       <c r="E29">
-        <v>-0.4701896741418786</v>
+        <v>-0.4701896741418767</v>
       </c>
       <c r="F29">
-        <v>-0.4051069136543075</v>
+        <v>-0.4051069136543081</v>
       </c>
       <c r="G29">
-        <v>0.09522280771403382</v>
+        <v>0.09522280771403496</v>
       </c>
     </row>
     <row r="30">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="C30">
-        <v>1.048286405261358</v>
+        <v>1.048286405261357</v>
       </c>
       <c r="D30">
-        <v>0.9322126306481026</v>
+        <v>0.9322126306481016</v>
       </c>
       <c r="E30">
-        <v>1.179506531728714</v>
+        <v>1.179506531728716</v>
       </c>
       <c r="F30">
-        <v>-0.05449094994176955</v>
+        <v>-0.05449094994176908</v>
       </c>
       <c r="G30">
-        <v>0.0802123032017069</v>
+        <v>0.08021230320170733</v>
       </c>
     </row>
     <row r="31">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="C31">
-        <v>3.299635846790032</v>
+        <v>3.29963584679003</v>
       </c>
       <c r="D31">
-        <v>0.9655539959764058</v>
+        <v>0.9655539959764041</v>
       </c>
       <c r="E31">
-        <v>-0.2269669205392337</v>
+        <v>-0.2269669205392321</v>
       </c>
       <c r="F31">
-        <v>0.4072709770195003</v>
+        <v>0.4072709770195002</v>
       </c>
       <c r="G31">
-        <v>-0.09526411380367429</v>
+        <v>-0.09526411380367547</v>
       </c>
     </row>
     <row r="32">
@@ -1213,19 +1213,19 @@
         </is>
       </c>
       <c r="C32">
-        <v>3.328642138707176</v>
+        <v>3.328642138707174</v>
       </c>
       <c r="D32">
-        <v>1.854835673276235</v>
+        <v>1.854835673276233</v>
       </c>
       <c r="E32">
-        <v>-0.7363365251419174</v>
+        <v>-0.7363365251419156</v>
       </c>
       <c r="F32">
-        <v>-0.3379843438731364</v>
+        <v>-0.3379843438731365</v>
       </c>
       <c r="G32">
-        <v>0.1651987264164814</v>
+        <v>0.1651987264164803</v>
       </c>
     </row>
     <row r="33">
@@ -1240,19 +1240,19 @@
         </is>
       </c>
       <c r="C33">
-        <v>-5.260580361427108</v>
+        <v>-5.260580361427103</v>
       </c>
       <c r="D33">
-        <v>-2.007597296879888</v>
+        <v>-2.007597296879885</v>
       </c>
       <c r="E33">
-        <v>0.356459032414535</v>
+        <v>0.3564590324145352</v>
       </c>
       <c r="F33">
         <v>1.37130353311339</v>
       </c>
       <c r="G33">
-        <v>0.1398295098733075</v>
+        <v>0.1398295098733105</v>
       </c>
     </row>
     <row r="34">
@@ -1267,19 +1267,19 @@
         </is>
       </c>
       <c r="C34">
-        <v>-0.8767619981862219</v>
+        <v>-0.8767619981862214</v>
       </c>
       <c r="D34">
-        <v>-1.561500939356805</v>
+        <v>-1.561500939356804</v>
       </c>
       <c r="E34">
-        <v>-0.1371626102857147</v>
+        <v>-0.137162610285713</v>
       </c>
       <c r="F34">
-        <v>-0.2774337086860739</v>
+        <v>-0.2774337086860742</v>
       </c>
       <c r="G34">
-        <v>0.1337806423481407</v>
+        <v>0.1337806423481426</v>
       </c>
     </row>
     <row r="35">
@@ -1294,19 +1294,19 @@
         </is>
       </c>
       <c r="C35">
-        <v>4.930178236157502</v>
+        <v>4.9301782361575</v>
       </c>
       <c r="D35">
-        <v>1.126644237831641</v>
+        <v>1.126644237831639</v>
       </c>
       <c r="E35">
-        <v>0.230050149666257</v>
+        <v>0.2300501496662595</v>
       </c>
       <c r="F35">
-        <v>0.05934855006407157</v>
+        <v>0.05934855006407198</v>
       </c>
       <c r="G35">
-        <v>-0.4818153880852481</v>
+        <v>-0.4818153880852495</v>
       </c>
     </row>
     <row r="36">
@@ -1321,19 +1321,19 @@
         </is>
       </c>
       <c r="C36">
-        <v>-3.909952107508408</v>
+        <v>-3.909952107508406</v>
       </c>
       <c r="D36">
-        <v>0.2426474309571854</v>
+        <v>0.2426474309571867</v>
       </c>
       <c r="E36">
-        <v>0.5579083320195378</v>
+        <v>0.5579083320195394</v>
       </c>
       <c r="F36">
-        <v>0.09893832603618341</v>
+        <v>0.09893832603618301</v>
       </c>
       <c r="G36">
-        <v>-0.06836775398256721</v>
+        <v>-0.06836775398256537</v>
       </c>
     </row>
     <row r="37">
@@ -1348,19 +1348,19 @@
         </is>
       </c>
       <c r="C37">
-        <v>-4.86893812289477</v>
+        <v>-4.868938122894768</v>
       </c>
       <c r="D37">
-        <v>-0.2929902201079101</v>
+        <v>-0.292990220107908</v>
       </c>
       <c r="E37">
-        <v>0.01775609540359849</v>
+        <v>0.01775609540359957</v>
       </c>
       <c r="F37">
         <v>1.058146454750383</v>
       </c>
       <c r="G37">
-        <v>-0.2975044755923612</v>
+        <v>-0.2975044755923594</v>
       </c>
     </row>
     <row r="38">
@@ -1375,19 +1375,19 @@
         </is>
       </c>
       <c r="C38">
-        <v>3.780185935191323</v>
+        <v>3.780185935191321</v>
       </c>
       <c r="D38">
-        <v>-0.8571823500442142</v>
+        <v>-0.8571823500442156</v>
       </c>
       <c r="E38">
-        <v>1.313484427655423</v>
+        <v>1.313484427655426</v>
       </c>
       <c r="F38">
-        <v>-1.695563647386614</v>
+        <v>-1.695563647386613</v>
       </c>
       <c r="G38">
-        <v>0.1401925644537342</v>
+        <v>0.1401925644537365</v>
       </c>
     </row>
     <row r="39">
@@ -1402,19 +1402,19 @@
         </is>
       </c>
       <c r="C39">
-        <v>1.323881494040586</v>
+        <v>1.323881494040585</v>
       </c>
       <c r="D39">
-        <v>0.7348309954470352</v>
+        <v>0.7348309954470343</v>
       </c>
       <c r="E39">
-        <v>-0.0240466408132496</v>
+        <v>-0.02404664081324812</v>
       </c>
       <c r="F39">
-        <v>0.11380022415998</v>
+        <v>0.1138002241599801</v>
       </c>
       <c r="G39">
-        <v>0.3813513427867433</v>
+        <v>0.3813513427867432</v>
       </c>
     </row>
     <row r="40">
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="C40">
-        <v>3.161685615957119</v>
+        <v>3.161685615957116</v>
       </c>
       <c r="D40">
-        <v>0.3081558927594638</v>
+        <v>0.3081558927594622</v>
       </c>
       <c r="E40">
-        <v>-0.01912843964130793</v>
+        <v>-0.01912843964130556</v>
       </c>
       <c r="F40">
         <v>-0.542644844841405</v>
       </c>
       <c r="G40">
-        <v>-0.4971674982643873</v>
+        <v>-0.4971674982643877</v>
       </c>
     </row>
     <row r="41">
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C41">
-        <v>1.61278491977245</v>
+        <v>1.612784919772448</v>
       </c>
       <c r="D41">
-        <v>1.037046467415483</v>
+        <v>1.037046467415482</v>
       </c>
       <c r="E41">
-        <v>-0.1771819454098021</v>
+        <v>-0.1771819454098004</v>
       </c>
       <c r="F41">
-        <v>0.1027077686006622</v>
+        <v>0.1027077686006621</v>
       </c>
       <c r="G41">
-        <v>-0.04849473294423104</v>
+        <v>-0.04849473294423089</v>
       </c>
     </row>
     <row r="42">
@@ -1483,19 +1483,19 @@
         </is>
       </c>
       <c r="C42">
-        <v>2.489084630896463</v>
+        <v>2.489084630896462</v>
       </c>
       <c r="D42">
-        <v>-2.056344732397178</v>
+        <v>-2.056344732397179</v>
       </c>
       <c r="E42">
-        <v>0.4191359173231555</v>
+        <v>0.4191359173231575</v>
       </c>
       <c r="F42">
-        <v>-0.1836270234317797</v>
+        <v>-0.1836270234317793</v>
       </c>
       <c r="G42">
-        <v>-0.07613584152032278</v>
+        <v>-0.07613584152032155</v>
       </c>
     </row>
     <row r="43">
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="C43">
-        <v>-3.368778121051411</v>
+        <v>-3.36877812105141</v>
       </c>
       <c r="D43">
-        <v>-0.01865106303673796</v>
+        <v>-0.01865106303673671</v>
       </c>
       <c r="E43">
-        <v>-0.9323859590842752</v>
+        <v>-0.9323859590842735</v>
       </c>
       <c r="F43">
-        <v>-0.8756926947290875</v>
+        <v>-0.8756926947290892</v>
       </c>
       <c r="G43">
-        <v>0.2170813301007123</v>
+        <v>0.2170813301007147</v>
       </c>
     </row>
     <row r="44">
@@ -1537,19 +1537,19 @@
         </is>
       </c>
       <c r="C44">
-        <v>-0.2243569999550419</v>
+        <v>-0.2243569999550417</v>
       </c>
       <c r="D44">
-        <v>-2.106243470238621</v>
+        <v>-2.10624347023862</v>
       </c>
       <c r="E44">
-        <v>0.1147627637099011</v>
+        <v>0.1147627637099033</v>
       </c>
       <c r="F44">
-        <v>-0.8516998567861885</v>
+        <v>-0.8516998567861886</v>
       </c>
       <c r="G44">
-        <v>-0.2588445312482092</v>
+        <v>-0.2588445312482072</v>
       </c>
     </row>
     <row r="45">
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="C45">
-        <v>4.749096909165897</v>
+        <v>4.749096909165893</v>
       </c>
       <c r="D45">
-        <v>1.059776736631399</v>
+        <v>1.059776736631397</v>
       </c>
       <c r="E45">
-        <v>1.030955663928605</v>
+        <v>1.030955663928607</v>
       </c>
       <c r="F45">
-        <v>-0.6730287446641818</v>
+        <v>-0.6730287446641808</v>
       </c>
       <c r="G45">
-        <v>0.5029498984690517</v>
+        <v>0.5029498984690522</v>
       </c>
     </row>
     <row r="46">
@@ -1591,19 +1591,19 @@
         </is>
       </c>
       <c r="C46">
-        <v>-5.31266772518252</v>
+        <v>-5.312667725182518</v>
       </c>
       <c r="D46">
-        <v>0.1184250817458858</v>
+        <v>0.118425081745888</v>
       </c>
       <c r="E46">
-        <v>0.2620661789993184</v>
+        <v>0.2620661789993196</v>
       </c>
       <c r="F46">
-        <v>0.1151457180337693</v>
+        <v>0.1151457180337687</v>
       </c>
       <c r="G46">
-        <v>0.08044630927152813</v>
+        <v>0.08044630927153018</v>
       </c>
     </row>
     <row r="47">
@@ -1618,19 +1618,19 @@
         </is>
       </c>
       <c r="C47">
-        <v>-1.678090260872939</v>
+        <v>-1.678090260872938</v>
       </c>
       <c r="D47">
-        <v>-1.604206936684736</v>
+        <v>-1.604206936684734</v>
       </c>
       <c r="E47">
-        <v>-0.8133459678645288</v>
+        <v>-0.8133459678645283</v>
       </c>
       <c r="F47">
-        <v>1.328473895513316</v>
+        <v>1.328473895513315</v>
       </c>
       <c r="G47">
-        <v>0.4476616000845703</v>
+        <v>0.4476616000845719</v>
       </c>
     </row>
     <row r="48">
@@ -1645,19 +1645,19 @@
         </is>
       </c>
       <c r="C48">
-        <v>4.578722506293992</v>
+        <v>4.578722506293989</v>
       </c>
       <c r="D48">
         <v>-3.073875379849784</v>
       </c>
       <c r="E48">
-        <v>-1.395464164855271</v>
+        <v>-1.395464164855269</v>
       </c>
       <c r="F48">
-        <v>-0.6248844286048583</v>
+        <v>-0.6248844286048585</v>
       </c>
       <c r="G48">
-        <v>-0.01761461288863235</v>
+        <v>-0.01761461288863343</v>
       </c>
     </row>
     <row r="49">
@@ -1672,19 +1672,19 @@
         </is>
       </c>
       <c r="C49">
-        <v>4.285219759648148</v>
+        <v>4.285219759648145</v>
       </c>
       <c r="D49">
-        <v>0.193119315362936</v>
+        <v>0.1931193153629344</v>
       </c>
       <c r="E49">
-        <v>0.2369201270884387</v>
+        <v>0.2369201270884403</v>
       </c>
       <c r="F49">
-        <v>0.7824893699850436</v>
+        <v>0.7824893699850441</v>
       </c>
       <c r="G49">
-        <v>0.1263446393685355</v>
+        <v>0.1263446393685351</v>
       </c>
     </row>
     <row r="50">
@@ -1705,13 +1705,13 @@
         <v>1.296209103994193</v>
       </c>
       <c r="E50">
-        <v>-1.261398106218175</v>
+        <v>-1.261398106218174</v>
       </c>
       <c r="F50">
-        <v>-0.1443813602160732</v>
+        <v>-0.1443813602160742</v>
       </c>
       <c r="G50">
-        <v>-0.1854661196744078</v>
+        <v>-0.185466119674407</v>
       </c>
     </row>
     <row r="51">
@@ -1729,16 +1729,16 @@
         <v>-0.671932081061094</v>
       </c>
       <c r="D51">
-        <v>0.3990928484260289</v>
+        <v>0.3990928484260291</v>
       </c>
       <c r="E51">
-        <v>1.613137682805308</v>
+        <v>1.613137682805309</v>
       </c>
       <c r="F51">
-        <v>0.5325019939591247</v>
+        <v>0.5325019939591253</v>
       </c>
       <c r="G51">
-        <v>-0.4081246552675413</v>
+        <v>-0.4081246552675404</v>
       </c>
     </row>
     <row r="52">
@@ -1759,13 +1759,13 @@
         <v>-2.281914249078842</v>
       </c>
       <c r="E52">
-        <v>0.13912483801491</v>
+        <v>0.1391248380149121</v>
       </c>
       <c r="F52">
-        <v>-0.3686937188461792</v>
+        <v>-0.3686937188461789</v>
       </c>
       <c r="G52">
-        <v>-0.09547869995176245</v>
+        <v>-0.09547869995176068</v>
       </c>
     </row>
     <row r="53">
@@ -1780,19 +1780,19 @@
         </is>
       </c>
       <c r="C53">
-        <v>3.272541249207547</v>
+        <v>3.272541249207544</v>
       </c>
       <c r="D53">
-        <v>0.3417726174869303</v>
+        <v>0.3417726174869289</v>
       </c>
       <c r="E53">
-        <v>0.3495006764319972</v>
+        <v>0.3495006764319986</v>
       </c>
       <c r="F53">
-        <v>0.6581962514291878</v>
+        <v>0.6581962514291884</v>
       </c>
       <c r="G53">
-        <v>0.1232131719599877</v>
+        <v>0.1232131719599866</v>
       </c>
     </row>
     <row r="54">
@@ -1807,19 +1807,19 @@
         </is>
       </c>
       <c r="C54">
-        <v>-0.2049768714724092</v>
+        <v>-0.2049768714724096</v>
       </c>
       <c r="D54">
-        <v>0.7130178014944984</v>
+        <v>0.7130178014944983</v>
       </c>
       <c r="E54">
-        <v>0.1646154432143476</v>
+        <v>0.1646154432143491</v>
       </c>
       <c r="F54">
         <v>0.244438653018419</v>
       </c>
       <c r="G54">
-        <v>-0.2618875713288281</v>
+        <v>-0.2618875713288286</v>
       </c>
     </row>
     <row r="55">
@@ -1834,19 +1834,19 @@
         </is>
       </c>
       <c r="C55">
-        <v>0.1867536233745058</v>
+        <v>0.1867536233745059</v>
       </c>
       <c r="D55">
         <v>-1.621670333204347</v>
       </c>
       <c r="E55">
-        <v>0.8072850232121427</v>
+        <v>0.8072850232121443</v>
       </c>
       <c r="F55">
-        <v>-0.119241297601165</v>
+        <v>-0.1192412976011647</v>
       </c>
       <c r="G55">
-        <v>0.2396589428454466</v>
+        <v>0.2396589428454484</v>
       </c>
     </row>
     <row r="56">
@@ -1861,19 +1861,19 @@
         </is>
       </c>
       <c r="C56">
-        <v>2.678433047825529</v>
+        <v>2.678433047825528</v>
       </c>
       <c r="D56">
         <v>-1.789087874325987</v>
       </c>
       <c r="E56">
-        <v>0.6874243135675083</v>
+        <v>0.6874243135675103</v>
       </c>
       <c r="F56">
-        <v>-0.02244085778382099</v>
+        <v>-0.0224408577838206</v>
       </c>
       <c r="G56">
-        <v>-0.2695190268328724</v>
+        <v>-0.2695190268328713</v>
       </c>
     </row>
     <row r="57">
@@ -1888,19 +1888,19 @@
         </is>
       </c>
       <c r="C57">
-        <v>2.639479908689848</v>
+        <v>2.639479908689846</v>
       </c>
       <c r="D57">
-        <v>-0.208224624373042</v>
+        <v>-0.2082246243730431</v>
       </c>
       <c r="E57">
-        <v>1.410272356093724</v>
+        <v>1.410272356093726</v>
       </c>
       <c r="F57">
-        <v>-0.1161968716378104</v>
+        <v>-0.1161968716378096</v>
       </c>
       <c r="G57">
-        <v>0.2769282447262617</v>
+        <v>0.2769282447262629</v>
       </c>
     </row>
     <row r="58">
@@ -1915,19 +1915,19 @@
         </is>
       </c>
       <c r="C58">
-        <v>3.928018089805089</v>
+        <v>3.928018089805086</v>
       </c>
       <c r="D58">
-        <v>0.5933920374116552</v>
+        <v>0.5933920374116536</v>
       </c>
       <c r="E58">
-        <v>0.8970235502762675</v>
+        <v>0.8970235502762693</v>
       </c>
       <c r="F58">
-        <v>0.2300756956572522</v>
+        <v>0.2300756956572528</v>
       </c>
       <c r="G58">
-        <v>-0.1550820677697593</v>
+        <v>-0.1550820677697598</v>
       </c>
     </row>
     <row r="59">
@@ -1942,19 +1942,19 @@
         </is>
       </c>
       <c r="C59">
-        <v>2.155867733615041</v>
+        <v>2.15586773361504</v>
       </c>
       <c r="D59">
-        <v>1.033213949597602</v>
+        <v>1.033213949597601</v>
       </c>
       <c r="E59">
-        <v>-0.737035274118792</v>
+        <v>-0.7370352741187898</v>
       </c>
       <c r="F59">
-        <v>-0.2396354004380742</v>
+        <v>-0.2396354004380745</v>
       </c>
       <c r="G59">
-        <v>0.3602563635082028</v>
+        <v>0.3602563635082026</v>
       </c>
     </row>
     <row r="60">
@@ -1969,19 +1969,19 @@
         </is>
       </c>
       <c r="C60">
-        <v>0.6085148502711343</v>
+        <v>0.6085148502711339</v>
       </c>
       <c r="D60">
-        <v>-2.110271314935639</v>
+        <v>-2.110271314935638</v>
       </c>
       <c r="E60">
-        <v>-2.663791708230662</v>
+        <v>-2.66379170823066</v>
       </c>
       <c r="F60">
-        <v>-0.2969583457570493</v>
+        <v>-0.2969583457570505</v>
       </c>
       <c r="G60">
-        <v>-0.2351376654287063</v>
+        <v>-0.2351376654287084</v>
       </c>
     </row>
     <row r="61">
@@ -2002,13 +2002,13 @@
         <v>1.13181575859879</v>
       </c>
       <c r="E61">
-        <v>0.1910257357272576</v>
+        <v>0.1910257357272593</v>
       </c>
       <c r="F61">
-        <v>-0.2206775119780353</v>
+        <v>-0.2206775119780355</v>
       </c>
       <c r="G61">
-        <v>0.1354245039222509</v>
+        <v>0.1354245039222522</v>
       </c>
     </row>
     <row r="62">
@@ -2023,19 +2023,19 @@
         </is>
       </c>
       <c r="C62">
-        <v>2.978008630934214</v>
+        <v>2.978008630934211</v>
       </c>
       <c r="D62">
-        <v>1.281469248825259</v>
+        <v>1.281469248825258</v>
       </c>
       <c r="E62">
-        <v>-1.441677558800123</v>
+        <v>-1.441677558800121</v>
       </c>
       <c r="F62">
-        <v>0.2945422902924698</v>
+        <v>0.2945422902924693</v>
       </c>
       <c r="G62">
-        <v>-0.2039329884828716</v>
+        <v>-0.203932988482873</v>
       </c>
     </row>
     <row r="63">
@@ -2050,19 +2050,19 @@
         </is>
       </c>
       <c r="C63">
-        <v>4.326480383020593</v>
+        <v>4.32648038302059</v>
       </c>
       <c r="D63">
-        <v>1.080719614141805</v>
+        <v>1.080719614141803</v>
       </c>
       <c r="E63">
-        <v>-0.1087510623745599</v>
+        <v>-0.1087510623745578</v>
       </c>
       <c r="F63">
-        <v>0.2447550923567443</v>
+        <v>0.2447550923567446</v>
       </c>
       <c r="G63">
-        <v>-0.1697239586436758</v>
+        <v>-0.1697239586436769</v>
       </c>
     </row>
     <row r="64">
@@ -2077,19 +2077,19 @@
         </is>
       </c>
       <c r="C64">
-        <v>1.838883116521039</v>
+        <v>1.838883116521038</v>
       </c>
       <c r="D64">
-        <v>-3.046351049597305</v>
+        <v>-3.046351049597303</v>
       </c>
       <c r="E64">
-        <v>0.05241220466064509</v>
+        <v>0.05241220466064667</v>
       </c>
       <c r="F64">
-        <v>-0.5093971560265979</v>
+        <v>-0.5093971560265975</v>
       </c>
       <c r="G64">
-        <v>0.3816328403939631</v>
+        <v>0.3816328403939651</v>
       </c>
     </row>
     <row r="65">
@@ -2104,19 +2104,19 @@
         </is>
       </c>
       <c r="C65">
-        <v>2.088809361968091</v>
+        <v>2.08880936196809</v>
       </c>
       <c r="D65">
         <v>-2.042287616157224</v>
       </c>
       <c r="E65">
-        <v>0.1469022811211879</v>
+        <v>0.1469022811211898</v>
       </c>
       <c r="F65">
-        <v>-0.1755780701912579</v>
+        <v>-0.1755780701912577</v>
       </c>
       <c r="G65">
-        <v>-0.180960705471765</v>
+        <v>-0.1809607054717637</v>
       </c>
     </row>
     <row r="66">
@@ -2131,19 +2131,19 @@
         </is>
       </c>
       <c r="C66">
-        <v>-1.046978305085391</v>
+        <v>-1.04697830508539</v>
       </c>
       <c r="D66">
-        <v>-0.06927575354823634</v>
+        <v>-0.06927575354823587</v>
       </c>
       <c r="E66">
-        <v>0.564096645142356</v>
+        <v>0.5640966451423571</v>
       </c>
       <c r="F66">
-        <v>0.4958434651606331</v>
+        <v>0.4958434651606332</v>
       </c>
       <c r="G66">
-        <v>0.3272279140742092</v>
+        <v>0.3272279140742093</v>
       </c>
     </row>
     <row r="67">
@@ -2158,19 +2158,19 @@
         </is>
       </c>
       <c r="C67">
-        <v>-0.4055477603826898</v>
+        <v>-0.4055477603826896</v>
       </c>
       <c r="D67">
-        <v>-0.8111304380514205</v>
+        <v>-0.8111304380514203</v>
       </c>
       <c r="E67">
-        <v>-0.06598002979323396</v>
+        <v>-0.0659800297932322</v>
       </c>
       <c r="F67">
-        <v>-0.1171552334109791</v>
+        <v>-0.1171552334109793</v>
       </c>
       <c r="G67">
-        <v>-0.101495209848351</v>
+        <v>-0.1014952098483496</v>
       </c>
     </row>
     <row r="68">
@@ -2185,19 +2185,19 @@
         </is>
       </c>
       <c r="C68">
-        <v>2.306439816136894</v>
+        <v>2.306439816136892</v>
       </c>
       <c r="D68">
-        <v>0.551349751076776</v>
+        <v>0.5513497510767748</v>
       </c>
       <c r="E68">
-        <v>0.4483523737329083</v>
+        <v>0.4483523737329105</v>
       </c>
       <c r="F68">
-        <v>-0.3512150138981202</v>
+        <v>-0.3512150138981199</v>
       </c>
       <c r="G68">
-        <v>-0.2073833112373159</v>
+        <v>-0.2073833112373152</v>
       </c>
     </row>
     <row r="69">
@@ -2212,19 +2212,19 @@
         </is>
       </c>
       <c r="C69">
-        <v>0.7309617150881331</v>
+        <v>0.7309617150881323</v>
       </c>
       <c r="D69">
-        <v>0.2046157523991989</v>
+        <v>0.2046157523991985</v>
       </c>
       <c r="E69">
-        <v>-0.3224162907751006</v>
+        <v>-0.3224162907750989</v>
       </c>
       <c r="F69">
-        <v>-0.158155404424946</v>
+        <v>-0.1581554044249461</v>
       </c>
       <c r="G69">
-        <v>0.2378530980856656</v>
+        <v>0.2378530980856661</v>
       </c>
     </row>
     <row r="70">
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="C70">
-        <v>-0.2153542463875026</v>
+        <v>-0.2153542463875022</v>
       </c>
       <c r="D70">
-        <v>-2.440524589843994</v>
+        <v>-2.440524589843993</v>
       </c>
       <c r="E70">
-        <v>0.3477695069055219</v>
+        <v>0.3477695069055237</v>
       </c>
       <c r="F70">
-        <v>-0.07252153055052714</v>
+        <v>-0.07252153055052704</v>
       </c>
       <c r="G70">
-        <v>-0.1386750227241116</v>
+        <v>-0.1386750227241091</v>
       </c>
     </row>
     <row r="71">
@@ -2266,19 +2266,19 @@
         </is>
       </c>
       <c r="C71">
-        <v>4.072193914804727</v>
+        <v>4.072193914804724</v>
       </c>
       <c r="D71">
-        <v>1.490838026491348</v>
+        <v>1.490838026491346</v>
       </c>
       <c r="E71">
-        <v>0.2399832462179211</v>
+        <v>0.2399832462179232</v>
       </c>
       <c r="F71">
-        <v>0.1441799051439579</v>
+        <v>0.1441799051439584</v>
       </c>
       <c r="G71">
-        <v>0.3811251432897867</v>
+        <v>0.381125143289787</v>
       </c>
     </row>
     <row r="72">
@@ -2293,19 +2293,19 @@
         </is>
       </c>
       <c r="C72">
-        <v>-7.308993242058845</v>
+        <v>-7.308993242058841</v>
       </c>
       <c r="D72">
-        <v>0.3326700197255399</v>
+        <v>0.3326700197255424</v>
       </c>
       <c r="E72">
-        <v>-0.4465632819506336</v>
+        <v>-0.4465632819506321</v>
       </c>
       <c r="F72">
-        <v>-0.0118701143401527</v>
+        <v>-0.01187011434015369</v>
       </c>
       <c r="G72">
-        <v>-0.09068772675652453</v>
+        <v>-0.09068772675652183</v>
       </c>
     </row>
     <row r="73">
@@ -2320,19 +2320,19 @@
         </is>
       </c>
       <c r="C73">
-        <v>-5.355161607867726</v>
+        <v>-5.355161607867724</v>
       </c>
       <c r="D73">
-        <v>0.3307754588608446</v>
+        <v>0.3307754588608462</v>
       </c>
       <c r="E73">
-        <v>0.1550595678727873</v>
+        <v>0.1550595678727887</v>
       </c>
       <c r="F73">
-        <v>-0.06989499400861453</v>
+        <v>-0.0698949940086151</v>
       </c>
       <c r="G73">
-        <v>-0.03075559947683866</v>
+        <v>-0.03075559947683573</v>
       </c>
     </row>
     <row r="74">
@@ -2347,16 +2347,16 @@
         </is>
       </c>
       <c r="C74">
-        <v>1.060001391955628</v>
+        <v>1.060001391955627</v>
       </c>
       <c r="D74">
-        <v>1.605397258288109</v>
+        <v>1.605397258288108</v>
       </c>
       <c r="E74">
-        <v>-0.2834849557121899</v>
+        <v>-0.2834849557121878</v>
       </c>
       <c r="F74">
-        <v>-0.1021971701441708</v>
+        <v>-0.102197170144171</v>
       </c>
       <c r="G74">
         <v>-0.4816696525619676</v>
@@ -2374,19 +2374,19 @@
         </is>
       </c>
       <c r="C75">
-        <v>-4.311929953987279</v>
+        <v>-4.311929953987276</v>
       </c>
       <c r="D75">
-        <v>0.3776583803883583</v>
+        <v>0.3776583803883596</v>
       </c>
       <c r="E75">
-        <v>0.3009198243566053</v>
+        <v>0.3009198243566069</v>
       </c>
       <c r="F75">
-        <v>-0.5236367678403476</v>
+        <v>-0.5236367678403483</v>
       </c>
       <c r="G75">
-        <v>-0.1868454507832504</v>
+        <v>-0.1868454507832477</v>
       </c>
     </row>
     <row r="76">
@@ -2401,19 +2401,19 @@
         </is>
       </c>
       <c r="C76">
-        <v>-4.558419823388314</v>
+        <v>-4.558419823388312</v>
       </c>
       <c r="D76">
-        <v>0.809807100128877</v>
+        <v>0.809807100128878</v>
       </c>
       <c r="E76">
-        <v>0.3446253029196795</v>
+        <v>0.3446253029196813</v>
       </c>
       <c r="F76">
-        <v>-0.4525359706367909</v>
+        <v>-0.4525359706367912</v>
       </c>
       <c r="G76">
-        <v>0.4677691523087504</v>
+        <v>0.4677691523087531</v>
       </c>
     </row>
     <row r="77">
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="C77">
-        <v>3.153846673028684</v>
+        <v>3.153846673028681</v>
       </c>
       <c r="D77">
-        <v>0.8311316493977866</v>
+        <v>0.8311316493977849</v>
       </c>
       <c r="E77">
-        <v>0.2536030106886932</v>
+        <v>0.2536030106886949</v>
       </c>
       <c r="F77">
-        <v>0.492998303861284</v>
+        <v>0.4929983038612844</v>
       </c>
       <c r="G77">
-        <v>0.53923720679641</v>
+        <v>0.5392372067964116</v>
       </c>
     </row>
     <row r="78">
@@ -2455,19 +2455,19 @@
         </is>
       </c>
       <c r="C78">
-        <v>1.818706471440117</v>
+        <v>1.818706471440115</v>
       </c>
       <c r="D78">
-        <v>-0.2668661910807248</v>
+        <v>-0.2668661910807256</v>
       </c>
       <c r="E78">
-        <v>1.423545719848316</v>
+        <v>1.423545719848318</v>
       </c>
       <c r="F78">
-        <v>-0.1142604356294304</v>
+        <v>-0.1142604356294298</v>
       </c>
       <c r="G78">
-        <v>-0.1225289449298947</v>
+        <v>-0.1225289449298935</v>
       </c>
     </row>
     <row r="79">
@@ -2485,16 +2485,16 @@
         <v>-1.190164051065726</v>
       </c>
       <c r="D79">
-        <v>0.7830051630621292</v>
+        <v>0.7830051630621293</v>
       </c>
       <c r="E79">
-        <v>0.7911386445257153</v>
+        <v>0.7911386445257169</v>
       </c>
       <c r="F79">
-        <v>0.2751031702932097</v>
+        <v>0.2751031702932099</v>
       </c>
       <c r="G79">
-        <v>-0.1563926872584036</v>
+        <v>-0.1563926872584024</v>
       </c>
     </row>
     <row r="80">
@@ -2509,19 +2509,19 @@
         </is>
       </c>
       <c r="C80">
-        <v>1.551804923159227</v>
+        <v>1.551804923159225</v>
       </c>
       <c r="D80">
-        <v>1.537363933595357</v>
+        <v>1.537363933595356</v>
       </c>
       <c r="E80">
-        <v>-0.6337471239962322</v>
+        <v>-0.6337471239962307</v>
       </c>
       <c r="F80">
-        <v>0.5138738718983273</v>
+        <v>0.5138738718983272</v>
       </c>
       <c r="G80">
-        <v>0.03911411818681017</v>
+        <v>0.03911411818680938</v>
       </c>
     </row>
     <row r="81">
@@ -2536,19 +2536,19 @@
         </is>
       </c>
       <c r="C81">
-        <v>-0.8689826255873982</v>
+        <v>-0.8689826255873978</v>
       </c>
       <c r="D81">
-        <v>-0.6352200919500022</v>
+        <v>-0.6352200919500018</v>
       </c>
       <c r="E81">
-        <v>0.1998068791658802</v>
+        <v>0.1998068791658819</v>
       </c>
       <c r="F81">
-        <v>-0.4816972216677717</v>
+        <v>-0.4816972216677719</v>
       </c>
       <c r="G81">
-        <v>0.1745329721682901</v>
+        <v>0.1745329721682914</v>
       </c>
     </row>
     <row r="82">
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="C82">
-        <v>0.4954525766243011</v>
+        <v>0.4954525766243004</v>
       </c>
       <c r="D82">
-        <v>0.8829499359035645</v>
+        <v>0.8829499359035641</v>
       </c>
       <c r="E82">
-        <v>-0.390757320594099</v>
+        <v>-0.3907573205940975</v>
       </c>
       <c r="F82">
-        <v>0.5558633216349735</v>
+        <v>0.5558633216349734</v>
       </c>
       <c r="G82">
-        <v>0.1311395696355281</v>
+        <v>0.1311395696355294</v>
       </c>
     </row>
     <row r="83">
@@ -2590,19 +2590,19 @@
         </is>
       </c>
       <c r="C83">
-        <v>-2.428530507622122</v>
+        <v>-2.428530507622121</v>
       </c>
       <c r="D83">
-        <v>-0.7102299739853393</v>
+        <v>-0.7102299739853378</v>
       </c>
       <c r="E83">
-        <v>-0.1387904827382173</v>
+        <v>-0.1387904827382161</v>
       </c>
       <c r="F83">
         <v>0.644423915033562</v>
       </c>
       <c r="G83">
-        <v>-0.005397615985510251</v>
+        <v>-0.005397615985507927</v>
       </c>
     </row>
     <row r="84">
@@ -2617,19 +2617,19 @@
         </is>
       </c>
       <c r="C84">
-        <v>-4.207632480797315</v>
+        <v>-4.207632480797313</v>
       </c>
       <c r="D84">
-        <v>-0.5974591053347664</v>
+        <v>-0.5974591053347649</v>
       </c>
       <c r="E84">
-        <v>0.3977391992982613</v>
+        <v>0.3977391992982628</v>
       </c>
       <c r="F84">
-        <v>-0.2814725026207925</v>
+        <v>-0.281472502620793</v>
       </c>
       <c r="G84">
-        <v>-0.08739258855907343</v>
+        <v>-0.08739258855907092</v>
       </c>
     </row>
     <row r="85">
@@ -2644,19 +2644,19 @@
         </is>
       </c>
       <c r="C85">
-        <v>3.296883377125916</v>
+        <v>3.296883377125915</v>
       </c>
       <c r="D85">
-        <v>-3.108595269361777</v>
+        <v>-3.108595269361776</v>
       </c>
       <c r="E85">
-        <v>-0.5193836299236269</v>
+        <v>-0.5193836299236252</v>
       </c>
       <c r="F85">
-        <v>0.460766459961346</v>
+        <v>0.4607664599613461</v>
       </c>
       <c r="G85">
-        <v>-0.01529233279741515</v>
+        <v>-0.01529233279741361</v>
       </c>
     </row>
     <row r="86">
@@ -2671,19 +2671,19 @@
         </is>
       </c>
       <c r="C86">
-        <v>2.223343242839811</v>
+        <v>2.22334324283981</v>
       </c>
       <c r="D86">
         <v>-1.782623295901296</v>
       </c>
       <c r="E86">
-        <v>-0.1516670036381844</v>
+        <v>-0.1516670036381824</v>
       </c>
       <c r="F86">
-        <v>-0.113329691239216</v>
+        <v>-0.1133296912392161</v>
       </c>
       <c r="G86">
-        <v>-0.1153699047285826</v>
+        <v>-0.1153699047285815</v>
       </c>
     </row>
     <row r="87">
@@ -2704,13 +2704,13 @@
         <v>1.094995754201249</v>
       </c>
       <c r="E87">
-        <v>-0.3045837481428788</v>
+        <v>-0.304583748142877</v>
       </c>
       <c r="F87">
-        <v>-0.2992978452694078</v>
+        <v>-0.2992978452694083</v>
       </c>
       <c r="G87">
-        <v>-0.003694024901574815</v>
+        <v>-0.003694024901573587</v>
       </c>
     </row>
     <row r="88">
@@ -2725,19 +2725,19 @@
         </is>
       </c>
       <c r="C88">
-        <v>2.213967839919764</v>
+        <v>2.213967839919763</v>
       </c>
       <c r="D88">
         <v>-3.642399531573024</v>
       </c>
       <c r="E88">
-        <v>-1.308791610133681</v>
+        <v>-1.308791610133679</v>
       </c>
       <c r="F88">
-        <v>-0.01048631135782141</v>
+        <v>-0.01048631135782158</v>
       </c>
       <c r="G88">
-        <v>-0.05447648783820724</v>
+        <v>-0.05447648783820687</v>
       </c>
     </row>
     <row r="89">
@@ -2752,19 +2752,19 @@
         </is>
       </c>
       <c r="C89">
-        <v>0.9630525796409508</v>
+        <v>0.9630525796409497</v>
       </c>
       <c r="D89">
-        <v>1.432823971155345</v>
+        <v>1.432823971155344</v>
       </c>
       <c r="E89">
-        <v>-1.356860991241304</v>
+        <v>-1.356860991241302</v>
       </c>
       <c r="F89">
-        <v>0.274125543135588</v>
+        <v>0.2741255431355875</v>
       </c>
       <c r="G89">
-        <v>0.3468311643223654</v>
+        <v>0.3468311643223657</v>
       </c>
     </row>
     <row r="90">
@@ -2779,19 +2779,19 @@
         </is>
       </c>
       <c r="C90">
-        <v>-1.976299755429064</v>
+        <v>-1.976299755429063</v>
       </c>
       <c r="D90">
-        <v>0.4490814711763203</v>
+        <v>0.4490814711763208</v>
       </c>
       <c r="E90">
-        <v>-0.06965672265047666</v>
+        <v>-0.06965672265047512</v>
       </c>
       <c r="F90">
-        <v>0.1591027525677197</v>
+        <v>0.1591027525677193</v>
       </c>
       <c r="G90">
-        <v>-0.05412161020777761</v>
+        <v>-0.05412161020777715</v>
       </c>
     </row>
     <row r="91">
@@ -2806,16 +2806,16 @@
         </is>
       </c>
       <c r="C91">
-        <v>0.6724232724195447</v>
+        <v>0.6724232724195438</v>
       </c>
       <c r="D91">
-        <v>1.63732868703574</v>
+        <v>1.637328687035739</v>
       </c>
       <c r="E91">
-        <v>-0.04056045650981591</v>
+        <v>-0.04056045650981394</v>
       </c>
       <c r="F91">
-        <v>-0.3692763486917418</v>
+        <v>-0.3692763486917419</v>
       </c>
       <c r="G91">
         <v>0.1066181636633164</v>
@@ -2833,19 +2833,19 @@
         </is>
       </c>
       <c r="C92">
-        <v>0.2279892820746972</v>
+        <v>0.2279892820746969</v>
       </c>
       <c r="D92">
-        <v>-0.1263050455658995</v>
+        <v>-0.1263050455658993</v>
       </c>
       <c r="E92">
-        <v>-0.47228993867193</v>
+        <v>-0.4722899386719293</v>
       </c>
       <c r="F92">
         <v>1.152044647566105</v>
       </c>
       <c r="G92">
-        <v>0.492167827615172</v>
+        <v>0.4921678276151725</v>
       </c>
     </row>
     <row r="93">
@@ -2860,19 +2860,19 @@
         </is>
       </c>
       <c r="C93">
-        <v>0.6207084812428114</v>
+        <v>0.620708481242811</v>
       </c>
       <c r="D93">
-        <v>-0.4288088864632286</v>
+        <v>-0.4288088864632287</v>
       </c>
       <c r="E93">
-        <v>0.9125843708668758</v>
+        <v>0.9125843708668775</v>
       </c>
       <c r="F93">
-        <v>0.2021762112413693</v>
+        <v>0.2021762112413695</v>
       </c>
       <c r="G93">
-        <v>0.1070764116781582</v>
+        <v>0.1070764116781595</v>
       </c>
     </row>
     <row r="94">
@@ -2887,16 +2887,16 @@
         </is>
       </c>
       <c r="C94">
-        <v>-3.209464098499542</v>
+        <v>-3.209464098499541</v>
       </c>
       <c r="D94">
-        <v>-0.09301745161129543</v>
+        <v>-0.09301745161129395</v>
       </c>
       <c r="E94">
         <v>-1.140506235897025</v>
       </c>
       <c r="F94">
-        <v>0.2131791534817229</v>
+        <v>0.213179153481722</v>
       </c>
       <c r="G94">
         <v>0.6117962984542566</v>
@@ -2914,19 +2914,19 @@
         </is>
       </c>
       <c r="C95">
-        <v>-4.450275941957838</v>
+        <v>-4.450275941957836</v>
       </c>
       <c r="D95">
-        <v>0.8517607808846647</v>
+        <v>0.8517607808846663</v>
       </c>
       <c r="E95">
-        <v>0.2330864534390613</v>
+        <v>0.2330864534390628</v>
       </c>
       <c r="F95">
-        <v>-0.180523688049372</v>
+        <v>-0.1805236880493726</v>
       </c>
       <c r="G95">
-        <v>-0.3118989332281577</v>
+        <v>-0.3118989332281555</v>
       </c>
     </row>
     <row r="96">
@@ -2944,16 +2944,16 @@
         <v>-1.576318050430517</v>
       </c>
       <c r="D96">
-        <v>-0.5361239140658718</v>
+        <v>-0.5361239140658709</v>
       </c>
       <c r="E96">
-        <v>0.4254166430755618</v>
+        <v>0.4254166430755632</v>
       </c>
       <c r="F96">
-        <v>0.6444037637408183</v>
+        <v>0.6444037637408181</v>
       </c>
       <c r="G96">
-        <v>-0.4518128480900716</v>
+        <v>-0.4518128480900706</v>
       </c>
     </row>
     <row r="97">
@@ -2968,19 +2968,19 @@
         </is>
       </c>
       <c r="C97">
-        <v>-0.9898303680291431</v>
+        <v>-0.9898303680291427</v>
       </c>
       <c r="D97">
-        <v>-1.616743819932617</v>
+        <v>-1.616743819932616</v>
       </c>
       <c r="E97">
-        <v>0.7598421249557644</v>
+        <v>0.7598421249557662</v>
       </c>
       <c r="F97">
         <v>0.1265621008949634</v>
       </c>
       <c r="G97">
-        <v>-0.3077427012292254</v>
+        <v>-0.3077427012292235</v>
       </c>
     </row>
     <row r="98">
@@ -2995,19 +2995,19 @@
         </is>
       </c>
       <c r="C98">
-        <v>-3.16442402594597</v>
+        <v>-3.164424025945969</v>
       </c>
       <c r="D98">
-        <v>0.6709544364261054</v>
+        <v>0.6709544364261059</v>
       </c>
       <c r="E98">
-        <v>0.7555157926978063</v>
+        <v>0.7555157926978084</v>
       </c>
       <c r="F98">
-        <v>-0.6581510736417272</v>
+        <v>-0.6581510736417275</v>
       </c>
       <c r="G98">
-        <v>0.1421992464148083</v>
+        <v>0.1421992464148102</v>
       </c>
     </row>
     <row r="99">
@@ -3022,19 +3022,19 @@
         </is>
       </c>
       <c r="C99">
-        <v>1.669298359858973</v>
+        <v>1.669298359858971</v>
       </c>
       <c r="D99">
-        <v>0.8932690590817625</v>
+        <v>0.8932690590817612</v>
       </c>
       <c r="E99">
-        <v>0.8090183454505806</v>
+        <v>0.8090183454505828</v>
       </c>
       <c r="F99">
-        <v>-0.03069507886103243</v>
+        <v>-0.03069507886103217</v>
       </c>
       <c r="G99">
-        <v>-0.5528991437093838</v>
+        <v>-0.552899143709384</v>
       </c>
     </row>
     <row r="100">
@@ -3049,19 +3049,19 @@
         </is>
       </c>
       <c r="C100">
-        <v>0.6804188423062482</v>
+        <v>0.6804188423062473</v>
       </c>
       <c r="D100">
-        <v>1.266134330467869</v>
+        <v>1.266134330467868</v>
       </c>
       <c r="E100">
-        <v>0.4900547800133155</v>
+        <v>0.4900547800133173</v>
       </c>
       <c r="F100">
-        <v>0.1496486327960031</v>
+        <v>0.1496486327960032</v>
       </c>
       <c r="G100">
-        <v>-0.01802461150397997</v>
+        <v>-0.01802461150397953</v>
       </c>
     </row>
     <row r="101">
@@ -3076,19 +3076,19 @@
         </is>
       </c>
       <c r="C101">
-        <v>1.329536367937857</v>
+        <v>1.329536367937856</v>
       </c>
       <c r="D101">
-        <v>-1.564696399731357</v>
+        <v>-1.564696399731356</v>
       </c>
       <c r="E101">
-        <v>0.5083538030644432</v>
+        <v>0.5083538030644446</v>
       </c>
       <c r="F101">
-        <v>0.7193976667372154</v>
+        <v>0.7193976667372155</v>
       </c>
       <c r="G101">
-        <v>0.08876463325452071</v>
+        <v>0.08876463325452195</v>
       </c>
     </row>
     <row r="102">
@@ -3103,19 +3103,19 @@
         </is>
       </c>
       <c r="C102">
-        <v>4.198989527674147</v>
+        <v>4.198989527674144</v>
       </c>
       <c r="D102">
-        <v>0.6871587100076597</v>
+        <v>0.6871587100076577</v>
       </c>
       <c r="E102">
-        <v>1.150966165223364</v>
+        <v>1.150966165223366</v>
       </c>
       <c r="F102">
-        <v>0.1332713475713787</v>
+        <v>0.1332713475713795</v>
       </c>
       <c r="G102">
-        <v>-0.1482709585601471</v>
+        <v>-0.1482709585601468</v>
       </c>
     </row>
     <row r="103">
@@ -3130,19 +3130,19 @@
         </is>
       </c>
       <c r="C103">
-        <v>-1.654019461536866</v>
+        <v>-1.654019461536865</v>
       </c>
       <c r="D103">
-        <v>-1.7667911885383</v>
+        <v>-1.766791188538298</v>
       </c>
       <c r="E103">
-        <v>0.05633485469453855</v>
+        <v>0.05633485469454008</v>
       </c>
       <c r="F103">
-        <v>-0.03717375342405869</v>
+        <v>-0.03717375342405887</v>
       </c>
       <c r="G103">
-        <v>0.07397934576581662</v>
+        <v>0.07397934576581847</v>
       </c>
     </row>
     <row r="104">
@@ -3157,19 +3157,19 @@
         </is>
       </c>
       <c r="C104">
-        <v>3.037383595014795</v>
+        <v>3.037383595014793</v>
       </c>
       <c r="D104">
-        <v>0.01389639146740207</v>
+        <v>0.01389639146740087</v>
       </c>
       <c r="E104">
-        <v>0.1275561831332938</v>
+        <v>0.1275561831332956</v>
       </c>
       <c r="F104">
-        <v>0.2554339809205055</v>
+        <v>0.2554339809205058</v>
       </c>
       <c r="G104">
-        <v>0.1298215758055991</v>
+        <v>0.1298215758055996</v>
       </c>
     </row>
     <row r="105">
@@ -3184,19 +3184,19 @@
         </is>
       </c>
       <c r="C105">
-        <v>-1.070036543989075</v>
+        <v>-1.070036543989074</v>
       </c>
       <c r="D105">
-        <v>-0.5430870642115886</v>
+        <v>-0.5430870642115881</v>
       </c>
       <c r="E105">
-        <v>-0.2699654829430294</v>
+        <v>-0.2699654829430274</v>
       </c>
       <c r="F105">
-        <v>-0.6567802168124105</v>
+        <v>-0.6567802168124111</v>
       </c>
       <c r="G105">
-        <v>-0.2390297608061923</v>
+        <v>-0.2390297608061914</v>
       </c>
     </row>
     <row r="106">
@@ -3211,19 +3211,19 @@
         </is>
       </c>
       <c r="C106">
-        <v>-4.822470806990067</v>
+        <v>-4.822470806990063</v>
       </c>
       <c r="D106">
-        <v>-1.227471940152562</v>
+        <v>-1.227471940152559</v>
       </c>
       <c r="E106">
-        <v>-0.6282183177806371</v>
+        <v>-0.6282183177806362</v>
       </c>
       <c r="F106">
-        <v>0.9195846083635264</v>
+        <v>0.9195846083635255</v>
       </c>
       <c r="G106">
-        <v>-0.08043600581986247</v>
+        <v>-0.08043600581986139</v>
       </c>
     </row>
     <row r="107">
@@ -3238,19 +3238,19 @@
         </is>
       </c>
       <c r="C107">
-        <v>0.5852032906460606</v>
+        <v>0.5852032906460596</v>
       </c>
       <c r="D107">
-        <v>1.274065357701716</v>
+        <v>1.274065357701715</v>
       </c>
       <c r="E107">
-        <v>-1.024701010336414</v>
+        <v>-1.024701010336413</v>
       </c>
       <c r="F107">
-        <v>8.434121034249009E-05</v>
+        <v>8.434121034185758E-05</v>
       </c>
       <c r="G107">
-        <v>-0.2022930053265222</v>
+        <v>-0.2022930053265227</v>
       </c>
     </row>
     <row r="108">
@@ -3265,19 +3265,19 @@
         </is>
       </c>
       <c r="C108">
-        <v>2.039601039167267</v>
+        <v>2.039601039167265</v>
       </c>
       <c r="D108">
-        <v>-0.05147424789989331</v>
+        <v>-0.05147424789989413</v>
       </c>
       <c r="E108">
-        <v>0.4756751997726388</v>
+        <v>0.4756751997726407</v>
       </c>
       <c r="F108">
-        <v>-0.03420857412944713</v>
+        <v>-0.03420857412944679</v>
       </c>
       <c r="G108">
-        <v>0.137248913805401</v>
+        <v>0.1372489138054017</v>
       </c>
     </row>
     <row r="109">
@@ -3292,19 +3292,19 @@
         </is>
       </c>
       <c r="C109">
-        <v>4.364622837018586</v>
+        <v>4.364622837018583</v>
       </c>
       <c r="D109">
-        <v>1.093905451282976</v>
+        <v>1.093905451282974</v>
       </c>
       <c r="E109">
-        <v>0.4709624963681696</v>
+        <v>0.4709624963681721</v>
       </c>
       <c r="F109">
-        <v>0.1354560508997184</v>
+        <v>0.1354560508997188</v>
       </c>
       <c r="G109">
-        <v>-0.3073299043718125</v>
+        <v>-0.3073299043718131</v>
       </c>
     </row>
     <row r="110">
@@ -3319,19 +3319,19 @@
         </is>
       </c>
       <c r="C110">
-        <v>-4.939260587579534</v>
+        <v>-4.939260587579532</v>
       </c>
       <c r="D110">
-        <v>0.3695308830383374</v>
+        <v>0.3695308830383392</v>
       </c>
       <c r="E110">
-        <v>-0.06313494306676586</v>
+        <v>-0.06313494306676404</v>
       </c>
       <c r="F110">
-        <v>-0.3922952497074156</v>
+        <v>-0.3922952497074163</v>
       </c>
       <c r="G110">
-        <v>0.02683710875454775</v>
+        <v>0.02683710875454953</v>
       </c>
     </row>
     <row r="111">
@@ -3346,19 +3346,19 @@
         </is>
       </c>
       <c r="C111">
-        <v>1.830176137181055</v>
+        <v>1.830176137181053</v>
       </c>
       <c r="D111">
-        <v>0.8756021853218824</v>
+        <v>0.8756021853218813</v>
       </c>
       <c r="E111">
-        <v>0.2480995621645692</v>
+        <v>0.2480995621645707</v>
       </c>
       <c r="F111">
-        <v>0.8268645098252665</v>
+        <v>0.8268645098252667</v>
       </c>
       <c r="G111">
-        <v>0.2154763903072828</v>
+        <v>0.2154763903072833</v>
       </c>
     </row>
     <row r="112">
@@ -3373,19 +3373,19 @@
         </is>
       </c>
       <c r="C112">
-        <v>5.130553095331353</v>
+        <v>5.130553095331351</v>
       </c>
       <c r="D112">
-        <v>-0.4558223827828693</v>
+        <v>-0.4558223827828711</v>
       </c>
       <c r="E112">
-        <v>0.8057986872331814</v>
+        <v>0.8057986872331836</v>
       </c>
       <c r="F112">
-        <v>-0.2112536575347258</v>
+        <v>-0.211253657534725</v>
       </c>
       <c r="G112">
-        <v>-0.0596843487940187</v>
+        <v>-0.0596843487940186</v>
       </c>
     </row>
     <row r="113">
@@ -3403,16 +3403,16 @@
         <v>-1.304354471110287</v>
       </c>
       <c r="D113">
-        <v>-0.6297775958910014</v>
+        <v>-0.6297775958910005</v>
       </c>
       <c r="E113">
-        <v>0.2349934986025725</v>
+        <v>0.2349934986025744</v>
       </c>
       <c r="F113">
-        <v>-0.3748811440696153</v>
+        <v>-0.3748811440696154</v>
       </c>
       <c r="G113">
-        <v>0.09632058723875823</v>
+        <v>0.09632058723876061</v>
       </c>
     </row>
     <row r="114">
@@ -3427,19 +3427,19 @@
         </is>
       </c>
       <c r="C114">
-        <v>-5.052795836491384</v>
+        <v>-5.052795836491382</v>
       </c>
       <c r="D114">
-        <v>-0.2801257539262166</v>
+        <v>-0.2801257539262147</v>
       </c>
       <c r="E114">
-        <v>0.03695708634918365</v>
+        <v>0.03695708634918604</v>
       </c>
       <c r="F114">
-        <v>-0.2328158706791676</v>
+        <v>-0.2328158706791684</v>
       </c>
       <c r="G114">
-        <v>-0.2337900467052712</v>
+        <v>-0.2337900467052686</v>
       </c>
     </row>
     <row r="115">
@@ -3454,19 +3454,19 @@
         </is>
       </c>
       <c r="C115">
-        <v>-0.6997740988308282</v>
+        <v>-0.6997740988308284</v>
       </c>
       <c r="D115">
-        <v>0.976865168443654</v>
+        <v>0.9768651684436539</v>
       </c>
       <c r="E115">
-        <v>0.3761030447395771</v>
+        <v>0.3761030447395787</v>
       </c>
       <c r="F115">
-        <v>0.4687455180605845</v>
+        <v>0.4687455180605846</v>
       </c>
       <c r="G115">
-        <v>-0.1308705042300833</v>
+        <v>-0.1308705042300828</v>
       </c>
     </row>
     <row r="116">
@@ -3481,19 +3481,19 @@
         </is>
       </c>
       <c r="C116">
-        <v>-1.465055913625762</v>
+        <v>-1.465055913625761</v>
       </c>
       <c r="D116">
-        <v>0.6658709120428435</v>
+        <v>0.6658709120428438</v>
       </c>
       <c r="E116">
-        <v>-0.4293315995625739</v>
+        <v>-0.4293315995625723</v>
       </c>
       <c r="F116">
-        <v>-0.2102229808059846</v>
+        <v>-0.2102229808059854</v>
       </c>
       <c r="G116">
-        <v>0.1113166238758161</v>
+        <v>0.1113166238758167</v>
       </c>
     </row>
     <row r="117">
@@ -3508,19 +3508,19 @@
         </is>
       </c>
       <c r="C117">
-        <v>-3.06854017960869</v>
+        <v>-3.068540179608688</v>
       </c>
       <c r="D117">
-        <v>0.7724370817636109</v>
+        <v>0.7724370817636117</v>
       </c>
       <c r="E117">
-        <v>-0.8028256011123475</v>
+        <v>-0.8028256011123457</v>
       </c>
       <c r="F117">
-        <v>-0.5571921881122618</v>
+        <v>-0.5571921881122626</v>
       </c>
       <c r="G117">
-        <v>0.1703554482709405</v>
+        <v>0.1703554482709433</v>
       </c>
     </row>
     <row r="118">
@@ -3535,19 +3535,19 @@
         </is>
       </c>
       <c r="C118">
-        <v>3.236199256707724</v>
+        <v>3.236199256707722</v>
       </c>
       <c r="D118">
-        <v>0.3516991717151899</v>
+        <v>0.3516991717151886</v>
       </c>
       <c r="E118">
-        <v>-0.7789631749972796</v>
+        <v>-0.7789631749972781</v>
       </c>
       <c r="F118">
-        <v>0.1401923469501549</v>
+        <v>0.1401923469501548</v>
       </c>
       <c r="G118">
-        <v>-0.1354334775461467</v>
+        <v>-0.1354334775461476</v>
       </c>
     </row>
     <row r="119">
@@ -3565,16 +3565,16 @@
         <v>-1.241489632773379</v>
       </c>
       <c r="D119">
-        <v>-0.292497365926838</v>
+        <v>-0.2924973659268374</v>
       </c>
       <c r="E119">
-        <v>0.2286884392392521</v>
+        <v>0.2286884392392537</v>
       </c>
       <c r="F119">
-        <v>-0.268605701244207</v>
+        <v>-0.2686057012442072</v>
       </c>
       <c r="G119">
-        <v>0.1767061097088141</v>
+        <v>0.1767061097088145</v>
       </c>
     </row>
     <row r="120">
@@ -3589,19 +3589,19 @@
         </is>
       </c>
       <c r="C120">
-        <v>4.314601512445955</v>
+        <v>4.314601512445951</v>
       </c>
       <c r="D120">
-        <v>0.9385871909566862</v>
+        <v>0.9385871909566845</v>
       </c>
       <c r="E120">
-        <v>-0.8978563755280095</v>
+        <v>-0.8978563755280076</v>
       </c>
       <c r="F120">
-        <v>0.01256691999150242</v>
+        <v>0.01256691999150239</v>
       </c>
       <c r="G120">
-        <v>-0.02146180262284441</v>
+        <v>-0.02146180262284474</v>
       </c>
     </row>
     <row r="121">
@@ -3616,19 +3616,19 @@
         </is>
       </c>
       <c r="C121">
-        <v>-5.476687090951429</v>
+        <v>-5.476687090951426</v>
       </c>
       <c r="D121">
-        <v>0.8883934868949048</v>
+        <v>0.8883934868949065</v>
       </c>
       <c r="E121">
-        <v>0.3523067216213299</v>
+        <v>0.3523067216213319</v>
       </c>
       <c r="F121">
-        <v>-0.2481866302343834</v>
+        <v>-0.2481866302343841</v>
       </c>
       <c r="G121">
-        <v>-0.1691219155382172</v>
+        <v>-0.1691219155382145</v>
       </c>
     </row>
     <row r="122">
@@ -3643,19 +3643,19 @@
         </is>
       </c>
       <c r="C122">
-        <v>-0.6279705216780006</v>
+        <v>-0.6279705216780007</v>
       </c>
       <c r="D122">
         <v>1.145915459201077</v>
       </c>
       <c r="E122">
-        <v>-0.5287209277397924</v>
+        <v>-0.5287209277397911</v>
       </c>
       <c r="F122">
-        <v>-0.07536745660616968</v>
+        <v>-0.07536745660617022</v>
       </c>
       <c r="G122">
-        <v>0.3209596577948399</v>
+        <v>0.3209596577948394</v>
       </c>
     </row>
     <row r="123">
@@ -3670,19 +3670,19 @@
         </is>
       </c>
       <c r="C123">
-        <v>-1.498501414677737</v>
+        <v>-1.498501414677736</v>
       </c>
       <c r="D123">
-        <v>-0.5488116284495399</v>
+        <v>-0.5488116284495389</v>
       </c>
       <c r="E123">
-        <v>-0.587614621099531</v>
+        <v>-0.5876146210995294</v>
       </c>
       <c r="F123">
-        <v>-0.3433000054630378</v>
+        <v>-0.3433000054630384</v>
       </c>
       <c r="G123">
-        <v>0.1440230749754973</v>
+        <v>0.1440230749754979</v>
       </c>
     </row>
     <row r="124">
@@ -3697,19 +3697,19 @@
         </is>
       </c>
       <c r="C124">
-        <v>1.552568295549103</v>
+        <v>1.552568295549102</v>
       </c>
       <c r="D124">
-        <v>0.1334820356507687</v>
+        <v>0.1334820356507678</v>
       </c>
       <c r="E124">
-        <v>-0.3303571102712911</v>
+        <v>-0.3303571102712888</v>
       </c>
       <c r="F124">
-        <v>-0.8771733063297347</v>
+        <v>-0.8771733063297348</v>
       </c>
       <c r="G124">
-        <v>0.07314316315684234</v>
+        <v>0.07314316315684333</v>
       </c>
     </row>
     <row r="125">
@@ -3724,19 +3724,19 @@
         </is>
       </c>
       <c r="C125">
-        <v>-3.825632944544781</v>
+        <v>-3.825632944544779</v>
       </c>
       <c r="D125">
-        <v>-0.4457421579192028</v>
+        <v>-0.4457421579192012</v>
       </c>
       <c r="E125">
-        <v>1.576065725670755</v>
+        <v>1.576065725670757</v>
       </c>
       <c r="F125">
-        <v>0.08728708963493652</v>
+        <v>0.0872870896349368</v>
       </c>
       <c r="G125">
-        <v>0.5321417501620751</v>
+        <v>0.5321417501620777</v>
       </c>
     </row>
     <row r="126">
@@ -3751,19 +3751,19 @@
         </is>
       </c>
       <c r="C126">
-        <v>-5.460312204871443</v>
+        <v>-5.460312204871441</v>
       </c>
       <c r="D126">
-        <v>0.241139961473649</v>
+        <v>0.241139961473651</v>
       </c>
       <c r="E126">
-        <v>0.1609010054702589</v>
+        <v>0.1609010054702602</v>
       </c>
       <c r="F126">
-        <v>-0.1703946301953234</v>
+        <v>-0.1703946301953241</v>
       </c>
       <c r="G126">
-        <v>-0.1124353026961364</v>
+        <v>-0.1124353026961348</v>
       </c>
     </row>
   </sheetData>

--- a/03_Outputs/all/03_DS/ds_idx15_vejez.xlsx
+++ b/03_Outputs/all/03_DS/ds_idx15_vejez.xlsx
@@ -403,19 +403,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>1.914875836338044</v>
+        <v>1.839010871902225</v>
       </c>
       <c r="D2">
-        <v>-2.348971029611666</v>
+        <v>-2.161913593890198</v>
       </c>
       <c r="E2">
-        <v>-0.4064627436056047</v>
+        <v>-0.04420605477791918</v>
       </c>
       <c r="F2">
-        <v>-0.5269395412491381</v>
+        <v>-0.5333685648376264</v>
       </c>
       <c r="G2">
-        <v>-0.2191939359627335</v>
+        <v>0.2666304125916659</v>
       </c>
     </row>
     <row r="3">
@@ -430,19 +430,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>2.738357441447329</v>
+        <v>1.639520822575078</v>
       </c>
       <c r="D3">
-        <v>1.514773735906487</v>
+        <v>1.68066208560771</v>
       </c>
       <c r="E3">
-        <v>-0.7982418132964311</v>
+        <v>-0.3954520239065</v>
       </c>
       <c r="F3">
-        <v>0.2219103758747128</v>
+        <v>0.1580503838153209</v>
       </c>
       <c r="G3">
-        <v>0.1697751064112071</v>
+        <v>-0.08479564373818936</v>
       </c>
     </row>
     <row r="4">
@@ -457,19 +457,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>1.870076949567595</v>
+        <v>0.5535312598093336</v>
       </c>
       <c r="D4">
-        <v>1.183394982467197</v>
+        <v>0.9887228562416728</v>
       </c>
       <c r="E4">
-        <v>0.6479417771450322</v>
+        <v>1.100558360246861</v>
       </c>
       <c r="F4">
-        <v>-0.194570149436314</v>
+        <v>-0.1432162381070479</v>
       </c>
       <c r="G4">
-        <v>0.1143571558618939</v>
+        <v>-0.05552146679948636</v>
       </c>
     </row>
     <row r="5">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>1.305571520702834</v>
+        <v>0.286072138613866</v>
       </c>
       <c r="D5">
-        <v>1.101983647394617</v>
+        <v>0.4347621279891651</v>
       </c>
       <c r="E5">
-        <v>-1.202032648636598</v>
+        <v>1.561363062943767</v>
       </c>
       <c r="F5">
-        <v>-0.1685415589295975</v>
+        <v>-0.2261745448323392</v>
       </c>
       <c r="G5">
-        <v>0.1477336156042715</v>
+        <v>0.06577518121067361</v>
       </c>
     </row>
     <row r="6">
@@ -511,19 +511,19 @@
         </is>
       </c>
       <c r="C6">
-        <v>1.352205629359006</v>
+        <v>1.400753956318101</v>
       </c>
       <c r="D6">
-        <v>-1.443996762495321</v>
+        <v>-0.8975277534409311</v>
       </c>
       <c r="E6">
-        <v>0.7581611725411148</v>
+        <v>-0.9227941135775906</v>
       </c>
       <c r="F6">
-        <v>0.5251095575949135</v>
+        <v>0.552029611871715</v>
       </c>
       <c r="G6">
-        <v>-0.07250163462953454</v>
+        <v>-0.064916977753503</v>
       </c>
     </row>
     <row r="7">
@@ -538,19 +538,19 @@
         </is>
       </c>
       <c r="C7">
-        <v>-1.585092952044973</v>
+        <v>-1.030632857018809</v>
       </c>
       <c r="D7">
-        <v>0.8269575722680066</v>
+        <v>0.7832096851529837</v>
       </c>
       <c r="E7">
-        <v>0.1679300552036828</v>
+        <v>-0.112785492770087</v>
       </c>
       <c r="F7">
-        <v>-0.1660361200343501</v>
+        <v>-0.1922963360953172</v>
       </c>
       <c r="G7">
-        <v>0.2923220688316568</v>
+        <v>-0.1321071363263636</v>
       </c>
     </row>
     <row r="8">
@@ -565,19 +565,19 @@
         </is>
       </c>
       <c r="C8">
-        <v>1.00808052354628</v>
+        <v>0.484234626465866</v>
       </c>
       <c r="D8">
-        <v>0.8408962772568725</v>
+        <v>0.9016786126393537</v>
       </c>
       <c r="E8">
-        <v>-0.01693279457625516</v>
+        <v>0.06281784227073628</v>
       </c>
       <c r="F8">
-        <v>-0.2858792877962741</v>
+        <v>-0.275421491205485</v>
       </c>
       <c r="G8">
-        <v>-0.06866952353239925</v>
+        <v>0.04290856788822662</v>
       </c>
     </row>
     <row r="9">
@@ -592,19 +592,19 @@
         </is>
       </c>
       <c r="C9">
-        <v>1.965270305393886</v>
+        <v>0.9544907682887368</v>
       </c>
       <c r="D9">
-        <v>-0.5076099086725117</v>
+        <v>-0.7053052633378093</v>
       </c>
       <c r="E9">
-        <v>0.210539160212582</v>
+        <v>0.7752419964191987</v>
       </c>
       <c r="F9">
-        <v>1.245853747272181</v>
+        <v>1.284857085131493</v>
       </c>
       <c r="G9">
-        <v>-0.3624807080379967</v>
+        <v>0.08938053465369108</v>
       </c>
     </row>
     <row r="10">
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="C10">
-        <v>-0.3184560164551202</v>
+        <v>-0.7517887276083034</v>
       </c>
       <c r="D10">
-        <v>1.213030248454283</v>
+        <v>0.919503235497841</v>
       </c>
       <c r="E10">
-        <v>-0.6886633214222831</v>
+        <v>0.08970174053489077</v>
       </c>
       <c r="F10">
-        <v>-0.11882026334393</v>
+        <v>-0.1429814449533513</v>
       </c>
       <c r="G10">
-        <v>-0.1114102332239934</v>
+        <v>0.0544915088779469</v>
       </c>
     </row>
     <row r="11">
@@ -646,19 +646,19 @@
         </is>
       </c>
       <c r="C11">
-        <v>-3.79081475070141</v>
+        <v>-2.816074698359538</v>
       </c>
       <c r="D11">
-        <v>0.5140726239988528</v>
+        <v>-0.003090880287206499</v>
       </c>
       <c r="E11">
-        <v>0.2762433594916041</v>
+        <v>0.6670562567888787</v>
       </c>
       <c r="F11">
-        <v>-0.1080894128842705</v>
+        <v>-0.09880773744064668</v>
       </c>
       <c r="G11">
-        <v>0.06307089285482431</v>
+        <v>-0.09434933505130029</v>
       </c>
     </row>
     <row r="12">
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="C12">
-        <v>0.3679178822926698</v>
+        <v>0.4420481621236587</v>
       </c>
       <c r="D12">
-        <v>-0.255146314191386</v>
+        <v>-0.05278668746363599</v>
       </c>
       <c r="E12">
-        <v>0.04828765849698247</v>
+        <v>-0.3085787095013065</v>
       </c>
       <c r="F12">
-        <v>0.02010571708270762</v>
+        <v>0.03893663602594179</v>
       </c>
       <c r="G12">
-        <v>-0.2510264936611599</v>
+        <v>0.176177211278078</v>
       </c>
     </row>
     <row r="13">
@@ -700,19 +700,19 @@
         </is>
       </c>
       <c r="C13">
-        <v>0.4340360703602931</v>
+        <v>-0.719728652995319</v>
       </c>
       <c r="D13">
-        <v>1.645706868896196</v>
+        <v>1.010463836395759</v>
       </c>
       <c r="E13">
-        <v>-1.690118162305267</v>
+        <v>0.2979674603133923</v>
       </c>
       <c r="F13">
-        <v>0.08960378967366732</v>
+        <v>0.01996820216189975</v>
       </c>
       <c r="G13">
-        <v>-0.2443760041474999</v>
+        <v>0.127287515991992</v>
       </c>
     </row>
     <row r="14">
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="C14">
-        <v>-4.630291498340202</v>
+        <v>-2.448164083597422</v>
       </c>
       <c r="D14">
-        <v>-2.409716964122745</v>
+        <v>-2.533752332922437</v>
       </c>
       <c r="E14">
-        <v>0.09426072681526609</v>
+        <v>-0.5505917781927652</v>
       </c>
       <c r="F14">
-        <v>0.5102834077398803</v>
+        <v>0.5018541235200097</v>
       </c>
       <c r="G14">
-        <v>-0.015826052536025</v>
+        <v>0.03771862557027159</v>
       </c>
     </row>
     <row r="15">
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="C15">
-        <v>-2.743567255921219</v>
+        <v>-2.366223663349591</v>
       </c>
       <c r="D15">
-        <v>1.455318939878499</v>
+        <v>1.010965399440677</v>
       </c>
       <c r="E15">
-        <v>0.09728582114367423</v>
+        <v>0.6720882630417219</v>
       </c>
       <c r="F15">
-        <v>-0.04264775513969826</v>
+        <v>-0.002134191495940114</v>
       </c>
       <c r="G15">
-        <v>-0.3056558645134989</v>
+        <v>0.1566707702014022</v>
       </c>
     </row>
     <row r="16">
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="C16">
-        <v>-0.348786910809605</v>
+        <v>-0.6969970275921862</v>
       </c>
       <c r="D16">
-        <v>1.950532940292911</v>
+        <v>1.59507228028979</v>
       </c>
       <c r="E16">
-        <v>-0.8833733787453393</v>
+        <v>0.6136790248976071</v>
       </c>
       <c r="F16">
-        <v>-0.1527725983842808</v>
+        <v>-0.1639232451893539</v>
       </c>
       <c r="G16">
-        <v>-0.418700731882921</v>
+        <v>0.3540739444861541</v>
       </c>
     </row>
     <row r="17">
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C17">
-        <v>5.067592786731089</v>
+        <v>2.706526626168289</v>
       </c>
       <c r="D17">
-        <v>1.603577384334798</v>
+        <v>1.744933841865554</v>
       </c>
       <c r="E17">
-        <v>0.7107500644823297</v>
+        <v>0.763303051694423</v>
       </c>
       <c r="F17">
-        <v>0.06285159294837767</v>
+        <v>0.09234662178437168</v>
       </c>
       <c r="G17">
-        <v>0.3192723411561029</v>
+        <v>-0.2599232603414567</v>
       </c>
     </row>
     <row r="18">
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="C18">
-        <v>2.503806110884882</v>
+        <v>1.954505650224813</v>
       </c>
       <c r="D18">
-        <v>-2.570524015901837</v>
+        <v>-2.39594086984849</v>
       </c>
       <c r="E18">
-        <v>0.4143184338907623</v>
+        <v>0.003155065469334251</v>
       </c>
       <c r="F18">
-        <v>0.4243924344526546</v>
+        <v>0.4359983710422551</v>
       </c>
       <c r="G18">
-        <v>0.08843689434764149</v>
+        <v>-0.1681152832662953</v>
       </c>
     </row>
     <row r="19">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="C19">
-        <v>-1.32531181044226</v>
+        <v>-1.133840325196261</v>
       </c>
       <c r="D19">
-        <v>-0.2687492108872086</v>
+        <v>-0.6454444876716638</v>
       </c>
       <c r="E19">
-        <v>-0.3582847893900675</v>
+        <v>0.310926892526216</v>
       </c>
       <c r="F19">
-        <v>0.5607063615858958</v>
+        <v>0.546326799503141</v>
       </c>
       <c r="G19">
-        <v>-0.04555740951739358</v>
+        <v>-0.03182374948772878</v>
       </c>
     </row>
     <row r="20">
@@ -889,19 +889,19 @@
         </is>
       </c>
       <c r="C20">
-        <v>-0.7699977647349876</v>
+        <v>0.2439541386827118</v>
       </c>
       <c r="D20">
-        <v>-2.285946986308765</v>
+        <v>-2.411298196936192</v>
       </c>
       <c r="E20">
-        <v>-1.03793764816774</v>
+        <v>0.2862584582525418</v>
       </c>
       <c r="F20">
-        <v>-0.145146398303111</v>
+        <v>-0.1853886562556104</v>
       </c>
       <c r="G20">
-        <v>-0.1082106803318544</v>
+        <v>0.235600522771273</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="C21">
-        <v>0.01153472375901381</v>
+        <v>-0.6588373570057986</v>
       </c>
       <c r="D21">
-        <v>1.621752112202973</v>
+        <v>1.147794827886895</v>
       </c>
       <c r="E21">
-        <v>-0.4635095925622611</v>
+        <v>0.8148888905798231</v>
       </c>
       <c r="F21">
-        <v>0.01334590434074556</v>
+        <v>-0.02763609644586704</v>
       </c>
       <c r="G21">
-        <v>0.3590118670977351</v>
+        <v>-0.1971196585703887</v>
       </c>
     </row>
     <row r="22">
@@ -943,19 +943,19 @@
         </is>
       </c>
       <c r="C22">
-        <v>-1.583574552433413</v>
+        <v>-1.169372560492755</v>
       </c>
       <c r="D22">
-        <v>1.310142830064821</v>
+        <v>1.38132683058839</v>
       </c>
       <c r="E22">
-        <v>0.0957109768249676</v>
+        <v>-0.4684225128038061</v>
       </c>
       <c r="F22">
-        <v>-0.004583322934613547</v>
+        <v>0.01031079804598827</v>
       </c>
       <c r="G22">
-        <v>-0.1744815963097501</v>
+        <v>0.04876306405823146</v>
       </c>
     </row>
     <row r="23">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="C23">
-        <v>1.079422363943429</v>
+        <v>0.7788184953763202</v>
       </c>
       <c r="D23">
-        <v>1.336491887752844</v>
+        <v>1.49403115813216</v>
       </c>
       <c r="E23">
-        <v>-0.6060565724531178</v>
+        <v>-0.1959648403351637</v>
       </c>
       <c r="F23">
-        <v>0.152745391551543</v>
+        <v>0.1264580002599428</v>
       </c>
       <c r="G23">
-        <v>-0.08690961817296358</v>
+        <v>0.1478332025217961</v>
       </c>
     </row>
     <row r="24">
@@ -997,19 +997,19 @@
         </is>
       </c>
       <c r="C24">
-        <v>-3.606285350663208</v>
+        <v>-2.438255771770216</v>
       </c>
       <c r="D24">
-        <v>0.4479065518284513</v>
+        <v>0.306178298367945</v>
       </c>
       <c r="E24">
-        <v>0.8490734769880733</v>
+        <v>0.1136118840582188</v>
       </c>
       <c r="F24">
-        <v>-0.5533305094345911</v>
+        <v>-0.519060016375249</v>
       </c>
       <c r="G24">
-        <v>0.2245577330659577</v>
+        <v>-0.2088968733499101</v>
       </c>
     </row>
     <row r="25">
@@ -1024,19 +1024,19 @@
         </is>
       </c>
       <c r="C25">
-        <v>-1.283812806304568</v>
+        <v>-1.19741415019076</v>
       </c>
       <c r="D25">
-        <v>-0.3422819474004088</v>
+        <v>-0.7007634316737044</v>
       </c>
       <c r="E25">
-        <v>1.108835409874759</v>
+        <v>1.297204999663305</v>
       </c>
       <c r="F25">
-        <v>-0.4644151146386359</v>
+        <v>-0.3727891096533578</v>
       </c>
       <c r="G25">
-        <v>-0.06900921923066232</v>
+        <v>-0.1568145315603992</v>
       </c>
     </row>
     <row r="26">
@@ -1051,19 +1051,19 @@
         </is>
       </c>
       <c r="C26">
-        <v>-4.296945239307936</v>
+        <v>-2.816170168439347</v>
       </c>
       <c r="D26">
-        <v>0.5089113625963815</v>
+        <v>0.3746014752060685</v>
       </c>
       <c r="E26">
-        <v>0.3048725282272239</v>
+        <v>-0.3819431974105689</v>
       </c>
       <c r="F26">
-        <v>-0.3357082198243974</v>
+        <v>-0.3318985726891804</v>
       </c>
       <c r="G26">
-        <v>0.1367557688361954</v>
+        <v>-0.1918424547118242</v>
       </c>
     </row>
     <row r="27">
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="C27">
-        <v>-1.525389440043445</v>
+        <v>-1.604763454252469</v>
       </c>
       <c r="D27">
-        <v>1.464051523182875</v>
+        <v>1.150299316984166</v>
       </c>
       <c r="E27">
-        <v>-0.127539669136622</v>
+        <v>0.3738719193950855</v>
       </c>
       <c r="F27">
-        <v>-0.0218910229946513</v>
+        <v>0.02958769733209626</v>
       </c>
       <c r="G27">
-        <v>-0.6338251428208617</v>
+        <v>0.2668338496829629</v>
       </c>
     </row>
     <row r="28">
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="C28">
-        <v>2.238366182301786</v>
+        <v>2.280936711820211</v>
       </c>
       <c r="D28">
-        <v>-2.667273309851379</v>
+        <v>-2.526047958182551</v>
       </c>
       <c r="E28">
-        <v>-1.212116172298364</v>
+        <v>-0.07828553825921571</v>
       </c>
       <c r="F28">
-        <v>-0.5592698886492637</v>
+        <v>-0.6264721947011245</v>
       </c>
       <c r="G28">
-        <v>0.1846088419834459</v>
+        <v>-0.04317415052482479</v>
       </c>
     </row>
     <row r="29">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="C29">
-        <v>-1.298302244592772</v>
+        <v>-1.310863192426792</v>
       </c>
       <c r="D29">
-        <v>1.004323689895456</v>
+        <v>0.6161275532960625</v>
       </c>
       <c r="E29">
-        <v>-0.4701896741418767</v>
+        <v>0.316817410845421</v>
       </c>
       <c r="F29">
-        <v>-0.4051069136543081</v>
+        <v>-0.4338463154299063</v>
       </c>
       <c r="G29">
-        <v>0.09522280771403496</v>
+        <v>-0.142909654031498</v>
       </c>
     </row>
     <row r="30">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="C30">
-        <v>1.048286405261357</v>
+        <v>0.4635711841393251</v>
       </c>
       <c r="D30">
-        <v>0.9322126306481016</v>
+        <v>1.113751773233083</v>
       </c>
       <c r="E30">
-        <v>1.179506531728716</v>
+        <v>0.2755805284091946</v>
       </c>
       <c r="F30">
-        <v>-0.05449094994176908</v>
+        <v>0.009039440749233116</v>
       </c>
       <c r="G30">
-        <v>0.08021230320170733</v>
+        <v>-0.2019516766261939</v>
       </c>
     </row>
     <row r="31">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="C31">
-        <v>3.29963584679003</v>
+        <v>2.081001495349428</v>
       </c>
       <c r="D31">
-        <v>0.9655539959764041</v>
+        <v>1.166498940606996</v>
       </c>
       <c r="E31">
-        <v>-0.2269669205392321</v>
+        <v>0.1563839540362648</v>
       </c>
       <c r="F31">
-        <v>0.4072709770195002</v>
+        <v>0.4044951312099392</v>
       </c>
       <c r="G31">
-        <v>-0.09526411380367547</v>
+        <v>0.1303481118767193</v>
       </c>
     </row>
     <row r="32">
@@ -1213,19 +1213,19 @@
         </is>
       </c>
       <c r="C32">
-        <v>3.328642138707174</v>
+        <v>2.20949141053619</v>
       </c>
       <c r="D32">
-        <v>1.854835673276233</v>
+        <v>2.254626304070345</v>
       </c>
       <c r="E32">
-        <v>-0.7363365251419156</v>
+        <v>-0.6900635583289469</v>
       </c>
       <c r="F32">
-        <v>-0.3379843438731365</v>
+        <v>-0.4019606764783178</v>
       </c>
       <c r="G32">
-        <v>0.1651987264164803</v>
+        <v>-0.03989143667537205</v>
       </c>
     </row>
     <row r="33">
@@ -1240,19 +1240,19 @@
         </is>
       </c>
       <c r="C33">
-        <v>-5.260580361427103</v>
+        <v>-2.95111462526845</v>
       </c>
       <c r="D33">
-        <v>-2.007597296879885</v>
+        <v>-2.16029721098028</v>
       </c>
       <c r="E33">
-        <v>0.3564590324145352</v>
+        <v>-0.5894876897519079</v>
       </c>
       <c r="F33">
-        <v>1.37130353311339</v>
+        <v>1.362310153925946</v>
       </c>
       <c r="G33">
-        <v>0.1398295098733105</v>
+        <v>-0.09887814409766513</v>
       </c>
     </row>
     <row r="34">
@@ -1267,19 +1267,19 @@
         </is>
       </c>
       <c r="C34">
-        <v>-0.8767619981862214</v>
+        <v>-0.4594815019063576</v>
       </c>
       <c r="D34">
-        <v>-1.561500939356804</v>
+        <v>-1.798304127940896</v>
       </c>
       <c r="E34">
-        <v>-0.137162610285713</v>
+        <v>0.3462781248294727</v>
       </c>
       <c r="F34">
-        <v>-0.2774337086860742</v>
+        <v>-0.2890093412400216</v>
       </c>
       <c r="G34">
-        <v>0.1337806423481426</v>
+        <v>-0.06952444348053471</v>
       </c>
     </row>
     <row r="35">
@@ -1294,19 +1294,19 @@
         </is>
       </c>
       <c r="C35">
-        <v>4.9301782361575</v>
+        <v>3.27834822974753</v>
       </c>
       <c r="D35">
-        <v>1.126644237831639</v>
+        <v>1.740031836867948</v>
       </c>
       <c r="E35">
-        <v>0.2300501496662595</v>
+        <v>-0.2670664800890128</v>
       </c>
       <c r="F35">
-        <v>0.05934855006407198</v>
+        <v>0.1084401685819258</v>
       </c>
       <c r="G35">
-        <v>-0.4818153880852495</v>
+        <v>0.3708339872972807</v>
       </c>
     </row>
     <row r="36">
@@ -1321,19 +1321,19 @@
         </is>
       </c>
       <c r="C36">
-        <v>-3.909952107508406</v>
+        <v>-2.555599909096352</v>
       </c>
       <c r="D36">
-        <v>0.2426474309571867</v>
+        <v>0.09534406808075468</v>
       </c>
       <c r="E36">
-        <v>0.5579083320195394</v>
+        <v>-0.06866681218048365</v>
       </c>
       <c r="F36">
-        <v>0.09893832603618301</v>
+        <v>0.1267674298351988</v>
       </c>
       <c r="G36">
-        <v>-0.06836775398256537</v>
+        <v>0.1270936914637735</v>
       </c>
     </row>
     <row r="37">
@@ -1348,19 +1348,19 @@
         </is>
       </c>
       <c r="C37">
-        <v>-4.868938122894768</v>
+        <v>-2.83322385287683</v>
       </c>
       <c r="D37">
-        <v>-0.292990220107908</v>
+        <v>-0.3972441443389783</v>
       </c>
       <c r="E37">
-        <v>0.01775609540359957</v>
+        <v>-0.3970639615258336</v>
       </c>
       <c r="F37">
-        <v>1.058146454750383</v>
+        <v>1.074702538500204</v>
       </c>
       <c r="G37">
-        <v>-0.2975044755923594</v>
+        <v>0.2365458868909258</v>
       </c>
     </row>
     <row r="38">
@@ -1375,19 +1375,19 @@
         </is>
       </c>
       <c r="C38">
-        <v>3.780185935191321</v>
+        <v>2.9994041858856</v>
       </c>
       <c r="D38">
-        <v>-0.8571823500442156</v>
+        <v>0.2728177967611435</v>
       </c>
       <c r="E38">
-        <v>1.313484427655426</v>
+        <v>-1.945460969962853</v>
       </c>
       <c r="F38">
-        <v>-1.695563647386613</v>
+        <v>-1.663604265993972</v>
       </c>
       <c r="G38">
-        <v>0.1401925644537365</v>
+        <v>-0.1315069766451107</v>
       </c>
     </row>
     <row r="39">
@@ -1402,19 +1402,19 @@
         </is>
       </c>
       <c r="C39">
-        <v>1.323881494040585</v>
+        <v>1.30777563836203</v>
       </c>
       <c r="D39">
-        <v>0.7348309954470343</v>
+        <v>1.341899030497336</v>
       </c>
       <c r="E39">
-        <v>-0.02404664081324812</v>
+        <v>-1.383012167542606</v>
       </c>
       <c r="F39">
-        <v>0.1138002241599801</v>
+        <v>0.05877515548255657</v>
       </c>
       <c r="G39">
-        <v>0.3813513427867432</v>
+        <v>-0.2656846569019804</v>
       </c>
     </row>
     <row r="40">
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="C40">
-        <v>3.161685615957116</v>
+        <v>1.735510934769253</v>
       </c>
       <c r="D40">
-        <v>0.3081558927594622</v>
+        <v>0.3071721023463315</v>
       </c>
       <c r="E40">
-        <v>-0.01912843964130556</v>
+        <v>0.6419923850112996</v>
       </c>
       <c r="F40">
-        <v>-0.542644844841405</v>
+        <v>-0.4953370260038868</v>
       </c>
       <c r="G40">
-        <v>-0.4971674982643877</v>
+        <v>0.2568276691017291</v>
       </c>
     </row>
     <row r="41">
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C41">
-        <v>1.612784919772448</v>
+        <v>0.827486415513251</v>
       </c>
       <c r="D41">
-        <v>1.037046467415482</v>
+        <v>1.123774894862972</v>
       </c>
       <c r="E41">
-        <v>-0.1771819454098004</v>
+        <v>-0.1007226953256334</v>
       </c>
       <c r="F41">
-        <v>0.1027077686006621</v>
+        <v>0.0962618042252603</v>
       </c>
       <c r="G41">
-        <v>-0.04849473294423089</v>
+        <v>-0.002415271807903586</v>
       </c>
     </row>
     <row r="42">
@@ -1483,19 +1483,19 @@
         </is>
       </c>
       <c r="C42">
-        <v>2.489084630896462</v>
+        <v>1.922926373161737</v>
       </c>
       <c r="D42">
-        <v>-2.056344732397179</v>
+        <v>-1.768442630322928</v>
       </c>
       <c r="E42">
-        <v>0.4191359173231575</v>
+        <v>-0.2395625147352812</v>
       </c>
       <c r="F42">
-        <v>-0.1836270234317793</v>
+        <v>-0.1629303652681401</v>
       </c>
       <c r="G42">
-        <v>-0.07613584152032155</v>
+        <v>0.05672339632986626</v>
       </c>
     </row>
     <row r="43">
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="C43">
-        <v>-3.36877812105141</v>
+        <v>-2.396047543566431</v>
       </c>
       <c r="D43">
-        <v>-0.01865106303673671</v>
+        <v>-0.5469913575817961</v>
       </c>
       <c r="E43">
-        <v>-0.9323859590842735</v>
+        <v>0.1551111498172837</v>
       </c>
       <c r="F43">
-        <v>-0.8756926947290892</v>
+        <v>-0.9373470740438355</v>
       </c>
       <c r="G43">
-        <v>0.2170813301007147</v>
+        <v>-0.1060942931340973</v>
       </c>
     </row>
     <row r="44">
@@ -1537,19 +1537,19 @@
         </is>
       </c>
       <c r="C44">
-        <v>-0.2243569999550417</v>
+        <v>0.1976175807969054</v>
       </c>
       <c r="D44">
-        <v>-2.10624347023862</v>
+        <v>-2.03448476049363</v>
       </c>
       <c r="E44">
-        <v>0.1147627637099033</v>
+        <v>-0.156296086544685</v>
       </c>
       <c r="F44">
-        <v>-0.8516998567861886</v>
+        <v>-0.827205916094831</v>
       </c>
       <c r="G44">
-        <v>-0.2588445312482072</v>
+        <v>0.1562491808293493</v>
       </c>
     </row>
     <row r="45">
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="C45">
-        <v>4.749096909165893</v>
+        <v>2.903739579113998</v>
       </c>
       <c r="D45">
-        <v>1.059776736631397</v>
+        <v>1.52572996460832</v>
       </c>
       <c r="E45">
-        <v>1.030955663928607</v>
+        <v>0.1495205606079606</v>
       </c>
       <c r="F45">
-        <v>-0.6730287446641808</v>
+        <v>-0.6414155856166776</v>
       </c>
       <c r="G45">
-        <v>0.5029498984690522</v>
+        <v>-0.3508226535246008</v>
       </c>
     </row>
     <row r="46">
@@ -1591,19 +1591,19 @@
         </is>
       </c>
       <c r="C46">
-        <v>-5.312667725182518</v>
+        <v>-3.190476543692534</v>
       </c>
       <c r="D46">
-        <v>0.118425081745888</v>
+        <v>0.04107351169153742</v>
       </c>
       <c r="E46">
-        <v>0.2620661789993196</v>
+        <v>-0.6030899287053682</v>
       </c>
       <c r="F46">
-        <v>0.1151457180337687</v>
+        <v>0.1088929113565984</v>
       </c>
       <c r="G46">
-        <v>0.08044630927153018</v>
+        <v>-0.005337487504505875</v>
       </c>
     </row>
     <row r="47">
@@ -1618,19 +1618,19 @@
         </is>
       </c>
       <c r="C47">
-        <v>-1.678090260872938</v>
+        <v>-0.7129478507590424</v>
       </c>
       <c r="D47">
-        <v>-1.604206936684734</v>
+        <v>-1.821304897588436</v>
       </c>
       <c r="E47">
-        <v>-0.8133459678645283</v>
+        <v>-0.2630257228200817</v>
       </c>
       <c r="F47">
-        <v>1.328473895513315</v>
+        <v>1.241622209593683</v>
       </c>
       <c r="G47">
-        <v>0.4476616000845719</v>
+        <v>-0.2451313172291464</v>
       </c>
     </row>
     <row r="48">
@@ -1645,19 +1645,19 @@
         </is>
       </c>
       <c r="C48">
-        <v>4.578722506293989</v>
+        <v>3.926788945314459</v>
       </c>
       <c r="D48">
-        <v>-3.073875379849784</v>
+        <v>-2.851367570334796</v>
       </c>
       <c r="E48">
-        <v>-1.395464164855269</v>
+        <v>0.351061025935975</v>
       </c>
       <c r="F48">
-        <v>-0.6248844286048585</v>
+        <v>-0.6763707122906584</v>
       </c>
       <c r="G48">
-        <v>-0.01761461288863343</v>
+        <v>0.1144438994268681</v>
       </c>
     </row>
     <row r="49">
@@ -1672,19 +1672,19 @@
         </is>
       </c>
       <c r="C49">
-        <v>4.285219759648145</v>
+        <v>2.648005512536512</v>
       </c>
       <c r="D49">
-        <v>0.1931193153629344</v>
+        <v>0.4641784820049322</v>
       </c>
       <c r="E49">
-        <v>0.2369201270884403</v>
+        <v>0.01306892812614335</v>
       </c>
       <c r="F49">
-        <v>0.7824893699850441</v>
+        <v>0.7863259984752653</v>
       </c>
       <c r="G49">
-        <v>0.1263446393685351</v>
+        <v>-0.1328011205917168</v>
       </c>
     </row>
     <row r="50">
@@ -1699,19 +1699,19 @@
         </is>
       </c>
       <c r="C50">
-        <v>-1.889256094903108</v>
+        <v>-1.760390688584983</v>
       </c>
       <c r="D50">
-        <v>1.296209103994193</v>
+        <v>0.6959065947375164</v>
       </c>
       <c r="E50">
-        <v>-1.261398106218174</v>
+        <v>0.5792674205373501</v>
       </c>
       <c r="F50">
-        <v>-0.1443813602160742</v>
+        <v>-0.1884148875062159</v>
       </c>
       <c r="G50">
-        <v>-0.185466119674407</v>
+        <v>0.2186456310683823</v>
       </c>
     </row>
     <row r="51">
@@ -1726,19 +1726,19 @@
         </is>
       </c>
       <c r="C51">
-        <v>-0.671932081061094</v>
+        <v>-0.7081548791108389</v>
       </c>
       <c r="D51">
-        <v>0.3990928484260291</v>
+        <v>0.4428832616476817</v>
       </c>
       <c r="E51">
-        <v>1.613137682805309</v>
+        <v>0.5725377860074997</v>
       </c>
       <c r="F51">
-        <v>0.5325019939591253</v>
+        <v>0.6579344038821949</v>
       </c>
       <c r="G51">
-        <v>-0.4081246552675404</v>
+        <v>0.1405432090290592</v>
       </c>
     </row>
     <row r="52">
@@ -1753,19 +1753,19 @@
         </is>
       </c>
       <c r="C52">
-        <v>1.735655031512366</v>
+        <v>1.363529877667301</v>
       </c>
       <c r="D52">
-        <v>-2.281914249078842</v>
+        <v>-2.208619900650269</v>
       </c>
       <c r="E52">
-        <v>0.1391248380149121</v>
+        <v>0.1400399418375833</v>
       </c>
       <c r="F52">
-        <v>-0.3686937188461789</v>
+        <v>-0.3465412465896867</v>
       </c>
       <c r="G52">
-        <v>-0.09547869995176068</v>
+        <v>0.02154745598600805</v>
       </c>
     </row>
     <row r="53">
@@ -1780,19 +1780,19 @@
         </is>
       </c>
       <c r="C53">
-        <v>3.272541249207544</v>
+        <v>2.292416840755966</v>
       </c>
       <c r="D53">
-        <v>0.3417726174869289</v>
+        <v>0.7810923825668672</v>
       </c>
       <c r="E53">
-        <v>0.3495006764319986</v>
+        <v>-0.4758871610522114</v>
       </c>
       <c r="F53">
-        <v>0.6581962514291884</v>
+        <v>0.6455394760245757</v>
       </c>
       <c r="G53">
-        <v>0.1232131719599866</v>
+        <v>-0.1093751699311094</v>
       </c>
     </row>
     <row r="54">
@@ -1807,19 +1807,19 @@
         </is>
       </c>
       <c r="C54">
-        <v>-0.2049768714724096</v>
+        <v>0.1443052756080432</v>
       </c>
       <c r="D54">
-        <v>0.7130178014944983</v>
+        <v>1.075385690750195</v>
       </c>
       <c r="E54">
-        <v>0.1646154432143491</v>
+        <v>-0.7948803443783723</v>
       </c>
       <c r="F54">
-        <v>0.244438653018419</v>
+        <v>0.2487910812255754</v>
       </c>
       <c r="G54">
-        <v>-0.2618875713288286</v>
+        <v>0.1940377771849583</v>
       </c>
     </row>
     <row r="55">
@@ -1834,19 +1834,19 @@
         </is>
       </c>
       <c r="C55">
-        <v>0.1867536233745059</v>
+        <v>-0.008508982509760843</v>
       </c>
       <c r="D55">
-        <v>-1.621670333204347</v>
+        <v>-1.882830096399324</v>
       </c>
       <c r="E55">
-        <v>0.8072850232121443</v>
+        <v>0.9481674466638006</v>
       </c>
       <c r="F55">
-        <v>-0.1192412976011647</v>
+        <v>-0.07933876016272648</v>
       </c>
       <c r="G55">
-        <v>0.2396589428454484</v>
+        <v>-0.2632608939386458</v>
       </c>
     </row>
     <row r="56">
@@ -1861,19 +1861,19 @@
         </is>
       </c>
       <c r="C56">
-        <v>2.678433047825528</v>
+        <v>2.21437537560753</v>
       </c>
       <c r="D56">
-        <v>-1.789087874325987</v>
+        <v>-1.242429605989442</v>
       </c>
       <c r="E56">
-        <v>0.6874243135675103</v>
+        <v>-0.5665966590574996</v>
       </c>
       <c r="F56">
-        <v>-0.0224408577838206</v>
+        <v>0.03304864709083198</v>
       </c>
       <c r="G56">
-        <v>-0.2695190268328713</v>
+        <v>0.0262599162305184</v>
       </c>
     </row>
     <row r="57">
@@ -1888,19 +1888,19 @@
         </is>
       </c>
       <c r="C57">
-        <v>2.639479908689846</v>
+        <v>1.145802090875085</v>
       </c>
       <c r="D57">
-        <v>-0.2082246243730431</v>
+        <v>-0.3257682345496168</v>
       </c>
       <c r="E57">
-        <v>1.410272356093726</v>
+        <v>1.053974341526671</v>
       </c>
       <c r="F57">
-        <v>-0.1161968716378096</v>
+        <v>-0.05658848165684129</v>
       </c>
       <c r="G57">
-        <v>0.2769282447262629</v>
+        <v>-0.1901761297329304</v>
       </c>
     </row>
     <row r="58">
@@ -1915,19 +1915,19 @@
         </is>
       </c>
       <c r="C58">
-        <v>3.928018089805086</v>
+        <v>2.199882115916258</v>
       </c>
       <c r="D58">
-        <v>0.5933920374116536</v>
+        <v>0.7930268288066217</v>
       </c>
       <c r="E58">
-        <v>0.8970235502762693</v>
+        <v>0.5651552150937031</v>
       </c>
       <c r="F58">
-        <v>0.2300756956572528</v>
+        <v>0.2986489507824257</v>
       </c>
       <c r="G58">
-        <v>-0.1550820677697598</v>
+        <v>0.01667899460798721</v>
       </c>
     </row>
     <row r="59">
@@ -1942,19 +1942,19 @@
         </is>
       </c>
       <c r="C59">
-        <v>2.15586773361504</v>
+        <v>1.13126282429313</v>
       </c>
       <c r="D59">
-        <v>1.033213949597601</v>
+        <v>0.8030684749516006</v>
       </c>
       <c r="E59">
-        <v>-0.7370352741187898</v>
+        <v>0.9368135498529445</v>
       </c>
       <c r="F59">
-        <v>-0.2396354004380745</v>
+        <v>-0.2774228806750972</v>
       </c>
       <c r="G59">
-        <v>0.3602563635082026</v>
+        <v>-0.1088541716335317</v>
       </c>
     </row>
     <row r="60">
@@ -1969,19 +1969,19 @@
         </is>
       </c>
       <c r="C60">
-        <v>0.6085148502711339</v>
+        <v>1.809411086706564</v>
       </c>
       <c r="D60">
-        <v>-2.110271314935638</v>
+        <v>-2.017643566205205</v>
       </c>
       <c r="E60">
-        <v>-2.66379170823066</v>
+        <v>0.1166571752621642</v>
       </c>
       <c r="F60">
-        <v>-0.2969583457570505</v>
+        <v>-0.3888819456643019</v>
       </c>
       <c r="G60">
-        <v>-0.2351376654287084</v>
+        <v>0.306849344425015</v>
       </c>
     </row>
     <row r="61">
@@ -1996,19 +1996,19 @@
         </is>
       </c>
       <c r="C61">
-        <v>-1.971789503562345</v>
+        <v>-1.468253337150532</v>
       </c>
       <c r="D61">
-        <v>1.13181575859879</v>
+        <v>1.047531896898536</v>
       </c>
       <c r="E61">
-        <v>0.1910257357272593</v>
+        <v>-0.1174873692004088</v>
       </c>
       <c r="F61">
-        <v>-0.2206775119780355</v>
+        <v>-0.2215757633698951</v>
       </c>
       <c r="G61">
-        <v>0.1354245039222522</v>
+        <v>-0.1262193629361317</v>
       </c>
     </row>
     <row r="62">
@@ -2023,19 +2023,19 @@
         </is>
       </c>
       <c r="C62">
-        <v>2.978008630934211</v>
+        <v>2.202925493300226</v>
       </c>
       <c r="D62">
-        <v>1.281469248825258</v>
+        <v>1.608672263124453</v>
       </c>
       <c r="E62">
-        <v>-1.441677558800121</v>
+        <v>-0.6201156192113326</v>
       </c>
       <c r="F62">
-        <v>0.2945422902924693</v>
+        <v>0.2257511411508985</v>
       </c>
       <c r="G62">
-        <v>-0.203932988482873</v>
+        <v>0.2760534665148936</v>
       </c>
     </row>
     <row r="63">
@@ -2050,19 +2050,19 @@
         </is>
       </c>
       <c r="C63">
-        <v>4.32648038302059</v>
+        <v>2.202842379388367</v>
       </c>
       <c r="D63">
-        <v>1.080719614141803</v>
+        <v>0.8876171964688915</v>
       </c>
       <c r="E63">
-        <v>-0.1087510623745578</v>
+        <v>1.344948426046934</v>
       </c>
       <c r="F63">
-        <v>0.2447550923567446</v>
+        <v>0.2751986501962092</v>
       </c>
       <c r="G63">
-        <v>-0.1697239586436769</v>
+        <v>0.1658703626138485</v>
       </c>
     </row>
     <row r="64">
@@ -2077,19 +2077,19 @@
         </is>
       </c>
       <c r="C64">
-        <v>1.838883116521038</v>
+        <v>1.759209575634501</v>
       </c>
       <c r="D64">
-        <v>-3.046351049597303</v>
+        <v>-2.845187308611023</v>
       </c>
       <c r="E64">
-        <v>0.05241220466064667</v>
+        <v>-0.3107356506646884</v>
       </c>
       <c r="F64">
-        <v>-0.5093971560265975</v>
+        <v>-0.5422636470894634</v>
       </c>
       <c r="G64">
-        <v>0.3816328403939651</v>
+        <v>-0.2170169044746975</v>
       </c>
     </row>
     <row r="65">
@@ -2104,19 +2104,19 @@
         </is>
       </c>
       <c r="C65">
-        <v>2.08880936196809</v>
+        <v>1.595262718814727</v>
       </c>
       <c r="D65">
-        <v>-2.042287616157224</v>
+        <v>-1.935197961946008</v>
       </c>
       <c r="E65">
-        <v>0.1469022811211898</v>
+        <v>0.1413899944144496</v>
       </c>
       <c r="F65">
-        <v>-0.1755780701912577</v>
+        <v>-0.1554323374534092</v>
       </c>
       <c r="G65">
-        <v>-0.1809607054717637</v>
+        <v>0.1670316893798421</v>
       </c>
     </row>
     <row r="66">
@@ -2131,19 +2131,19 @@
         </is>
       </c>
       <c r="C66">
-        <v>-1.04697830508539</v>
+        <v>-0.7292875711071578</v>
       </c>
       <c r="D66">
-        <v>-0.06927575354823587</v>
+        <v>-0.2077548646391924</v>
       </c>
       <c r="E66">
-        <v>0.5640966451423571</v>
+        <v>0.1626980001314655</v>
       </c>
       <c r="F66">
-        <v>0.4958434651606332</v>
+        <v>0.4669510679911414</v>
       </c>
       <c r="G66">
-        <v>0.3272279140742093</v>
+        <v>0.07191530282060071</v>
       </c>
     </row>
     <row r="67">
@@ -2158,19 +2158,19 @@
         </is>
       </c>
       <c r="C67">
-        <v>-0.4055477603826896</v>
+        <v>0.04356307965473912</v>
       </c>
       <c r="D67">
-        <v>-0.8111304380514203</v>
+        <v>-0.6691106990402781</v>
       </c>
       <c r="E67">
-        <v>-0.0659800297932322</v>
+        <v>-0.3784672937987154</v>
       </c>
       <c r="F67">
-        <v>-0.1171552334109793</v>
+        <v>-0.1147696177676812</v>
       </c>
       <c r="G67">
-        <v>-0.1014952098483496</v>
+        <v>0.07348601038419326</v>
       </c>
     </row>
     <row r="68">
@@ -2185,19 +2185,19 @@
         </is>
       </c>
       <c r="C68">
-        <v>2.306439816136892</v>
+        <v>1.08724854641561</v>
       </c>
       <c r="D68">
-        <v>0.5513497510767748</v>
+        <v>0.5461601356566703</v>
       </c>
       <c r="E68">
-        <v>0.4483523737329105</v>
+        <v>0.6247547780878249</v>
       </c>
       <c r="F68">
-        <v>-0.3512150138981199</v>
+        <v>-0.2933381070308989</v>
       </c>
       <c r="G68">
-        <v>-0.2073833112373152</v>
+        <v>0.03779721255926703</v>
       </c>
     </row>
     <row r="69">
@@ -2212,19 +2212,19 @@
         </is>
       </c>
       <c r="C69">
-        <v>0.7309617150881323</v>
+        <v>0.6144391139813635</v>
       </c>
       <c r="D69">
-        <v>0.2046157523991985</v>
+        <v>0.3782082479440951</v>
       </c>
       <c r="E69">
-        <v>-0.3224162907750989</v>
+        <v>-0.5738973291858682</v>
       </c>
       <c r="F69">
-        <v>-0.1581554044249461</v>
+        <v>-0.2043918831644752</v>
       </c>
       <c r="G69">
-        <v>0.2378530980856661</v>
+        <v>-0.181054265499349</v>
       </c>
     </row>
     <row r="70">
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="C70">
-        <v>-0.2153542463875022</v>
+        <v>0.3453559457380456</v>
       </c>
       <c r="D70">
-        <v>-2.440524589843993</v>
+        <v>-2.22858012340127</v>
       </c>
       <c r="E70">
-        <v>0.3477695069055237</v>
+        <v>-0.5276822957328621</v>
       </c>
       <c r="F70">
-        <v>-0.07252153055052704</v>
+        <v>-0.05298305873714337</v>
       </c>
       <c r="G70">
-        <v>-0.1386750227241091</v>
+        <v>0.05958518891851777</v>
       </c>
     </row>
     <row r="71">
@@ -2266,19 +2266,19 @@
         </is>
       </c>
       <c r="C71">
-        <v>4.072193914804724</v>
+        <v>2.688237180906775</v>
       </c>
       <c r="D71">
-        <v>1.490838026491346</v>
+        <v>2.125187242214348</v>
       </c>
       <c r="E71">
-        <v>0.2399832462179232</v>
+        <v>-0.9255074778411998</v>
       </c>
       <c r="F71">
-        <v>0.1441799051439584</v>
+        <v>0.1174027813020833</v>
       </c>
       <c r="G71">
-        <v>0.381125143289787</v>
+        <v>-0.2999435860954894</v>
       </c>
     </row>
     <row r="72">
@@ -2293,19 +2293,19 @@
         </is>
       </c>
       <c r="C72">
-        <v>-7.308993242058841</v>
+        <v>-5.227532921612816</v>
       </c>
       <c r="D72">
-        <v>0.3326700197255424</v>
+        <v>-0.5471902821591643</v>
       </c>
       <c r="E72">
-        <v>-0.4465632819506321</v>
+        <v>0.5773928344982386</v>
       </c>
       <c r="F72">
-        <v>-0.01187011434015369</v>
+        <v>-0.01775999974000012</v>
       </c>
       <c r="G72">
-        <v>-0.09068772675652183</v>
+        <v>0.1409576522975354</v>
       </c>
     </row>
     <row r="73">
@@ -2320,19 +2320,19 @@
         </is>
       </c>
       <c r="C73">
-        <v>-5.355161607867724</v>
+        <v>-3.446971864774098</v>
       </c>
       <c r="D73">
-        <v>0.3307754588608462</v>
+        <v>0.1071821900418558</v>
       </c>
       <c r="E73">
-        <v>0.1550595678727887</v>
+        <v>-0.3747465053142328</v>
       </c>
       <c r="F73">
-        <v>-0.0698949940086151</v>
+        <v>-0.06663490647596096</v>
       </c>
       <c r="G73">
-        <v>-0.03075559947683573</v>
+        <v>-0.05953707240452505</v>
       </c>
     </row>
     <row r="74">
@@ -2347,19 +2347,19 @@
         </is>
       </c>
       <c r="C74">
-        <v>1.060001391955627</v>
+        <v>-0.03527131789163493</v>
       </c>
       <c r="D74">
-        <v>1.605397258288108</v>
+        <v>1.279619271679357</v>
       </c>
       <c r="E74">
-        <v>-0.2834849557121878</v>
+        <v>0.8688799389734392</v>
       </c>
       <c r="F74">
-        <v>-0.102197170144171</v>
+        <v>-0.06483510577867097</v>
       </c>
       <c r="G74">
-        <v>-0.4816696525619676</v>
+        <v>0.2721232495994222</v>
       </c>
     </row>
     <row r="75">
@@ -2374,19 +2374,19 @@
         </is>
       </c>
       <c r="C75">
-        <v>-4.311929953987276</v>
+        <v>-2.937297814258928</v>
       </c>
       <c r="D75">
-        <v>0.3776583803883596</v>
+        <v>0.1298203070172723</v>
       </c>
       <c r="E75">
-        <v>0.3009198243566069</v>
+        <v>0.0008291385178073041</v>
       </c>
       <c r="F75">
-        <v>-0.5236367678403483</v>
+        <v>-0.4879679419176874</v>
       </c>
       <c r="G75">
-        <v>-0.1868454507832477</v>
+        <v>0.009972493835075784</v>
       </c>
     </row>
     <row r="76">
@@ -2401,19 +2401,19 @@
         </is>
       </c>
       <c r="C76">
-        <v>-4.558419823388312</v>
+        <v>-3.052506720634756</v>
       </c>
       <c r="D76">
-        <v>0.809807100128878</v>
+        <v>0.5443465657415898</v>
       </c>
       <c r="E76">
-        <v>0.3446253029196813</v>
+        <v>-0.01452368116795111</v>
       </c>
       <c r="F76">
-        <v>-0.4525359706367912</v>
+        <v>-0.4694637037023855</v>
       </c>
       <c r="G76">
-        <v>0.4677691523087531</v>
+        <v>-0.26170763988898</v>
       </c>
     </row>
     <row r="77">
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="C77">
-        <v>3.153846673028681</v>
+        <v>1.108501687481541</v>
       </c>
       <c r="D77">
-        <v>0.8311316493977849</v>
+        <v>0.3770890886399601</v>
       </c>
       <c r="E77">
-        <v>0.2536030106886949</v>
+        <v>1.418899150667578</v>
       </c>
       <c r="F77">
-        <v>0.4929983038612844</v>
+        <v>0.4841212422155218</v>
       </c>
       <c r="G77">
-        <v>0.5392372067964116</v>
+        <v>-0.1513394496109454</v>
       </c>
     </row>
     <row r="78">
@@ -2455,19 +2455,19 @@
         </is>
       </c>
       <c r="C78">
-        <v>1.818706471440115</v>
+        <v>1.242775121577969</v>
       </c>
       <c r="D78">
-        <v>-0.2668661910807256</v>
+        <v>0.1950714531278918</v>
       </c>
       <c r="E78">
-        <v>1.423545719848318</v>
+        <v>-0.310765676987514</v>
       </c>
       <c r="F78">
-        <v>-0.1142604356294298</v>
+        <v>-0.03553902757623593</v>
       </c>
       <c r="G78">
-        <v>-0.1225289449298935</v>
+        <v>-0.01909347709499865</v>
       </c>
     </row>
     <row r="79">
@@ -2482,19 +2482,19 @@
         </is>
       </c>
       <c r="C79">
-        <v>-1.190164051065726</v>
+        <v>-1.416550687829511</v>
       </c>
       <c r="D79">
-        <v>0.7830051630621293</v>
+        <v>0.3385961964274331</v>
       </c>
       <c r="E79">
-        <v>0.7911386445257169</v>
+        <v>1.270638965798116</v>
       </c>
       <c r="F79">
-        <v>0.2751031702932099</v>
+        <v>0.3509097561064929</v>
       </c>
       <c r="G79">
-        <v>-0.1563926872584024</v>
+        <v>0.01595144111893106</v>
       </c>
     </row>
     <row r="80">
@@ -2509,19 +2509,19 @@
         </is>
       </c>
       <c r="C80">
-        <v>1.551804923159225</v>
+        <v>0.7624558082034327</v>
       </c>
       <c r="D80">
-        <v>1.537363933595356</v>
+        <v>1.470713276902939</v>
       </c>
       <c r="E80">
-        <v>-0.6337471239962307</v>
+        <v>0.2616757961947982</v>
       </c>
       <c r="F80">
-        <v>0.5138738718983272</v>
+        <v>0.4809520470140139</v>
       </c>
       <c r="G80">
-        <v>0.03911411818680938</v>
+        <v>0.049995817835377</v>
       </c>
     </row>
     <row r="81">
@@ -2536,19 +2536,19 @@
         </is>
       </c>
       <c r="C81">
-        <v>-0.8689826255873978</v>
+        <v>-0.0812147330627592</v>
       </c>
       <c r="D81">
-        <v>-0.6352200919500018</v>
+        <v>-0.3357036029187511</v>
       </c>
       <c r="E81">
-        <v>0.1998068791658819</v>
+        <v>-0.7557560341849772</v>
       </c>
       <c r="F81">
-        <v>-0.4816972216677719</v>
+        <v>-0.499436975447984</v>
       </c>
       <c r="G81">
-        <v>0.1745329721682914</v>
+        <v>-0.01451328569206958</v>
       </c>
     </row>
     <row r="82">
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="C82">
-        <v>0.4954525766243004</v>
+        <v>0.1375175205617371</v>
       </c>
       <c r="D82">
-        <v>0.8829499359035641</v>
+        <v>0.8938989174241313</v>
       </c>
       <c r="E82">
-        <v>-0.3907573205940975</v>
+        <v>-0.2902010091470309</v>
       </c>
       <c r="F82">
-        <v>0.5558633216349734</v>
+        <v>0.5231245220012147</v>
       </c>
       <c r="G82">
-        <v>0.1311395696355294</v>
+        <v>-0.01799411548352827</v>
       </c>
     </row>
     <row r="83">
@@ -2590,19 +2590,19 @@
         </is>
       </c>
       <c r="C83">
-        <v>-2.428530507622121</v>
+        <v>-1.387751362197188</v>
       </c>
       <c r="D83">
-        <v>-0.7102299739853378</v>
+        <v>-0.7134665702219555</v>
       </c>
       <c r="E83">
-        <v>-0.1387904827382161</v>
+        <v>-0.736049590353747</v>
       </c>
       <c r="F83">
-        <v>0.644423915033562</v>
+        <v>0.6247192754445139</v>
       </c>
       <c r="G83">
-        <v>-0.005397615985507927</v>
+        <v>-0.06280651749336262</v>
       </c>
     </row>
     <row r="84">
@@ -2617,19 +2617,19 @@
         </is>
       </c>
       <c r="C84">
-        <v>-4.207632480797313</v>
+        <v>-2.383875601153178</v>
       </c>
       <c r="D84">
-        <v>-0.5974591053347649</v>
+        <v>-0.5224938374408571</v>
       </c>
       <c r="E84">
-        <v>0.3977391992982628</v>
+        <v>-0.7341601495210128</v>
       </c>
       <c r="F84">
-        <v>-0.281472502620793</v>
+        <v>-0.2610588568449501</v>
       </c>
       <c r="G84">
-        <v>-0.08739258855907092</v>
+        <v>0.01167181307679237</v>
       </c>
     </row>
     <row r="85">
@@ -2644,19 +2644,19 @@
         </is>
       </c>
       <c r="C85">
-        <v>3.296883377125915</v>
+        <v>2.377786510668908</v>
       </c>
       <c r="D85">
-        <v>-3.108595269361776</v>
+        <v>-3.220759171631432</v>
       </c>
       <c r="E85">
-        <v>-0.5193836299236252</v>
+        <v>0.5261959735818638</v>
       </c>
       <c r="F85">
-        <v>0.4607664599613461</v>
+        <v>0.4422573321711865</v>
       </c>
       <c r="G85">
-        <v>-0.01529233279741361</v>
+        <v>-0.002761465039437614</v>
       </c>
     </row>
     <row r="86">
@@ -2671,19 +2671,19 @@
         </is>
       </c>
       <c r="C86">
-        <v>2.22334324283981</v>
+        <v>1.422178612744733</v>
       </c>
       <c r="D86">
-        <v>-1.782623295901296</v>
+        <v>-1.955612062925864</v>
       </c>
       <c r="E86">
-        <v>-0.1516670036381824</v>
+        <v>0.7798006318391821</v>
       </c>
       <c r="F86">
-        <v>-0.1133296912392161</v>
+        <v>-0.09801048215780624</v>
       </c>
       <c r="G86">
-        <v>-0.1153699047285815</v>
+        <v>0.08247765960815193</v>
       </c>
     </row>
     <row r="87">
@@ -2698,19 +2698,19 @@
         </is>
       </c>
       <c r="C87">
-        <v>-1.442974070941331</v>
+        <v>-1.587586146498063</v>
       </c>
       <c r="D87">
-        <v>1.094995754201249</v>
+        <v>0.529108731029116</v>
       </c>
       <c r="E87">
-        <v>-0.304583748142877</v>
+        <v>0.9385879067366193</v>
       </c>
       <c r="F87">
-        <v>-0.2992978452694083</v>
+        <v>-0.299936951989778</v>
       </c>
       <c r="G87">
-        <v>-0.003694024901573587</v>
+        <v>0.008001402621872617</v>
       </c>
     </row>
     <row r="88">
@@ -2725,19 +2725,19 @@
         </is>
       </c>
       <c r="C88">
-        <v>2.213967839919763</v>
+        <v>2.298660002864017</v>
       </c>
       <c r="D88">
-        <v>-3.642399531573024</v>
+        <v>-3.65017534635435</v>
       </c>
       <c r="E88">
-        <v>-1.308791610133679</v>
+        <v>0.311493383302043</v>
       </c>
       <c r="F88">
-        <v>-0.01048631135782158</v>
+        <v>-0.05768556013755081</v>
       </c>
       <c r="G88">
-        <v>-0.05447648783820687</v>
+        <v>0.07681335261915993</v>
       </c>
     </row>
     <row r="89">
@@ -2752,19 +2752,19 @@
         </is>
       </c>
       <c r="C89">
-        <v>0.9630525796409497</v>
+        <v>0.2426018985200276</v>
       </c>
       <c r="D89">
-        <v>1.432823971155344</v>
+        <v>1.156580996106513</v>
       </c>
       <c r="E89">
-        <v>-1.356860991241302</v>
+        <v>0.03966529121407797</v>
       </c>
       <c r="F89">
-        <v>0.2741255431355875</v>
+        <v>0.1734360573223446</v>
       </c>
       <c r="G89">
-        <v>0.3468311643223657</v>
+        <v>-0.08098069371162318</v>
       </c>
     </row>
     <row r="90">
@@ -2779,19 +2779,19 @@
         </is>
       </c>
       <c r="C90">
-        <v>-1.976299755429063</v>
+        <v>-1.363807047560512</v>
       </c>
       <c r="D90">
-        <v>0.4490814711763208</v>
+        <v>0.2978442325920183</v>
       </c>
       <c r="E90">
-        <v>-0.06965672265047512</v>
+        <v>-0.08760228620364774</v>
       </c>
       <c r="F90">
-        <v>0.1591027525677193</v>
+        <v>0.1506417934398214</v>
       </c>
       <c r="G90">
-        <v>-0.05412161020777715</v>
+        <v>-0.04529608939880819</v>
       </c>
     </row>
     <row r="91">
@@ -2806,19 +2806,19 @@
         </is>
       </c>
       <c r="C91">
-        <v>0.6724232724195438</v>
+        <v>-0.01395245744377593</v>
       </c>
       <c r="D91">
-        <v>1.637328687035739</v>
+        <v>1.470055994683394</v>
       </c>
       <c r="E91">
-        <v>-0.04056045650981394</v>
+        <v>0.5633858812986579</v>
       </c>
       <c r="F91">
-        <v>-0.3692763486917419</v>
+        <v>-0.3691143242832799</v>
       </c>
       <c r="G91">
-        <v>0.1066181636633164</v>
+        <v>-0.03501470545789274</v>
       </c>
     </row>
     <row r="92">
@@ -2833,19 +2833,19 @@
         </is>
       </c>
       <c r="C92">
-        <v>0.2279892820746969</v>
+        <v>0.5929447250739524</v>
       </c>
       <c r="D92">
-        <v>-0.1263050455658993</v>
+        <v>0.1698482499294495</v>
       </c>
       <c r="E92">
-        <v>-0.4722899386719293</v>
+        <v>-1.092362562764272</v>
       </c>
       <c r="F92">
-        <v>1.152044647566105</v>
+        <v>1.065872056706864</v>
       </c>
       <c r="G92">
-        <v>0.4921678276151725</v>
+        <v>-0.2927801705763346</v>
       </c>
     </row>
     <row r="93">
@@ -2860,19 +2860,19 @@
         </is>
       </c>
       <c r="C93">
-        <v>0.620708481242811</v>
+        <v>0.3323094948120652</v>
       </c>
       <c r="D93">
-        <v>-0.4288088864632287</v>
+        <v>-0.3616990807514001</v>
       </c>
       <c r="E93">
-        <v>0.9125843708668775</v>
+        <v>0.2664056317546476</v>
       </c>
       <c r="F93">
-        <v>0.2021762112413695</v>
+        <v>0.2469755735639602</v>
       </c>
       <c r="G93">
-        <v>0.1070764116781595</v>
+        <v>-0.1453917515340379</v>
       </c>
     </row>
     <row r="94">
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="C94">
-        <v>-3.209464098499541</v>
+        <v>-1.721706286654919</v>
       </c>
       <c r="D94">
-        <v>-0.09301745161129395</v>
+        <v>-0.447882040745247</v>
       </c>
       <c r="E94">
-        <v>-1.140506235897025</v>
+        <v>-0.005069204250680803</v>
       </c>
       <c r="F94">
-        <v>0.213179153481722</v>
+        <v>0.09253860263297561</v>
       </c>
       <c r="G94">
-        <v>0.6117962984542566</v>
+        <v>-0.2055344396990527</v>
       </c>
     </row>
     <row r="95">
@@ -2914,19 +2914,19 @@
         </is>
       </c>
       <c r="C95">
-        <v>-4.450275941957836</v>
+        <v>-3.295169397248583</v>
       </c>
       <c r="D95">
-        <v>0.8517607808846663</v>
+        <v>0.3980234258526965</v>
       </c>
       <c r="E95">
-        <v>0.2330864534390628</v>
+        <v>0.4947339978116505</v>
       </c>
       <c r="F95">
-        <v>-0.1805236880493726</v>
+        <v>-0.1324604739013725</v>
       </c>
       <c r="G95">
-        <v>-0.3118989332281555</v>
+        <v>0.1763492597597761</v>
       </c>
     </row>
     <row r="96">
@@ -2941,19 +2941,19 @@
         </is>
       </c>
       <c r="C96">
-        <v>-1.576318050430517</v>
+        <v>-0.4157037204060638</v>
       </c>
       <c r="D96">
-        <v>-0.5361239140658709</v>
+        <v>-0.008266264980580251</v>
       </c>
       <c r="E96">
-        <v>0.4254166430755632</v>
+        <v>-1.407701408655081</v>
       </c>
       <c r="F96">
-        <v>0.6444037637408181</v>
+        <v>0.6711075325041121</v>
       </c>
       <c r="G96">
-        <v>-0.4518128480900706</v>
+        <v>0.2610289652498488</v>
       </c>
     </row>
     <row r="97">
@@ -2968,19 +2968,19 @@
         </is>
       </c>
       <c r="C97">
-        <v>-0.9898303680291427</v>
+        <v>-0.3832915375497994</v>
       </c>
       <c r="D97">
-        <v>-1.616743819932616</v>
+        <v>-1.479599576437648</v>
       </c>
       <c r="E97">
-        <v>0.7598421249557662</v>
+        <v>-0.2784793457877385</v>
       </c>
       <c r="F97">
-        <v>0.1265621008949634</v>
+        <v>0.1808558717697856</v>
       </c>
       <c r="G97">
-        <v>-0.3077427012292235</v>
+        <v>0.1242700169201102</v>
       </c>
     </row>
     <row r="98">
@@ -2995,19 +2995,19 @@
         </is>
       </c>
       <c r="C98">
-        <v>-3.164424025945969</v>
+        <v>-2.125115052958473</v>
       </c>
       <c r="D98">
-        <v>0.6709544364261059</v>
+        <v>0.6224720586817922</v>
       </c>
       <c r="E98">
-        <v>0.7555157926978084</v>
+        <v>-0.07672864120976408</v>
       </c>
       <c r="F98">
-        <v>-0.6581510736417275</v>
+        <v>-0.6261707341440231</v>
       </c>
       <c r="G98">
-        <v>0.1421992464148102</v>
+        <v>-0.1406533659755011</v>
       </c>
     </row>
     <row r="99">
@@ -3022,19 +3022,19 @@
         </is>
       </c>
       <c r="C99">
-        <v>1.669298359858971</v>
+        <v>1.009305175056198</v>
       </c>
       <c r="D99">
-        <v>0.8932690590817612</v>
+        <v>1.276115534187383</v>
       </c>
       <c r="E99">
-        <v>0.8090183454505828</v>
+        <v>-0.2025233296237564</v>
       </c>
       <c r="F99">
-        <v>-0.03069507886103217</v>
+        <v>0.0512696830886087</v>
       </c>
       <c r="G99">
-        <v>-0.552899143709384</v>
+        <v>0.2703774252599733</v>
       </c>
     </row>
     <row r="100">
@@ -3049,19 +3049,19 @@
         </is>
       </c>
       <c r="C100">
-        <v>0.6804188423062473</v>
+        <v>0.1367163615411768</v>
       </c>
       <c r="D100">
-        <v>1.266134330467868</v>
+        <v>1.3238343799334</v>
       </c>
       <c r="E100">
-        <v>0.4900547800133173</v>
+        <v>0.1572231219028959</v>
       </c>
       <c r="F100">
-        <v>0.1496486327960032</v>
+        <v>0.1814963926863884</v>
       </c>
       <c r="G100">
-        <v>-0.01802461150397953</v>
+        <v>-0.06529777993933691</v>
       </c>
     </row>
     <row r="101">
@@ -3076,19 +3076,19 @@
         </is>
       </c>
       <c r="C101">
-        <v>1.329536367937856</v>
+        <v>1.004868971741891</v>
       </c>
       <c r="D101">
-        <v>-1.564696399731356</v>
+        <v>-1.488225390892863</v>
       </c>
       <c r="E101">
-        <v>0.5083538030644446</v>
+        <v>0.1267352828913347</v>
       </c>
       <c r="F101">
-        <v>0.7193976667372155</v>
+        <v>0.7407415155937074</v>
       </c>
       <c r="G101">
-        <v>0.08876463325452195</v>
+        <v>-0.1816675164894583</v>
       </c>
     </row>
     <row r="102">
@@ -3103,19 +3103,19 @@
         </is>
       </c>
       <c r="C102">
-        <v>4.198989527674144</v>
+        <v>2.764313017376976</v>
       </c>
       <c r="D102">
-        <v>0.6871587100076577</v>
+        <v>1.363948432184383</v>
       </c>
       <c r="E102">
-        <v>1.150966165223366</v>
+        <v>-0.4257967514197358</v>
       </c>
       <c r="F102">
-        <v>0.1332713475713795</v>
+        <v>0.204368389669211</v>
       </c>
       <c r="G102">
-        <v>-0.1482709585601468</v>
+        <v>-0.01400761913076093</v>
       </c>
     </row>
     <row r="103">
@@ -3130,19 +3130,19 @@
         </is>
       </c>
       <c r="C103">
-        <v>-1.654019461536865</v>
+        <v>-0.5087714140610166</v>
       </c>
       <c r="D103">
-        <v>-1.766791188538298</v>
+        <v>-1.594481448034846</v>
       </c>
       <c r="E103">
-        <v>0.05633485469454008</v>
+        <v>-0.7895132503065229</v>
       </c>
       <c r="F103">
-        <v>-0.03717375342405887</v>
+        <v>-0.05812960522941107</v>
       </c>
       <c r="G103">
-        <v>0.07397934576581847</v>
+        <v>-0.07006020856004137</v>
       </c>
     </row>
     <row r="104">
@@ -3157,19 +3157,19 @@
         </is>
       </c>
       <c r="C104">
-        <v>3.037383595014793</v>
+        <v>1.379598761762736</v>
       </c>
       <c r="D104">
-        <v>0.01389639146740087</v>
+        <v>-0.2935400518017238</v>
       </c>
       <c r="E104">
-        <v>0.1275561831332956</v>
+        <v>1.123177686298596</v>
       </c>
       <c r="F104">
-        <v>0.2554339809205058</v>
+        <v>0.2686921031360277</v>
       </c>
       <c r="G104">
-        <v>0.1298215758055996</v>
+        <v>-0.2355295591782887</v>
       </c>
     </row>
     <row r="105">
@@ -3184,19 +3184,19 @@
         </is>
       </c>
       <c r="C105">
-        <v>-1.070036543989074</v>
+        <v>-0.2165011323841212</v>
       </c>
       <c r="D105">
-        <v>-0.5430870642115881</v>
+        <v>-0.3132693576233153</v>
       </c>
       <c r="E105">
-        <v>-0.2699654829430274</v>
+        <v>-0.6292010679917693</v>
       </c>
       <c r="F105">
-        <v>-0.6567802168124111</v>
+        <v>-0.6592695267029259</v>
       </c>
       <c r="G105">
-        <v>-0.2390297608061914</v>
+        <v>0.221749392959666</v>
       </c>
     </row>
     <row r="106">
@@ -3211,19 +3211,19 @@
         </is>
       </c>
       <c r="C106">
-        <v>-4.822470806990063</v>
+        <v>-2.155117117570998</v>
       </c>
       <c r="D106">
-        <v>-1.227471940152559</v>
+        <v>-1.059200427339337</v>
       </c>
       <c r="E106">
-        <v>-0.6282183177806362</v>
+        <v>-1.290988626194469</v>
       </c>
       <c r="F106">
-        <v>0.9195846083635255</v>
+        <v>0.8634370148858768</v>
       </c>
       <c r="G106">
-        <v>-0.08043600581986139</v>
+        <v>0.1765802823489862</v>
       </c>
     </row>
     <row r="107">
@@ -3238,19 +3238,19 @@
         </is>
       </c>
       <c r="C107">
-        <v>0.5852032906460596</v>
+        <v>0.5581011579811478</v>
       </c>
       <c r="D107">
-        <v>1.274065357701715</v>
+        <v>1.503763092568728</v>
       </c>
       <c r="E107">
-        <v>-1.024701010336413</v>
+        <v>-0.791989086801595</v>
       </c>
       <c r="F107">
-        <v>8.434121034185758E-05</v>
+        <v>-0.05135279649343313</v>
       </c>
       <c r="G107">
-        <v>-0.2022930053265227</v>
+        <v>0.1852244493097013</v>
       </c>
     </row>
     <row r="108">
@@ -3265,19 +3265,19 @@
         </is>
       </c>
       <c r="C108">
-        <v>2.039601039167265</v>
+        <v>1.350769212799546</v>
       </c>
       <c r="D108">
-        <v>-0.05147424789989413</v>
+        <v>0.2081325440397148</v>
       </c>
       <c r="E108">
-        <v>0.4756751997726407</v>
+        <v>-0.1291953681347499</v>
       </c>
       <c r="F108">
-        <v>-0.03420857412944679</v>
+        <v>-0.0168940246004872</v>
       </c>
       <c r="G108">
-        <v>0.1372489138054017</v>
+        <v>-0.1283421373169</v>
       </c>
     </row>
     <row r="109">
@@ -3292,19 +3292,19 @@
         </is>
       </c>
       <c r="C109">
-        <v>4.364622837018583</v>
+        <v>3.07995742707377</v>
       </c>
       <c r="D109">
-        <v>1.093905451282974</v>
+        <v>1.949360503257368</v>
       </c>
       <c r="E109">
-        <v>0.4709624963681721</v>
+        <v>-1.078363214546839</v>
       </c>
       <c r="F109">
-        <v>0.1354560508997188</v>
+        <v>0.1732126121323299</v>
       </c>
       <c r="G109">
-        <v>-0.3073299043718131</v>
+        <v>0.1309595508377981</v>
       </c>
     </row>
     <row r="110">
@@ -3319,19 +3319,19 @@
         </is>
       </c>
       <c r="C110">
-        <v>-4.939260587579532</v>
+        <v>-2.722560154132829</v>
       </c>
       <c r="D110">
-        <v>0.3695308830383392</v>
+        <v>0.5752747169622118</v>
       </c>
       <c r="E110">
-        <v>-0.06313494306676404</v>
+        <v>-1.345050324794683</v>
       </c>
       <c r="F110">
-        <v>-0.3922952497074163</v>
+        <v>-0.4142801188265118</v>
       </c>
       <c r="G110">
-        <v>0.02683710875454953</v>
+        <v>-0.01450089418288265</v>
       </c>
     </row>
     <row r="111">
@@ -3346,19 +3346,19 @@
         </is>
       </c>
       <c r="C111">
-        <v>1.830176137181053</v>
+        <v>0.6600466295955367</v>
       </c>
       <c r="D111">
-        <v>0.8756021853218813</v>
+        <v>0.6196069414900999</v>
       </c>
       <c r="E111">
-        <v>0.2480995621645707</v>
+        <v>1.055226745978905</v>
       </c>
       <c r="F111">
-        <v>0.8268645098252667</v>
+        <v>0.8427323602078718</v>
       </c>
       <c r="G111">
-        <v>0.2154763903072833</v>
+        <v>-0.09989706149189553</v>
       </c>
     </row>
     <row r="112">
@@ -3373,19 +3373,19 @@
         </is>
       </c>
       <c r="C112">
-        <v>5.130553095331351</v>
+        <v>3.160758353949882</v>
       </c>
       <c r="D112">
-        <v>-0.4558223827828711</v>
+        <v>-0.1711048009799861</v>
       </c>
       <c r="E112">
-        <v>0.8057986872331836</v>
+        <v>0.5094599009276419</v>
       </c>
       <c r="F112">
-        <v>-0.211253657534725</v>
+        <v>-0.151988306519739</v>
       </c>
       <c r="G112">
-        <v>-0.0596843487940186</v>
+        <v>-0.05837003313149804</v>
       </c>
     </row>
     <row r="113">
@@ -3400,19 +3400,19 @@
         </is>
       </c>
       <c r="C113">
-        <v>-1.304354471110287</v>
+        <v>-0.5215846957571713</v>
       </c>
       <c r="D113">
-        <v>-0.6297775958910005</v>
+        <v>-0.399390430560085</v>
       </c>
       <c r="E113">
-        <v>0.2349934986025744</v>
+        <v>-0.7324887258054692</v>
       </c>
       <c r="F113">
-        <v>-0.3748811440696154</v>
+        <v>-0.3731795283021782</v>
       </c>
       <c r="G113">
-        <v>0.09632058723876061</v>
+        <v>-0.07080912061083514</v>
       </c>
     </row>
     <row r="114">
@@ -3427,19 +3427,19 @@
         </is>
       </c>
       <c r="C114">
-        <v>-5.052795836491382</v>
+        <v>-2.962776196931117</v>
       </c>
       <c r="D114">
-        <v>-0.2801257539262147</v>
+        <v>-0.2849790629476541</v>
       </c>
       <c r="E114">
-        <v>0.03695708634918604</v>
+        <v>-0.8289901858238603</v>
       </c>
       <c r="F114">
-        <v>-0.2328158706791684</v>
+        <v>-0.2227994763780034</v>
       </c>
       <c r="G114">
-        <v>-0.2337900467052686</v>
+        <v>0.1127718614670426</v>
       </c>
     </row>
     <row r="115">
@@ -3454,19 +3454,19 @@
         </is>
       </c>
       <c r="C115">
-        <v>-0.6997740988308284</v>
+        <v>-0.8279085207129887</v>
       </c>
       <c r="D115">
-        <v>0.9768651684436539</v>
+        <v>0.8076829161138082</v>
       </c>
       <c r="E115">
-        <v>0.3761030447395787</v>
+        <v>0.4060395417676167</v>
       </c>
       <c r="F115">
-        <v>0.4687455180605846</v>
+        <v>0.5031548386232529</v>
       </c>
       <c r="G115">
-        <v>-0.1308705042300828</v>
+        <v>-0.01110007055404521</v>
       </c>
     </row>
     <row r="116">
@@ -3481,19 +3481,19 @@
         </is>
       </c>
       <c r="C116">
-        <v>-1.465055913625761</v>
+        <v>-0.706577181812413</v>
       </c>
       <c r="D116">
-        <v>0.6658709120428438</v>
+        <v>0.7944007497574752</v>
       </c>
       <c r="E116">
-        <v>-0.4293315995625723</v>
+        <v>-0.6860686267146576</v>
       </c>
       <c r="F116">
-        <v>-0.2102229808059854</v>
+        <v>-0.2521206876748739</v>
       </c>
       <c r="G116">
-        <v>0.1113166238758167</v>
+        <v>-0.02346527229411917</v>
       </c>
     </row>
     <row r="117">
@@ -3508,19 +3508,19 @@
         </is>
       </c>
       <c r="C117">
-        <v>-3.068540179608688</v>
+        <v>-2.330926970631769</v>
       </c>
       <c r="D117">
-        <v>0.7724370817636117</v>
+        <v>0.3575490389108458</v>
       </c>
       <c r="E117">
-        <v>-0.8028256011123457</v>
+        <v>-0.0862381113936137</v>
       </c>
       <c r="F117">
-        <v>-0.5571921881122626</v>
+        <v>-0.6107220141402399</v>
       </c>
       <c r="G117">
-        <v>0.1703554482709433</v>
+        <v>0.02481165898085299</v>
       </c>
     </row>
     <row r="118">
@@ -3535,19 +3535,19 @@
         </is>
       </c>
       <c r="C118">
-        <v>3.236199256707722</v>
+        <v>2.535728723532479</v>
       </c>
       <c r="D118">
-        <v>0.3516991717151886</v>
+        <v>0.8561328640013834</v>
       </c>
       <c r="E118">
-        <v>-0.7789631749972781</v>
+        <v>-0.7912678596903487</v>
       </c>
       <c r="F118">
-        <v>0.1401923469501548</v>
+        <v>0.101229758116166</v>
       </c>
       <c r="G118">
-        <v>-0.1354334775461476</v>
+        <v>0.1613837846509327</v>
       </c>
     </row>
     <row r="119">
@@ -3562,19 +3562,19 @@
         </is>
       </c>
       <c r="C119">
-        <v>-1.241489632773379</v>
+        <v>-0.3795954339276689</v>
       </c>
       <c r="D119">
-        <v>-0.2924973659268374</v>
+        <v>-0.03861113444944195</v>
       </c>
       <c r="E119">
-        <v>0.2286884392392537</v>
+        <v>-0.8152614104281863</v>
       </c>
       <c r="F119">
-        <v>-0.2686057012442072</v>
+        <v>-0.3015246399042431</v>
       </c>
       <c r="G119">
-        <v>0.1767061097088145</v>
+        <v>-0.00355953639740095</v>
       </c>
     </row>
     <row r="120">
@@ -3589,19 +3589,19 @@
         </is>
       </c>
       <c r="C120">
-        <v>4.314601512445951</v>
+        <v>2.649002635117879</v>
       </c>
       <c r="D120">
-        <v>0.9385871909566845</v>
+        <v>1.08834145902653</v>
       </c>
       <c r="E120">
-        <v>-0.8978563755280076</v>
+        <v>0.09441982104314617</v>
       </c>
       <c r="F120">
-        <v>0.01256691999150239</v>
+        <v>-0.02213229402703127</v>
       </c>
       <c r="G120">
-        <v>-0.02146180262284474</v>
+        <v>0.1095495792758815</v>
       </c>
     </row>
     <row r="121">
@@ -3616,19 +3616,19 @@
         </is>
       </c>
       <c r="C121">
-        <v>-5.476687090951426</v>
+        <v>-4.303200073939087</v>
       </c>
       <c r="D121">
-        <v>0.8883934868949065</v>
+        <v>0.04116990319698477</v>
       </c>
       <c r="E121">
-        <v>0.3523067216213319</v>
+        <v>1.359700196399688</v>
       </c>
       <c r="F121">
-        <v>-0.2481866302343841</v>
+        <v>-0.1887825817073567</v>
       </c>
       <c r="G121">
-        <v>-0.1691219155382145</v>
+        <v>0.177803766429488</v>
       </c>
     </row>
     <row r="122">
@@ -3643,19 +3643,19 @@
         </is>
       </c>
       <c r="C122">
-        <v>-0.6279705216780007</v>
+        <v>-0.941428016342206</v>
       </c>
       <c r="D122">
-        <v>1.145915459201077</v>
+        <v>0.5526379906451673</v>
       </c>
       <c r="E122">
-        <v>-0.5287209277397911</v>
+        <v>1.083305507621273</v>
       </c>
       <c r="F122">
-        <v>-0.07536745660617022</v>
+        <v>-0.1248283962460986</v>
       </c>
       <c r="G122">
-        <v>0.3209596577948394</v>
+        <v>-0.133784575704458</v>
       </c>
     </row>
     <row r="123">
@@ -3670,19 +3670,19 @@
         </is>
       </c>
       <c r="C123">
-        <v>-1.498501414677736</v>
+        <v>-0.4910190445850966</v>
       </c>
       <c r="D123">
-        <v>-0.5488116284495389</v>
+        <v>-0.495262012792087</v>
       </c>
       <c r="E123">
-        <v>-0.5876146210995294</v>
+        <v>-0.411398458127453</v>
       </c>
       <c r="F123">
-        <v>-0.3433000054630384</v>
+        <v>-0.3904868742829362</v>
       </c>
       <c r="G123">
-        <v>0.1440230749754979</v>
+        <v>0.01386892132536104</v>
       </c>
     </row>
     <row r="124">
@@ -3697,19 +3697,19 @@
         </is>
       </c>
       <c r="C124">
-        <v>1.552568295549102</v>
+        <v>0.5864444800012237</v>
       </c>
       <c r="D124">
-        <v>0.1334820356507678</v>
+        <v>-0.1399607547196105</v>
       </c>
       <c r="E124">
-        <v>-0.3303571102712888</v>
+        <v>0.6819033288196421</v>
       </c>
       <c r="F124">
-        <v>-0.8771733063297348</v>
+        <v>-0.8861799591207351</v>
       </c>
       <c r="G124">
-        <v>0.07314316315684333</v>
+        <v>-0.09853606370684297</v>
       </c>
     </row>
     <row r="125">
@@ -3724,19 +3724,19 @@
         </is>
       </c>
       <c r="C125">
-        <v>-3.825632944544779</v>
+        <v>-2.268921947371267</v>
       </c>
       <c r="D125">
-        <v>-0.4457421579192012</v>
+        <v>-0.3163671156993469</v>
       </c>
       <c r="E125">
-        <v>1.576065725670757</v>
+        <v>-0.5396935904020463</v>
       </c>
       <c r="F125">
-        <v>0.0872870896349368</v>
+        <v>0.114074878588167</v>
       </c>
       <c r="G125">
-        <v>0.5321417501620777</v>
+        <v>-0.41893776871865</v>
       </c>
     </row>
     <row r="126">
@@ -3751,19 +3751,19 @@
         </is>
       </c>
       <c r="C126">
-        <v>-5.460312204871441</v>
+        <v>-3.154676979078838</v>
       </c>
       <c r="D126">
-        <v>0.241139961473651</v>
+        <v>0.3424759759414758</v>
       </c>
       <c r="E126">
-        <v>0.1609010054702602</v>
+        <v>-1.11971483509866</v>
       </c>
       <c r="F126">
-        <v>-0.1703946301953241</v>
+        <v>-0.1722604718368709</v>
       </c>
       <c r="G126">
-        <v>-0.1124353026961348</v>
+        <v>0.03131350033066337</v>
       </c>
     </row>
   </sheetData>

--- a/03_Outputs/all/03_DS/ds_idx15_vejez.xlsx
+++ b/03_Outputs/all/03_DS/ds_idx15_vejez.xlsx
@@ -403,19 +403,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>1.839010871902225</v>
+        <v>1.674909473220988</v>
       </c>
       <c r="D2">
-        <v>-2.161913593890198</v>
+        <v>-2.380681016321146</v>
       </c>
       <c r="E2">
-        <v>-0.04420605477791918</v>
+        <v>-0.09292194364106034</v>
       </c>
       <c r="F2">
-        <v>-0.5333685648376264</v>
+        <v>0.3786833157667859</v>
       </c>
       <c r="G2">
-        <v>0.2666304125916659</v>
+        <v>-0.4535418681551858</v>
       </c>
     </row>
     <row r="3">
@@ -430,19 +430,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>1.639520822575078</v>
+        <v>2.373527678234779</v>
       </c>
       <c r="D3">
-        <v>1.68066208560771</v>
+        <v>1.533615558327731</v>
       </c>
       <c r="E3">
-        <v>-0.3954520239065</v>
+        <v>-0.5320391578089255</v>
       </c>
       <c r="F3">
-        <v>0.1580503838153209</v>
+        <v>0.4743350767728872</v>
       </c>
       <c r="G3">
-        <v>-0.08479564373818936</v>
+        <v>0.2865769627058879</v>
       </c>
     </row>
     <row r="4">
@@ -457,19 +457,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.5535312598093336</v>
+        <v>1.309094707903618</v>
       </c>
       <c r="D4">
-        <v>0.9887228562416728</v>
+        <v>1.012878724013655</v>
       </c>
       <c r="E4">
-        <v>1.100558360246861</v>
+        <v>1.106748918874793</v>
       </c>
       <c r="F4">
-        <v>-0.1432162381070479</v>
+        <v>-0.2160728175462882</v>
       </c>
       <c r="G4">
-        <v>-0.05552146679948636</v>
+        <v>-0.2268437120685775</v>
       </c>
     </row>
     <row r="5">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.286072138613866</v>
+        <v>0.6467950960163521</v>
       </c>
       <c r="D5">
-        <v>0.4347621279891651</v>
+        <v>0.5161127085251456</v>
       </c>
       <c r="E5">
-        <v>1.561363062943767</v>
+        <v>1.485493810930482</v>
       </c>
       <c r="F5">
-        <v>-0.2261745448323392</v>
+        <v>0.8981211785080475</v>
       </c>
       <c r="G5">
-        <v>0.06577518121067361</v>
+        <v>-0.02632956961950246</v>
       </c>
     </row>
     <row r="6">
@@ -511,19 +511,19 @@
         </is>
       </c>
       <c r="C6">
-        <v>1.400753956318101</v>
+        <v>1.557404047764492</v>
       </c>
       <c r="D6">
-        <v>-0.8975277534409311</v>
+        <v>-1.081104288325204</v>
       </c>
       <c r="E6">
-        <v>-0.9227941135775906</v>
+        <v>-0.8707781658455418</v>
       </c>
       <c r="F6">
-        <v>0.552029611871715</v>
+        <v>-0.7670585645275999</v>
       </c>
       <c r="G6">
-        <v>-0.064916977753503</v>
+        <v>0.3907154835304485</v>
       </c>
     </row>
     <row r="7">
@@ -538,19 +538,19 @@
         </is>
       </c>
       <c r="C7">
-        <v>-1.030632857018809</v>
+        <v>-1.129565510229344</v>
       </c>
       <c r="D7">
-        <v>0.7832096851529837</v>
+        <v>0.8872369918669004</v>
       </c>
       <c r="E7">
-        <v>-0.112785492770087</v>
+        <v>-0.09777549414992587</v>
       </c>
       <c r="F7">
-        <v>-0.1922963360953172</v>
+        <v>-0.2059988563222577</v>
       </c>
       <c r="G7">
-        <v>-0.1321071363263636</v>
+        <v>-0.242572595697764</v>
       </c>
     </row>
     <row r="8">
@@ -565,19 +565,19 @@
         </is>
       </c>
       <c r="C8">
-        <v>0.484234626465866</v>
+        <v>0.816670002348032</v>
       </c>
       <c r="D8">
-        <v>0.9016786126393537</v>
+        <v>0.8579652210802351</v>
       </c>
       <c r="E8">
-        <v>0.06281784227073628</v>
+        <v>-0.0004835766667685704</v>
       </c>
       <c r="F8">
-        <v>-0.275421491205485</v>
+        <v>0.160558286733528</v>
       </c>
       <c r="G8">
-        <v>0.04290856788822662</v>
+        <v>-0.2491823506751376</v>
       </c>
     </row>
     <row r="9">
@@ -592,19 +592,19 @@
         </is>
       </c>
       <c r="C9">
-        <v>0.9544907682887368</v>
+        <v>1.480547118617274</v>
       </c>
       <c r="D9">
-        <v>-0.7053052633378093</v>
+        <v>-0.7047508648155589</v>
       </c>
       <c r="E9">
-        <v>0.7752419964191987</v>
+        <v>0.8862043579006624</v>
       </c>
       <c r="F9">
-        <v>1.284857085131493</v>
+        <v>-0.5030136555986374</v>
       </c>
       <c r="G9">
-        <v>0.08938053465369108</v>
+        <v>1.192419903014491</v>
       </c>
     </row>
     <row r="10">
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="C10">
-        <v>-0.7517887276083034</v>
+        <v>-0.6274153035400012</v>
       </c>
       <c r="D10">
-        <v>0.919503235497841</v>
+        <v>1.04279467997204</v>
       </c>
       <c r="E10">
-        <v>0.08970174053489077</v>
+        <v>0.1081640545591804</v>
       </c>
       <c r="F10">
-        <v>-0.1429814449533513</v>
+        <v>0.5328055889351268</v>
       </c>
       <c r="G10">
-        <v>0.0544915088779469</v>
+        <v>-0.01234144655085356</v>
       </c>
     </row>
     <row r="11">
@@ -646,19 +646,19 @@
         </is>
       </c>
       <c r="C11">
-        <v>-2.816074698359538</v>
+        <v>-3.325408717264688</v>
       </c>
       <c r="D11">
-        <v>-0.003090880287206499</v>
+        <v>0.3316679116404281</v>
       </c>
       <c r="E11">
-        <v>0.6670562567888787</v>
+        <v>0.8178752092893854</v>
       </c>
       <c r="F11">
-        <v>-0.09880773744064668</v>
+        <v>-0.2991914989672441</v>
       </c>
       <c r="G11">
-        <v>-0.09434933505130029</v>
+        <v>-0.1754227831429641</v>
       </c>
     </row>
     <row r="12">
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="C12">
-        <v>0.4420481621236587</v>
+        <v>0.399808518196247</v>
       </c>
       <c r="D12">
-        <v>-0.05278668746363599</v>
+        <v>-0.1365285313856276</v>
       </c>
       <c r="E12">
-        <v>-0.3085787095013065</v>
+        <v>-0.3566454126513431</v>
       </c>
       <c r="F12">
-        <v>0.03893663602594179</v>
+        <v>0.02513466551003203</v>
       </c>
       <c r="G12">
-        <v>0.176177211278078</v>
+        <v>0.04770616423561684</v>
       </c>
     </row>
     <row r="13">
@@ -700,19 +700,19 @@
         </is>
       </c>
       <c r="C13">
-        <v>-0.719728652995319</v>
+        <v>-0.3696884398673731</v>
       </c>
       <c r="D13">
-        <v>1.010463836395759</v>
+        <v>1.206280804578066</v>
       </c>
       <c r="E13">
-        <v>0.2979674603133923</v>
+        <v>0.3612684430453962</v>
       </c>
       <c r="F13">
-        <v>0.01996820216189975</v>
+        <v>1.09631856527921</v>
       </c>
       <c r="G13">
-        <v>0.127287515991992</v>
+        <v>0.3020710526710936</v>
       </c>
     </row>
     <row r="14">
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="C14">
-        <v>-2.448164083597422</v>
+        <v>-3.87935852261573</v>
       </c>
       <c r="D14">
-        <v>-2.533752332922437</v>
+        <v>-2.361396603996886</v>
       </c>
       <c r="E14">
-        <v>-0.5505917781927652</v>
+        <v>-0.3857681562000246</v>
       </c>
       <c r="F14">
-        <v>0.5018541235200097</v>
+        <v>-0.3161152352356665</v>
       </c>
       <c r="G14">
-        <v>0.03771862557027159</v>
+        <v>0.4547626045665553</v>
       </c>
     </row>
     <row r="15">
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="C15">
-        <v>-2.366223663349591</v>
+        <v>-2.626024366575254</v>
       </c>
       <c r="D15">
-        <v>1.010965399440677</v>
+        <v>1.285150555238636</v>
       </c>
       <c r="E15">
-        <v>0.6720882630417219</v>
+        <v>0.7249899549238439</v>
       </c>
       <c r="F15">
-        <v>-0.002134191495940114</v>
+        <v>0.07017892001911823</v>
       </c>
       <c r="G15">
-        <v>0.1566707702014022</v>
+        <v>0.006548175710276948</v>
       </c>
     </row>
     <row r="16">
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="C16">
-        <v>-0.6969970275921862</v>
+        <v>-0.5523605215818573</v>
       </c>
       <c r="D16">
-        <v>1.59507228028979</v>
+        <v>1.704520925366335</v>
       </c>
       <c r="E16">
-        <v>0.6136790248976071</v>
+        <v>0.5121581809317804</v>
       </c>
       <c r="F16">
-        <v>-0.1639232451893539</v>
+        <v>0.7540061107223356</v>
       </c>
       <c r="G16">
-        <v>0.3540739444861541</v>
+        <v>0.01337425324879749</v>
       </c>
     </row>
     <row r="17">
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C17">
-        <v>2.706526626168289</v>
+        <v>4.279948624093747</v>
       </c>
       <c r="D17">
-        <v>1.744933841865554</v>
+        <v>1.574464490560833</v>
       </c>
       <c r="E17">
-        <v>0.763303051694423</v>
+        <v>0.7113685980151739</v>
       </c>
       <c r="F17">
-        <v>0.09234662178437168</v>
+        <v>-0.419649284047278</v>
       </c>
       <c r="G17">
-        <v>-0.2599232603414567</v>
+        <v>-0.03041404937502193</v>
       </c>
     </row>
     <row r="18">
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="C18">
-        <v>1.954505650224813</v>
+        <v>2.205755806147468</v>
       </c>
       <c r="D18">
-        <v>-2.39594086984849</v>
+        <v>-2.557100273414268</v>
       </c>
       <c r="E18">
-        <v>0.003155065469334251</v>
+        <v>0.1334194114620162</v>
       </c>
       <c r="F18">
-        <v>0.4359983710422551</v>
+        <v>-0.5544516787932822</v>
       </c>
       <c r="G18">
-        <v>-0.1681152832662953</v>
+        <v>0.3145630132961715</v>
       </c>
     </row>
     <row r="19">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="C19">
-        <v>-1.133840325196261</v>
+        <v>-1.410123629617422</v>
       </c>
       <c r="D19">
-        <v>-0.6454444876716638</v>
+        <v>-0.484144679482815</v>
       </c>
       <c r="E19">
-        <v>0.310926892526216</v>
+        <v>0.4244848587111271</v>
       </c>
       <c r="F19">
-        <v>0.546326799503141</v>
+        <v>0.0585885590983492</v>
       </c>
       <c r="G19">
-        <v>-0.03182374948772878</v>
+        <v>0.5802215997161331</v>
       </c>
     </row>
     <row r="20">
@@ -889,19 +889,19 @@
         </is>
       </c>
       <c r="C20">
-        <v>0.2439541386827118</v>
+        <v>-0.7132287867575099</v>
       </c>
       <c r="D20">
-        <v>-2.411298196936192</v>
+        <v>-2.510256135673643</v>
       </c>
       <c r="E20">
-        <v>0.2862584582525418</v>
+        <v>0.176233891769239</v>
       </c>
       <c r="F20">
-        <v>-0.1853886562556104</v>
+        <v>0.7799630333050066</v>
       </c>
       <c r="G20">
-        <v>0.235600522771273</v>
+        <v>-0.0001445140753283548</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="C21">
-        <v>-0.6588373570057986</v>
+        <v>-0.3176333366947382</v>
       </c>
       <c r="D21">
-        <v>1.147794827886895</v>
+        <v>1.303760841787839</v>
       </c>
       <c r="E21">
-        <v>0.8148888905798231</v>
+        <v>0.8293524790013551</v>
       </c>
       <c r="F21">
-        <v>-0.02763609644586704</v>
+        <v>0.3133460213925099</v>
       </c>
       <c r="G21">
-        <v>-0.1971196585703887</v>
+        <v>0.04089832508423324</v>
       </c>
     </row>
     <row r="22">
@@ -943,19 +943,19 @@
         </is>
       </c>
       <c r="C22">
-        <v>-1.169372560492755</v>
+        <v>-1.292102304250449</v>
       </c>
       <c r="D22">
-        <v>1.38132683058839</v>
+        <v>1.466461329064531</v>
       </c>
       <c r="E22">
-        <v>-0.4684225128038061</v>
+        <v>-0.4939394414908497</v>
       </c>
       <c r="F22">
-        <v>0.01031079804598827</v>
+        <v>0.004626741363144924</v>
       </c>
       <c r="G22">
-        <v>0.04876306405823146</v>
+        <v>0.01648023707964802</v>
       </c>
     </row>
     <row r="23">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="C23">
-        <v>0.7788184953763202</v>
+        <v>0.992292636447352</v>
       </c>
       <c r="D23">
-        <v>1.49403115813216</v>
+        <v>1.373781885943135</v>
       </c>
       <c r="E23">
-        <v>-0.1959648403351637</v>
+        <v>-0.3951986693070927</v>
       </c>
       <c r="F23">
-        <v>0.1264580002599428</v>
+        <v>0.5135809903648109</v>
       </c>
       <c r="G23">
-        <v>0.1478332025217961</v>
+        <v>0.2551080804992961</v>
       </c>
     </row>
     <row r="24">
@@ -997,19 +997,19 @@
         </is>
       </c>
       <c r="C24">
-        <v>-2.438255771770216</v>
+        <v>-2.976383657445853</v>
       </c>
       <c r="D24">
-        <v>0.306178298367945</v>
+        <v>0.531582283078011</v>
       </c>
       <c r="E24">
-        <v>0.1136118840582188</v>
+        <v>0.2029133332508586</v>
       </c>
       <c r="F24">
-        <v>-0.519060016375249</v>
+        <v>-0.4681671976816104</v>
       </c>
       <c r="G24">
-        <v>-0.2088968733499101</v>
+        <v>-0.6543194033587862</v>
       </c>
     </row>
     <row r="25">
@@ -1024,19 +1024,19 @@
         </is>
       </c>
       <c r="C25">
-        <v>-1.19741415019076</v>
+        <v>-1.245203867450168</v>
       </c>
       <c r="D25">
-        <v>-0.7007634316737044</v>
+        <v>-0.5116832734335708</v>
       </c>
       <c r="E25">
-        <v>1.297204999663305</v>
+        <v>1.443533832686089</v>
       </c>
       <c r="F25">
-        <v>-0.3727891096533578</v>
+        <v>-0.6122835466372533</v>
       </c>
       <c r="G25">
-        <v>-0.1568145315603992</v>
+        <v>-0.5574531099422423</v>
       </c>
     </row>
     <row r="26">
@@ -1051,19 +1051,19 @@
         </is>
       </c>
       <c r="C26">
-        <v>-2.816170168439347</v>
+        <v>-3.585170019338998</v>
       </c>
       <c r="D26">
-        <v>0.3746014752060685</v>
+        <v>0.6168664114724995</v>
       </c>
       <c r="E26">
-        <v>-0.3819431974105689</v>
+        <v>-0.3023821536250295</v>
       </c>
       <c r="F26">
-        <v>-0.3318985726891804</v>
+        <v>-0.1916371023567284</v>
       </c>
       <c r="G26">
-        <v>-0.1918424547118242</v>
+        <v>-0.3817532028923203</v>
       </c>
     </row>
     <row r="27">
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="C27">
-        <v>-1.604763454252469</v>
+        <v>-1.616853066508639</v>
       </c>
       <c r="D27">
-        <v>1.150299316984166</v>
+        <v>1.353067812919553</v>
       </c>
       <c r="E27">
-        <v>0.3738719193950855</v>
+        <v>0.4136795280488877</v>
       </c>
       <c r="F27">
-        <v>0.02958769733209626</v>
+        <v>0.2340809771969301</v>
       </c>
       <c r="G27">
-        <v>0.2668338496829629</v>
+        <v>0.08485142983033275</v>
       </c>
     </row>
     <row r="28">
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="C28">
-        <v>2.280936711820211</v>
+        <v>1.882982589982229</v>
       </c>
       <c r="D28">
-        <v>-2.526047958182551</v>
+        <v>-2.820131346146331</v>
       </c>
       <c r="E28">
-        <v>-0.07828553825921571</v>
+        <v>-0.2252527577988365</v>
       </c>
       <c r="F28">
-        <v>-0.6264721947011245</v>
+        <v>0.9415770296083433</v>
       </c>
       <c r="G28">
-        <v>-0.04317415052482479</v>
+        <v>-0.4130343592959618</v>
       </c>
     </row>
     <row r="29">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="C29">
-        <v>-1.310863192426792</v>
+        <v>-1.333731049315133</v>
       </c>
       <c r="D29">
-        <v>0.6161275532960625</v>
+        <v>0.8092040066423187</v>
       </c>
       <c r="E29">
-        <v>0.316817410845421</v>
+        <v>0.3797687312225661</v>
       </c>
       <c r="F29">
-        <v>-0.4338463154299063</v>
+        <v>0.3236901533908606</v>
       </c>
       <c r="G29">
-        <v>-0.142909654031498</v>
+        <v>-0.3631635066549022</v>
       </c>
     </row>
     <row r="30">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="C30">
-        <v>0.4635711841393251</v>
+        <v>1.09369247035347</v>
       </c>
       <c r="D30">
-        <v>1.113751773233083</v>
+        <v>1.096381873527114</v>
       </c>
       <c r="E30">
-        <v>0.2755805284091946</v>
+        <v>0.2958492139870864</v>
       </c>
       <c r="F30">
-        <v>0.009039440749233116</v>
+        <v>-0.7736542328101703</v>
       </c>
       <c r="G30">
-        <v>-0.2019516766261939</v>
+        <v>-0.1938752808816665</v>
       </c>
     </row>
     <row r="31">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="C31">
-        <v>2.081001495349428</v>
+        <v>2.844758649033861</v>
       </c>
       <c r="D31">
-        <v>1.166498940606996</v>
+        <v>0.9676587269386518</v>
       </c>
       <c r="E31">
-        <v>0.1563839540362648</v>
+        <v>0.002724001396237075</v>
       </c>
       <c r="F31">
-        <v>0.4044951312099392</v>
+        <v>0.1868081323327374</v>
       </c>
       <c r="G31">
-        <v>0.1303481118767193</v>
+        <v>0.4543283381628581</v>
       </c>
     </row>
     <row r="32">
@@ -1213,19 +1213,19 @@
         </is>
       </c>
       <c r="C32">
-        <v>2.20949141053619</v>
+        <v>3.084079007597126</v>
       </c>
       <c r="D32">
-        <v>2.254626304070345</v>
+        <v>2.018554358350786</v>
       </c>
       <c r="E32">
-        <v>-0.6900635583289469</v>
+        <v>-0.9087265592844942</v>
       </c>
       <c r="F32">
-        <v>-0.4019606764783178</v>
+        <v>0.5766812536840955</v>
       </c>
       <c r="G32">
-        <v>-0.03989143667537205</v>
+        <v>-0.2630926631295377</v>
       </c>
     </row>
     <row r="33">
@@ -1240,19 +1240,19 @@
         </is>
       </c>
       <c r="C33">
-        <v>-2.95111462526845</v>
+        <v>-4.38663924062512</v>
       </c>
       <c r="D33">
-        <v>-2.16029721098028</v>
+        <v>-1.932430802413792</v>
       </c>
       <c r="E33">
-        <v>-0.5894876897519079</v>
+        <v>-0.3889604221425924</v>
       </c>
       <c r="F33">
-        <v>1.362310153925946</v>
+        <v>-0.6859347055586822</v>
       </c>
       <c r="G33">
-        <v>-0.09887814409766513</v>
+        <v>1.248793060844299</v>
       </c>
     </row>
     <row r="34">
@@ -1267,19 +1267,19 @@
         </is>
       </c>
       <c r="C34">
-        <v>-0.4594815019063576</v>
+        <v>-0.9042494843391056</v>
       </c>
       <c r="D34">
-        <v>-1.798304127940896</v>
+        <v>-1.736655448610809</v>
       </c>
       <c r="E34">
-        <v>0.3462781248294727</v>
+        <v>0.4405738826114068</v>
       </c>
       <c r="F34">
-        <v>-0.2890093412400216</v>
+        <v>0.07551422214436018</v>
       </c>
       <c r="G34">
-        <v>-0.06952444348053471</v>
+        <v>-0.2793633229684118</v>
       </c>
     </row>
     <row r="35">
@@ -1294,19 +1294,19 @@
         </is>
       </c>
       <c r="C35">
-        <v>3.27834822974753</v>
+        <v>4.411618543005972</v>
       </c>
       <c r="D35">
-        <v>1.740031836867948</v>
+        <v>1.384590447039082</v>
       </c>
       <c r="E35">
-        <v>-0.2670664800890128</v>
+        <v>-0.4930348162495088</v>
       </c>
       <c r="F35">
-        <v>0.1084401685819258</v>
+        <v>0.07693160420184167</v>
       </c>
       <c r="G35">
-        <v>0.3708339872972807</v>
+        <v>0.1215162007427789</v>
       </c>
     </row>
     <row r="36">
@@ -1321,19 +1321,19 @@
         </is>
       </c>
       <c r="C36">
-        <v>-2.555599909096352</v>
+        <v>-3.27150617331539</v>
       </c>
       <c r="D36">
-        <v>0.09534406808075468</v>
+        <v>0.31711416960794</v>
       </c>
       <c r="E36">
-        <v>-0.06866681218048365</v>
+        <v>0.0123163089219902</v>
       </c>
       <c r="F36">
-        <v>0.1267674298351988</v>
+        <v>-0.3812224754660203</v>
       </c>
       <c r="G36">
-        <v>0.1270936914637735</v>
+        <v>0.03900579067278966</v>
       </c>
     </row>
     <row r="37">
@@ -1348,19 +1348,19 @@
         </is>
       </c>
       <c r="C37">
-        <v>-2.83322385287683</v>
+        <v>-4.097568583811053</v>
       </c>
       <c r="D37">
-        <v>-0.3972441443389783</v>
+        <v>-0.2144439764237613</v>
       </c>
       <c r="E37">
-        <v>-0.3970639615258336</v>
+        <v>-0.3867012670493176</v>
       </c>
       <c r="F37">
-        <v>1.074702538500204</v>
+        <v>-0.1393285741549294</v>
       </c>
       <c r="G37">
-        <v>0.2365458868909258</v>
+        <v>1.077401808766686</v>
       </c>
     </row>
     <row r="38">
@@ -1375,19 +1375,19 @@
         </is>
       </c>
       <c r="C38">
-        <v>2.9994041858856</v>
+        <v>3.904844597827371</v>
       </c>
       <c r="D38">
-        <v>0.2728177967611435</v>
+        <v>-0.0926247322180791</v>
       </c>
       <c r="E38">
-        <v>-1.945460969962853</v>
+        <v>-1.935953866855487</v>
       </c>
       <c r="F38">
-        <v>-1.663604265993972</v>
+        <v>-0.6945371660480574</v>
       </c>
       <c r="G38">
-        <v>-0.1315069766451107</v>
+        <v>-1.863138092414004</v>
       </c>
     </row>
     <row r="39">
@@ -1402,19 +1402,19 @@
         </is>
       </c>
       <c r="C39">
-        <v>1.30777563836203</v>
+        <v>1.660186226980185</v>
       </c>
       <c r="D39">
-        <v>1.341899030497336</v>
+        <v>1.142226499160542</v>
       </c>
       <c r="E39">
-        <v>-1.383012167542606</v>
+        <v>-1.498785566576443</v>
       </c>
       <c r="F39">
-        <v>0.05877515548255657</v>
+        <v>-0.1432052036883608</v>
       </c>
       <c r="G39">
-        <v>-0.2656846569019804</v>
+        <v>0.04340259292351316</v>
       </c>
     </row>
     <row r="40">
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="C40">
-        <v>1.735510934769253</v>
+        <v>2.534355961354152</v>
       </c>
       <c r="D40">
-        <v>0.3071721023463315</v>
+        <v>0.2009323841802795</v>
       </c>
       <c r="E40">
-        <v>0.6419923850112996</v>
+        <v>0.6078134073559622</v>
       </c>
       <c r="F40">
-        <v>-0.4953370260038868</v>
+        <v>0.2003214449297301</v>
       </c>
       <c r="G40">
-        <v>0.2568276691017291</v>
+        <v>-0.4705633425635519</v>
       </c>
     </row>
     <row r="41">
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C41">
-        <v>0.827486415513251</v>
+        <v>1.356043018299028</v>
       </c>
       <c r="D41">
-        <v>1.123774894862972</v>
+        <v>1.064257623254456</v>
       </c>
       <c r="E41">
-        <v>-0.1007226953256334</v>
+        <v>-0.1524133820448652</v>
       </c>
       <c r="F41">
-        <v>0.0962618042252603</v>
+        <v>0.1351043045262304</v>
       </c>
       <c r="G41">
-        <v>-0.002415271807903586</v>
+        <v>0.1328428847241309</v>
       </c>
     </row>
     <row r="42">
@@ -1483,19 +1483,19 @@
         </is>
       </c>
       <c r="C42">
-        <v>1.922926373161737</v>
+        <v>2.216287900430873</v>
       </c>
       <c r="D42">
-        <v>-1.768442630322928</v>
+        <v>-1.950658814471511</v>
       </c>
       <c r="E42">
-        <v>-0.2395625147352812</v>
+        <v>-0.159861364016179</v>
       </c>
       <c r="F42">
-        <v>-0.1629303652681401</v>
+        <v>-0.3513640782869243</v>
       </c>
       <c r="G42">
-        <v>0.05672339632986626</v>
+        <v>-0.2501717108511523</v>
       </c>
     </row>
     <row r="43">
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="C43">
-        <v>-2.396047543566431</v>
+        <v>-3.189796780830663</v>
       </c>
       <c r="D43">
-        <v>-0.5469913575817961</v>
+        <v>-0.2895307466778606</v>
       </c>
       <c r="E43">
-        <v>0.1551111498172837</v>
+        <v>0.2296850959818426</v>
       </c>
       <c r="F43">
-        <v>-0.9373470740438355</v>
+        <v>0.7382737831596978</v>
       </c>
       <c r="G43">
-        <v>-0.1060942931340973</v>
+        <v>-0.7738213105475799</v>
       </c>
     </row>
     <row r="44">
@@ -1537,19 +1537,19 @@
         </is>
       </c>
       <c r="C44">
-        <v>0.1976175807969054</v>
+        <v>-0.1858275454569238</v>
       </c>
       <c r="D44">
-        <v>-2.03448476049363</v>
+        <v>-2.072399698889962</v>
       </c>
       <c r="E44">
-        <v>-0.156296086544685</v>
+        <v>-0.07287110558425108</v>
       </c>
       <c r="F44">
-        <v>-0.827205916094831</v>
+        <v>0.03326675672849458</v>
       </c>
       <c r="G44">
-        <v>0.1562491808293493</v>
+        <v>-0.8376953002161641</v>
       </c>
     </row>
     <row r="45">
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="C45">
-        <v>2.903739579113998</v>
+        <v>4.247828573538622</v>
       </c>
       <c r="D45">
-        <v>1.52572996460832</v>
+        <v>1.262504891890129</v>
       </c>
       <c r="E45">
-        <v>0.1495205606079606</v>
+        <v>0.05153006715507558</v>
       </c>
       <c r="F45">
-        <v>-0.6414155856166776</v>
+        <v>-0.466234291188752</v>
       </c>
       <c r="G45">
-        <v>-0.3508226535246008</v>
+        <v>-0.7949310736688199</v>
       </c>
     </row>
     <row r="46">
@@ -1591,19 +1591,19 @@
         </is>
       </c>
       <c r="C46">
-        <v>-3.190476543692534</v>
+        <v>-4.32261427781793</v>
       </c>
       <c r="D46">
-        <v>0.04107351169153742</v>
+        <v>0.2794669631485705</v>
       </c>
       <c r="E46">
-        <v>-0.6030899287053682</v>
+        <v>-0.5448939569023288</v>
       </c>
       <c r="F46">
-        <v>0.1088929113565984</v>
+        <v>-0.2502516826736738</v>
       </c>
       <c r="G46">
-        <v>-0.005337487504505875</v>
+        <v>0.06277108366753589</v>
       </c>
     </row>
     <row r="47">
@@ -1618,19 +1618,19 @@
         </is>
       </c>
       <c r="C47">
-        <v>-0.7129478507590424</v>
+        <v>-1.508180638823074</v>
       </c>
       <c r="D47">
-        <v>-1.821304897588436</v>
+        <v>-1.773031686805856</v>
       </c>
       <c r="E47">
-        <v>-0.2630257228200817</v>
+        <v>-0.2015070994417013</v>
       </c>
       <c r="F47">
-        <v>1.241622209593683</v>
+        <v>0.1138688338048358</v>
       </c>
       <c r="G47">
-        <v>-0.2451313172291464</v>
+        <v>1.318705733580973</v>
       </c>
     </row>
     <row r="48">
@@ -1645,19 +1645,19 @@
         </is>
       </c>
       <c r="C48">
-        <v>3.926788945314459</v>
+        <v>3.848504778651483</v>
       </c>
       <c r="D48">
-        <v>-2.851367570334796</v>
+        <v>-3.306896699740447</v>
       </c>
       <c r="E48">
-        <v>0.351061025935975</v>
+        <v>0.1077109458871434</v>
       </c>
       <c r="F48">
-        <v>-0.6763707122906584</v>
+        <v>1.182270447598903</v>
       </c>
       <c r="G48">
-        <v>0.1144438994268681</v>
+        <v>-0.4155344224014735</v>
       </c>
     </row>
     <row r="49">
@@ -1672,19 +1672,19 @@
         </is>
       </c>
       <c r="C49">
-        <v>2.648005512536512</v>
+        <v>3.673586491778142</v>
       </c>
       <c r="D49">
-        <v>0.4641784820049322</v>
+        <v>0.2442777486062649</v>
       </c>
       <c r="E49">
-        <v>0.01306892812614335</v>
+        <v>-0.0181421046392678</v>
       </c>
       <c r="F49">
-        <v>0.7863259984752653</v>
+        <v>-0.3184185452052744</v>
       </c>
       <c r="G49">
-        <v>-0.1328011205917168</v>
+        <v>0.7247883457185321</v>
       </c>
     </row>
     <row r="50">
@@ -1699,19 +1699,19 @@
         </is>
       </c>
       <c r="C50">
-        <v>-1.760390688584983</v>
+        <v>-2.101787205774819</v>
       </c>
       <c r="D50">
-        <v>0.6959065947375164</v>
+        <v>0.9151622255602314</v>
       </c>
       <c r="E50">
-        <v>0.5792674205373501</v>
+        <v>0.5547725543524276</v>
       </c>
       <c r="F50">
-        <v>-0.1884148875062159</v>
+        <v>0.9948866788351272</v>
       </c>
       <c r="G50">
-        <v>0.2186456310683823</v>
+        <v>0.0516129051779923</v>
       </c>
     </row>
     <row r="51">
@@ -1726,19 +1726,19 @@
         </is>
       </c>
       <c r="C51">
-        <v>-0.7081548791108389</v>
+        <v>-0.5067197403507991</v>
       </c>
       <c r="D51">
-        <v>0.4428832616476817</v>
+        <v>0.5308113220257983</v>
       </c>
       <c r="E51">
-        <v>0.5725377860074997</v>
+        <v>0.6642203576124247</v>
       </c>
       <c r="F51">
-        <v>0.6579344038821949</v>
+        <v>-1.100763246509132</v>
       </c>
       <c r="G51">
-        <v>0.1405432090290592</v>
+        <v>0.3877802295272662</v>
       </c>
     </row>
     <row r="52">
@@ -1753,19 +1753,19 @@
         </is>
       </c>
       <c r="C52">
-        <v>1.363529877667301</v>
+        <v>1.375429749464558</v>
       </c>
       <c r="D52">
-        <v>-2.208619900650269</v>
+        <v>-2.332718896991488</v>
       </c>
       <c r="E52">
-        <v>0.1400399418375833</v>
+        <v>0.2183678342841899</v>
       </c>
       <c r="F52">
-        <v>-0.3465412465896867</v>
+        <v>-0.0584809621660914</v>
       </c>
       <c r="G52">
-        <v>0.02154745598600805</v>
+        <v>-0.3739614796441755</v>
       </c>
     </row>
     <row r="53">
@@ -1780,19 +1780,19 @@
         </is>
       </c>
       <c r="C53">
-        <v>2.292416840755966</v>
+        <v>3.192511698254898</v>
       </c>
       <c r="D53">
-        <v>0.7810923825668672</v>
+        <v>0.572078540522251</v>
       </c>
       <c r="E53">
-        <v>-0.4758871610522114</v>
+        <v>-0.5111210515082545</v>
       </c>
       <c r="F53">
-        <v>0.6455394760245757</v>
+        <v>-0.5336449326097135</v>
       </c>
       <c r="G53">
-        <v>-0.1093751699311094</v>
+        <v>0.5410287436586124</v>
       </c>
     </row>
     <row r="54">
@@ -1807,19 +1807,19 @@
         </is>
       </c>
       <c r="C54">
-        <v>0.1443052756080432</v>
+        <v>0.2265787494111656</v>
       </c>
       <c r="D54">
-        <v>1.075385690750195</v>
+        <v>1.01086369358139</v>
       </c>
       <c r="E54">
-        <v>-0.7948803443783723</v>
+        <v>-0.8603006434001942</v>
       </c>
       <c r="F54">
-        <v>0.2487910812255754</v>
+        <v>-0.217369030615503</v>
       </c>
       <c r="G54">
-        <v>0.1940377771849583</v>
+        <v>0.2157831632651413</v>
       </c>
     </row>
     <row r="55">
@@ -1834,19 +1834,19 @@
         </is>
       </c>
       <c r="C55">
-        <v>-0.008508982509760843</v>
+        <v>0.02138827306763136</v>
       </c>
       <c r="D55">
-        <v>-1.882830096399324</v>
+        <v>-1.807057302101448</v>
       </c>
       <c r="E55">
-        <v>0.9481674466638006</v>
+        <v>1.133394051849771</v>
       </c>
       <c r="F55">
-        <v>-0.07933876016272648</v>
+        <v>-0.6320637311398143</v>
       </c>
       <c r="G55">
-        <v>-0.2632608939386458</v>
+        <v>-0.2507702120243689</v>
       </c>
     </row>
     <row r="56">
@@ -1861,19 +1861,19 @@
         </is>
       </c>
       <c r="C56">
-        <v>2.21437537560753</v>
+        <v>2.528633341027191</v>
       </c>
       <c r="D56">
-        <v>-1.242429605989442</v>
+        <v>-1.502383018345449</v>
       </c>
       <c r="E56">
-        <v>-0.5665966590574996</v>
+        <v>-0.55583772806834</v>
       </c>
       <c r="F56">
-        <v>0.03304864709083198</v>
+        <v>-0.4756972776084102</v>
       </c>
       <c r="G56">
-        <v>0.0262599162305184</v>
+        <v>-0.08263928061264564</v>
       </c>
     </row>
     <row r="57">
@@ -1888,19 +1888,19 @@
         </is>
       </c>
       <c r="C57">
-        <v>1.145802090875085</v>
+        <v>2.177990804057972</v>
       </c>
       <c r="D57">
-        <v>-0.3257682345496168</v>
+        <v>-0.3002526775552953</v>
       </c>
       <c r="E57">
-        <v>1.053974341526671</v>
+        <v>1.250404619176445</v>
       </c>
       <c r="F57">
-        <v>-0.05658848165684129</v>
+        <v>-1.045972693506399</v>
       </c>
       <c r="G57">
-        <v>-0.1901761297329304</v>
+        <v>-0.3318889487109352</v>
       </c>
     </row>
     <row r="58">
@@ -1915,19 +1915,19 @@
         </is>
       </c>
       <c r="C58">
-        <v>2.199882115916258</v>
+        <v>3.357285499508679</v>
       </c>
       <c r="D58">
-        <v>0.7930268288066217</v>
+        <v>0.6414283640056875</v>
       </c>
       <c r="E58">
-        <v>0.5651552150937031</v>
+        <v>0.5615453771717078</v>
       </c>
       <c r="F58">
-        <v>0.2986489507824257</v>
+        <v>-0.5921202398994565</v>
       </c>
       <c r="G58">
-        <v>0.01667899460798721</v>
+        <v>0.1444591799703369</v>
       </c>
     </row>
     <row r="59">
@@ -1942,19 +1942,19 @@
         </is>
       </c>
       <c r="C59">
-        <v>1.13126282429313</v>
+        <v>1.523762910942362</v>
       </c>
       <c r="D59">
-        <v>0.8030684749516006</v>
+        <v>0.7145315285603651</v>
       </c>
       <c r="E59">
-        <v>0.9368135498529445</v>
+        <v>0.760803562160811</v>
       </c>
       <c r="F59">
-        <v>-0.2774228806750972</v>
+        <v>0.766227234300059</v>
       </c>
       <c r="G59">
-        <v>-0.1088541716335317</v>
+        <v>-0.1192603997563355</v>
       </c>
     </row>
     <row r="60">
@@ -1969,19 +1969,19 @@
         </is>
       </c>
       <c r="C60">
-        <v>1.809411086706564</v>
+        <v>0.4680022880209668</v>
       </c>
       <c r="D60">
-        <v>-2.017643566205205</v>
+        <v>-2.407232056989506</v>
       </c>
       <c r="E60">
-        <v>0.1166571752621642</v>
+        <v>-0.3873111022198142</v>
       </c>
       <c r="F60">
-        <v>-0.3888819456643019</v>
+        <v>2.218646883299312</v>
       </c>
       <c r="G60">
-        <v>0.306849344425015</v>
+        <v>0.1340507243633816</v>
       </c>
     </row>
     <row r="61">
@@ -1996,19 +1996,19 @@
         </is>
       </c>
       <c r="C61">
-        <v>-1.468253337150532</v>
+        <v>-1.627653500463413</v>
       </c>
       <c r="D61">
-        <v>1.047531896898536</v>
+        <v>1.190000319346199</v>
       </c>
       <c r="E61">
-        <v>-0.1174873692004088</v>
+        <v>-0.09886519144747613</v>
       </c>
       <c r="F61">
-        <v>-0.2215757633698951</v>
+        <v>-0.08712665098481405</v>
       </c>
       <c r="G61">
-        <v>-0.1262193629361317</v>
+        <v>-0.2478917274513411</v>
       </c>
     </row>
     <row r="62">
@@ -2023,19 +2023,19 @@
         </is>
       </c>
       <c r="C62">
-        <v>2.202925493300226</v>
+        <v>2.623771727341876</v>
       </c>
       <c r="D62">
-        <v>1.608672263124453</v>
+        <v>1.327829134196289</v>
       </c>
       <c r="E62">
-        <v>-0.6201156192113326</v>
+        <v>-0.9265358740671551</v>
       </c>
       <c r="F62">
-        <v>0.2257511411508985</v>
+        <v>1.073815677772898</v>
       </c>
       <c r="G62">
-        <v>0.2760534665148936</v>
+        <v>0.5038341490504414</v>
       </c>
     </row>
     <row r="63">
@@ -2050,19 +2050,19 @@
         </is>
       </c>
       <c r="C63">
-        <v>2.202842379388367</v>
+        <v>3.33128034957527</v>
       </c>
       <c r="D63">
-        <v>0.8876171964688915</v>
+        <v>0.7701350771204978</v>
       </c>
       <c r="E63">
-        <v>1.344948426046934</v>
+        <v>1.259028496010243</v>
       </c>
       <c r="F63">
-        <v>0.2751986501962092</v>
+        <v>0.2224800822943524</v>
       </c>
       <c r="G63">
-        <v>0.1658703626138485</v>
+        <v>0.3121529441863116</v>
       </c>
     </row>
     <row r="64">
@@ -2077,19 +2077,19 @@
         </is>
       </c>
       <c r="C64">
-        <v>1.759209575634501</v>
+        <v>1.6768353549473</v>
       </c>
       <c r="D64">
-        <v>-2.845187308611023</v>
+        <v>-3.02277330201168</v>
       </c>
       <c r="E64">
-        <v>-0.3107356506646884</v>
+        <v>-0.2114467077378147</v>
       </c>
       <c r="F64">
-        <v>-0.5422636470894634</v>
+        <v>-0.1521259166330003</v>
       </c>
       <c r="G64">
-        <v>-0.2170169044746975</v>
+        <v>-0.5869920303535531</v>
       </c>
     </row>
     <row r="65">
@@ -2104,19 +2104,19 @@
         </is>
       </c>
       <c r="C65">
-        <v>1.595262718814727</v>
+        <v>1.739902440556698</v>
       </c>
       <c r="D65">
-        <v>-1.935197961946008</v>
+        <v>-2.07678079891269</v>
       </c>
       <c r="E65">
-        <v>0.1413899944144496</v>
+        <v>0.203961471677659</v>
       </c>
       <c r="F65">
-        <v>-0.1554323374534092</v>
+        <v>-0.1166891462799627</v>
       </c>
       <c r="G65">
-        <v>0.1670316893798421</v>
+        <v>-0.1891885564883333</v>
       </c>
     </row>
     <row r="66">
@@ -2131,19 +2131,19 @@
         </is>
       </c>
       <c r="C66">
-        <v>-0.7292875711071578</v>
+        <v>-0.6592187700434945</v>
       </c>
       <c r="D66">
-        <v>-0.2077548646391924</v>
+        <v>-0.07745993636694007</v>
       </c>
       <c r="E66">
-        <v>0.1626980001314655</v>
+        <v>0.3083851054358426</v>
       </c>
       <c r="F66">
-        <v>0.4669510679911414</v>
+        <v>-0.7636148787943876</v>
       </c>
       <c r="G66">
-        <v>0.07191530282060071</v>
+        <v>0.3042389760936004</v>
       </c>
     </row>
     <row r="67">
@@ -2158,19 +2158,19 @@
         </is>
       </c>
       <c r="C67">
-        <v>0.04356307965473912</v>
+        <v>-0.2813197344280739</v>
       </c>
       <c r="D67">
-        <v>-0.6691106990402781</v>
+        <v>-0.7225233217602479</v>
       </c>
       <c r="E67">
-        <v>-0.3784672937987154</v>
+        <v>-0.3964594465280145</v>
       </c>
       <c r="F67">
-        <v>-0.1147696177676812</v>
+        <v>0.08748957253412359</v>
       </c>
       <c r="G67">
-        <v>0.07348601038419326</v>
+        <v>-0.09265386208770934</v>
       </c>
     </row>
     <row r="68">
@@ -2185,19 +2185,19 @@
         </is>
       </c>
       <c r="C68">
-        <v>1.08724854641561</v>
+        <v>1.797816712719591</v>
       </c>
       <c r="D68">
-        <v>0.5461601356566703</v>
+        <v>0.4952792050960885</v>
       </c>
       <c r="E68">
-        <v>0.6247547780878249</v>
+        <v>0.6248180929437895</v>
       </c>
       <c r="F68">
-        <v>-0.2933381070308989</v>
+        <v>-0.1036895493891711</v>
       </c>
       <c r="G68">
-        <v>0.03779721255926703</v>
+        <v>-0.343588326481639</v>
       </c>
     </row>
     <row r="69">
@@ -2212,19 +2212,19 @@
         </is>
       </c>
       <c r="C69">
-        <v>0.6144391139813635</v>
+        <v>0.7894314868418174</v>
       </c>
       <c r="D69">
-        <v>0.3782082479440951</v>
+        <v>0.3089131497729245</v>
       </c>
       <c r="E69">
-        <v>-0.5738973291858682</v>
+        <v>-0.6038764129602521</v>
       </c>
       <c r="F69">
-        <v>-0.2043918831644752</v>
+        <v>0.1416366893578303</v>
       </c>
       <c r="G69">
-        <v>-0.181054265499349</v>
+        <v>-0.1636618552684567</v>
       </c>
     </row>
     <row r="70">
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="C70">
-        <v>0.3453559457380456</v>
+        <v>-0.07012478193376488</v>
       </c>
       <c r="D70">
-        <v>-2.22858012340127</v>
+        <v>-2.298918175964697</v>
       </c>
       <c r="E70">
-        <v>-0.5276822957328621</v>
+        <v>-0.4156126006010016</v>
       </c>
       <c r="F70">
-        <v>-0.05298305873714337</v>
+        <v>-0.3346400429442152</v>
       </c>
       <c r="G70">
-        <v>0.05958518891851777</v>
+        <v>-0.126891609994511</v>
       </c>
     </row>
     <row r="71">
@@ -2266,19 +2266,19 @@
         </is>
       </c>
       <c r="C71">
-        <v>2.688237180906775</v>
+        <v>3.832579803298468</v>
       </c>
       <c r="D71">
-        <v>2.125187242214348</v>
+        <v>1.841404467527931</v>
       </c>
       <c r="E71">
-        <v>-0.9255074778411998</v>
+        <v>-1.065242027089778</v>
       </c>
       <c r="F71">
-        <v>0.1174027813020833</v>
+        <v>-0.212158204966075</v>
       </c>
       <c r="G71">
-        <v>-0.2999435860954894</v>
+        <v>0.07299655266021839</v>
       </c>
     </row>
     <row r="72">
@@ -2293,19 +2293,19 @@
         </is>
       </c>
       <c r="C72">
-        <v>-5.227532921612816</v>
+        <v>-6.766339137628891</v>
       </c>
       <c r="D72">
-        <v>-0.5471902821591643</v>
+        <v>-0.02035958398906756</v>
       </c>
       <c r="E72">
-        <v>0.5773928344982386</v>
+        <v>0.7453913033735662</v>
       </c>
       <c r="F72">
-        <v>-0.01775999974000012</v>
+        <v>0.3935071126696424</v>
       </c>
       <c r="G72">
-        <v>0.1409576522975354</v>
+        <v>0.07949952978907404</v>
       </c>
     </row>
     <row r="73">
@@ -2320,19 +2320,19 @@
         </is>
       </c>
       <c r="C73">
-        <v>-3.446971864774098</v>
+        <v>-4.498974900937135</v>
       </c>
       <c r="D73">
-        <v>0.1071821900418558</v>
+        <v>0.4053003459978668</v>
       </c>
       <c r="E73">
-        <v>-0.3747465053142328</v>
+        <v>-0.2795473691588286</v>
       </c>
       <c r="F73">
-        <v>-0.06663490647596096</v>
+        <v>-0.1602694221286596</v>
       </c>
       <c r="G73">
-        <v>-0.05953707240452505</v>
+        <v>-0.09695712046082036</v>
       </c>
     </row>
     <row r="74">
@@ -2347,19 +2347,19 @@
         </is>
       </c>
       <c r="C74">
-        <v>-0.03527131789163493</v>
+        <v>0.50927684159165</v>
       </c>
       <c r="D74">
-        <v>1.279619271679357</v>
+        <v>1.364781525648434</v>
       </c>
       <c r="E74">
-        <v>0.8688799389734392</v>
+        <v>0.8486383287527222</v>
       </c>
       <c r="F74">
-        <v>-0.06483510577867097</v>
+        <v>0.3834573343962174</v>
       </c>
       <c r="G74">
-        <v>0.2721232495994222</v>
+        <v>0.01535099374310323</v>
       </c>
     </row>
     <row r="75">
@@ -2374,19 +2374,19 @@
         </is>
       </c>
       <c r="C75">
-        <v>-2.937297814258928</v>
+        <v>-3.734671653388264</v>
       </c>
       <c r="D75">
-        <v>0.1298203070172723</v>
+        <v>0.3986474964453412</v>
       </c>
       <c r="E75">
-        <v>0.0008291385178073041</v>
+        <v>0.08661802030142374</v>
       </c>
       <c r="F75">
-        <v>-0.4879679419176874</v>
+        <v>-0.07158348492934068</v>
       </c>
       <c r="G75">
-        <v>0.009972493835075784</v>
+        <v>-0.5183841458517591</v>
       </c>
     </row>
     <row r="76">
@@ -2401,19 +2401,19 @@
         </is>
       </c>
       <c r="C76">
-        <v>-3.052506720634756</v>
+        <v>-3.816373613732942</v>
       </c>
       <c r="D76">
-        <v>0.5443465657415898</v>
+        <v>0.8241743609739222</v>
       </c>
       <c r="E76">
-        <v>-0.01452368116795111</v>
+        <v>0.05321451782250264</v>
       </c>
       <c r="F76">
-        <v>-0.4694637037023855</v>
+        <v>-0.1789717711150476</v>
       </c>
       <c r="G76">
-        <v>-0.26170763988898</v>
+        <v>-0.5258786967681923</v>
       </c>
     </row>
     <row r="77">
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="C77">
-        <v>1.108501687481541</v>
+        <v>2.142340290080005</v>
       </c>
       <c r="D77">
-        <v>0.3770890886399601</v>
+        <v>0.4179690594966713</v>
       </c>
       <c r="E77">
-        <v>1.418899150667578</v>
+        <v>1.509271052902518</v>
       </c>
       <c r="F77">
-        <v>0.4841212422155218</v>
+        <v>-0.2133969840553999</v>
       </c>
       <c r="G77">
-        <v>-0.1513394496109454</v>
+        <v>0.4217855838897661</v>
       </c>
     </row>
     <row r="78">
@@ -2455,19 +2455,19 @@
         </is>
       </c>
       <c r="C78">
-        <v>1.242775121577969</v>
+        <v>1.86658633345099</v>
       </c>
       <c r="D78">
-        <v>0.1950714531278918</v>
+        <v>0.0732512318860665</v>
       </c>
       <c r="E78">
-        <v>-0.310765676987514</v>
+        <v>-0.2473550910079182</v>
       </c>
       <c r="F78">
-        <v>-0.03553902757623593</v>
+        <v>-0.971566813887056</v>
       </c>
       <c r="G78">
-        <v>-0.01909347709499865</v>
+        <v>-0.2790951098509891</v>
       </c>
     </row>
     <row r="79">
@@ -2482,19 +2482,19 @@
         </is>
       </c>
       <c r="C79">
-        <v>-1.416550687829511</v>
+        <v>-1.309871802973513</v>
       </c>
       <c r="D79">
-        <v>0.3385961964274331</v>
+        <v>0.559114304575326</v>
       </c>
       <c r="E79">
-        <v>1.270638965798116</v>
+        <v>1.380931736570131</v>
       </c>
       <c r="F79">
-        <v>0.3509097561064929</v>
+        <v>-0.4785845834524489</v>
       </c>
       <c r="G79">
-        <v>0.01595144111893106</v>
+        <v>0.2211024969336655</v>
       </c>
     </row>
     <row r="80">
@@ -2509,19 +2509,19 @@
         </is>
       </c>
       <c r="C80">
-        <v>0.7624558082034327</v>
+        <v>1.209931332471371</v>
       </c>
       <c r="D80">
-        <v>1.470713276902939</v>
+        <v>1.412431867249178</v>
       </c>
       <c r="E80">
-        <v>0.2616757961947982</v>
+        <v>0.1253356883033094</v>
       </c>
       <c r="F80">
-        <v>0.4809520470140139</v>
+        <v>0.4281537858276629</v>
       </c>
       <c r="G80">
-        <v>0.049995817835377</v>
+        <v>0.5948223539867695</v>
       </c>
     </row>
     <row r="81">
@@ -2536,19 +2536,19 @@
         </is>
       </c>
       <c r="C81">
-        <v>-0.0812147330627592</v>
+        <v>-0.4166040730021636</v>
       </c>
       <c r="D81">
-        <v>-0.3357036029187511</v>
+        <v>-0.3976214767082862</v>
       </c>
       <c r="E81">
-        <v>-0.7557560341849772</v>
+        <v>-0.7777504686872583</v>
       </c>
       <c r="F81">
-        <v>-0.499436975447984</v>
+        <v>-0.115125941697036</v>
       </c>
       <c r="G81">
-        <v>-0.01451328569206958</v>
+        <v>-0.5316121970468248</v>
       </c>
     </row>
     <row r="82">
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="C82">
-        <v>0.1375175205617371</v>
+        <v>0.3050562611022868</v>
       </c>
       <c r="D82">
-        <v>0.8938989174241313</v>
+        <v>0.8770817020750971</v>
       </c>
       <c r="E82">
-        <v>-0.2902010091470309</v>
+        <v>-0.3350968630709499</v>
       </c>
       <c r="F82">
-        <v>0.5231245220012147</v>
+        <v>0.2202174936495753</v>
       </c>
       <c r="G82">
-        <v>-0.01799411548352827</v>
+        <v>0.5951356537990585</v>
       </c>
     </row>
     <row r="83">
@@ -2590,19 +2590,19 @@
         </is>
       </c>
       <c r="C83">
-        <v>-1.387751362197188</v>
+        <v>-2.047988863987779</v>
       </c>
       <c r="D83">
-        <v>-0.7134665702219555</v>
+        <v>-0.6150955762947308</v>
       </c>
       <c r="E83">
-        <v>-0.736049590353747</v>
+        <v>-0.6455932395054421</v>
       </c>
       <c r="F83">
-        <v>0.6247192754445139</v>
+        <v>-0.1373767199298988</v>
       </c>
       <c r="G83">
-        <v>-0.06280651749336262</v>
+        <v>0.6248910153967007</v>
       </c>
     </row>
     <row r="84">
@@ -2617,19 +2617,19 @@
         </is>
       </c>
       <c r="C84">
-        <v>-2.383875601153178</v>
+        <v>-3.403714422070412</v>
       </c>
       <c r="D84">
-        <v>-0.5224938374408571</v>
+        <v>-0.3729575437517335</v>
       </c>
       <c r="E84">
-        <v>-0.7341601495210128</v>
+        <v>-0.6700215715932984</v>
       </c>
       <c r="F84">
-        <v>-0.2610588568449501</v>
+        <v>-0.2283740370151802</v>
       </c>
       <c r="G84">
-        <v>0.01167181307679237</v>
+        <v>-0.3143787487361859</v>
       </c>
     </row>
     <row r="85">
@@ -2644,19 +2644,19 @@
         </is>
       </c>
       <c r="C85">
-        <v>2.377786510668908</v>
+        <v>2.516835379533499</v>
       </c>
       <c r="D85">
-        <v>-3.220759171631432</v>
+        <v>-3.401872200349805</v>
       </c>
       <c r="E85">
-        <v>0.5261959735818638</v>
+        <v>0.6177036410247642</v>
       </c>
       <c r="F85">
-        <v>0.4422573321711865</v>
+        <v>0.154403883520091</v>
       </c>
       <c r="G85">
-        <v>-0.002761465039437614</v>
+        <v>0.4904309474575311</v>
       </c>
     </row>
     <row r="86">
@@ -2671,19 +2671,19 @@
         </is>
       </c>
       <c r="C86">
-        <v>1.422178612744733</v>
+        <v>1.606996291175687</v>
       </c>
       <c r="D86">
-        <v>-1.955612062925864</v>
+        <v>-2.041811234155997</v>
       </c>
       <c r="E86">
-        <v>0.7798006318391821</v>
+        <v>0.8395422979071555</v>
       </c>
       <c r="F86">
-        <v>-0.09801048215780624</v>
+        <v>0.1337199870996474</v>
       </c>
       <c r="G86">
-        <v>0.08247765960815193</v>
+        <v>-0.07848054926005915</v>
       </c>
     </row>
     <row r="87">
@@ -2698,19 +2698,19 @@
         </is>
       </c>
       <c r="C87">
-        <v>-1.587586146498063</v>
+        <v>-1.636347781195395</v>
       </c>
       <c r="D87">
-        <v>0.529108731029116</v>
+        <v>0.765533675883608</v>
       </c>
       <c r="E87">
-        <v>0.9385879067366193</v>
+        <v>0.9996513996118386</v>
       </c>
       <c r="F87">
-        <v>-0.299936951989778</v>
+        <v>0.3256735252218673</v>
       </c>
       <c r="G87">
-        <v>0.008001402621872617</v>
+        <v>-0.2375345388536221</v>
       </c>
     </row>
     <row r="88">
@@ -2725,19 +2725,19 @@
         </is>
       </c>
       <c r="C88">
-        <v>2.298660002864017</v>
+        <v>1.698570390145999</v>
       </c>
       <c r="D88">
-        <v>-3.65017534635435</v>
+        <v>-3.935235845384958</v>
       </c>
       <c r="E88">
-        <v>0.311493383302043</v>
+        <v>0.2055661791825183</v>
       </c>
       <c r="F88">
-        <v>-0.05768556013755081</v>
+        <v>0.9256574557544647</v>
       </c>
       <c r="G88">
-        <v>0.07681335261915993</v>
+        <v>0.163045537380811</v>
       </c>
     </row>
     <row r="89">
@@ -2752,19 +2752,19 @@
         </is>
       </c>
       <c r="C89">
-        <v>0.2426018985200276</v>
+        <v>0.5281216381836815</v>
       </c>
       <c r="D89">
-        <v>1.156580996106513</v>
+        <v>1.177277553273649</v>
       </c>
       <c r="E89">
-        <v>0.03966529121407797</v>
+        <v>-0.0406232484497967</v>
       </c>
       <c r="F89">
-        <v>0.1734360573223446</v>
+        <v>0.8682687866867136</v>
       </c>
       <c r="G89">
-        <v>-0.08098069371162318</v>
+        <v>0.3987754670851489</v>
       </c>
     </row>
     <row r="90">
@@ -2779,19 +2779,19 @@
         </is>
       </c>
       <c r="C90">
-        <v>-1.363807047560512</v>
+        <v>-1.63700554234955</v>
       </c>
       <c r="D90">
-        <v>0.2978442325920183</v>
+        <v>0.443811278611979</v>
       </c>
       <c r="E90">
-        <v>-0.08760228620364774</v>
+        <v>-0.03236263196617684</v>
       </c>
       <c r="F90">
-        <v>0.1506417934398214</v>
+        <v>-0.09832119987758162</v>
       </c>
       <c r="G90">
-        <v>-0.04529608939880819</v>
+        <v>0.1393792394915134</v>
       </c>
     </row>
     <row r="91">
@@ -2806,19 +2806,19 @@
         </is>
       </c>
       <c r="C91">
-        <v>-0.01395245744377593</v>
+        <v>0.4473631034756956</v>
       </c>
       <c r="D91">
-        <v>1.470055994683394</v>
+        <v>1.517998559328855</v>
       </c>
       <c r="E91">
-        <v>0.5633858812986579</v>
+        <v>0.5099583390328719</v>
       </c>
       <c r="F91">
-        <v>-0.3691143242832799</v>
+        <v>0.1881064265453948</v>
       </c>
       <c r="G91">
-        <v>-0.03501470545789274</v>
+        <v>-0.3442350343005041</v>
       </c>
     </row>
     <row r="92">
@@ -2833,19 +2833,19 @@
         </is>
       </c>
       <c r="C92">
-        <v>0.5929447250739524</v>
+        <v>0.4921181861950761</v>
       </c>
       <c r="D92">
-        <v>0.1698482499294495</v>
+        <v>0.05570628631378063</v>
       </c>
       <c r="E92">
-        <v>-1.092362562764272</v>
+        <v>-1.142743106294468</v>
       </c>
       <c r="F92">
-        <v>1.065872056706864</v>
+        <v>-0.08466200574039766</v>
       </c>
       <c r="G92">
-        <v>-0.2927801705763346</v>
+        <v>1.095142140602357</v>
       </c>
     </row>
     <row r="93">
@@ -2860,19 +2860,19 @@
         </is>
       </c>
       <c r="C93">
-        <v>0.3323094948120652</v>
+        <v>0.5968966193351612</v>
       </c>
       <c r="D93">
-        <v>-0.3616990807514001</v>
+        <v>-0.3669706302003547</v>
       </c>
       <c r="E93">
-        <v>0.2664056317546476</v>
+        <v>0.3535046578134932</v>
       </c>
       <c r="F93">
-        <v>0.2469755735639602</v>
+        <v>-0.6866483959985125</v>
       </c>
       <c r="G93">
-        <v>-0.1453917515340379</v>
+        <v>0.07683727533045846</v>
       </c>
     </row>
     <row r="94">
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="C94">
-        <v>-1.721706286654919</v>
+        <v>-2.653907063154613</v>
       </c>
       <c r="D94">
-        <v>-0.447882040745247</v>
+        <v>-0.305519548680745</v>
       </c>
       <c r="E94">
-        <v>-0.005069204250680803</v>
+        <v>-0.05722070991805184</v>
       </c>
       <c r="F94">
-        <v>0.09253860263297561</v>
+        <v>0.5680793711202348</v>
       </c>
       <c r="G94">
-        <v>-0.2055344396990527</v>
+        <v>0.2503804452343794</v>
       </c>
     </row>
     <row r="95">
@@ -2914,19 +2914,19 @@
         </is>
       </c>
       <c r="C95">
-        <v>-3.295169397248583</v>
+        <v>-4.055625448970792</v>
       </c>
       <c r="D95">
-        <v>0.3980234258526965</v>
+        <v>0.727212667311419</v>
       </c>
       <c r="E95">
-        <v>0.4947339978116505</v>
+        <v>0.5777998283126438</v>
       </c>
       <c r="F95">
-        <v>-0.1324604739013725</v>
+        <v>0.01230376907187189</v>
       </c>
       <c r="G95">
-        <v>0.1763492597597761</v>
+        <v>-0.1399008280072332</v>
       </c>
     </row>
     <row r="96">
@@ -2941,19 +2941,19 @@
         </is>
       </c>
       <c r="C96">
-        <v>-0.4157037204060638</v>
+        <v>-0.8743344194233964</v>
       </c>
       <c r="D96">
-        <v>-0.008266264980580251</v>
+        <v>-0.07475156435196084</v>
       </c>
       <c r="E96">
-        <v>-1.407701408655081</v>
+        <v>-1.414185814056744</v>
       </c>
       <c r="F96">
-        <v>0.6711075325041121</v>
+        <v>-0.4793999028598904</v>
       </c>
       <c r="G96">
-        <v>0.2610289652498488</v>
+        <v>0.5940010338478517</v>
       </c>
     </row>
     <row r="97">
@@ -2968,19 +2968,19 @@
         </is>
       </c>
       <c r="C97">
-        <v>-0.3832915375497994</v>
+        <v>-0.7072816612946031</v>
       </c>
       <c r="D97">
-        <v>-1.479599576437648</v>
+        <v>-1.457388852904361</v>
       </c>
       <c r="E97">
-        <v>-0.2784793457877385</v>
+        <v>-0.1395101521938826</v>
       </c>
       <c r="F97">
-        <v>0.1808558717697856</v>
+        <v>-0.6308132885255171</v>
       </c>
       <c r="G97">
-        <v>0.1242700169201102</v>
+        <v>0.03686864534501694</v>
       </c>
     </row>
     <row r="98">
@@ -2995,19 +2995,19 @@
         </is>
       </c>
       <c r="C98">
-        <v>-2.125115052958473</v>
+        <v>-2.558486505210728</v>
       </c>
       <c r="D98">
-        <v>0.6224720586817922</v>
+        <v>0.8077572347073689</v>
       </c>
       <c r="E98">
-        <v>-0.07672864120976408</v>
+        <v>-0.02016838243535068</v>
       </c>
       <c r="F98">
-        <v>-0.6261707341440231</v>
+        <v>-0.3722814918503374</v>
       </c>
       <c r="G98">
-        <v>-0.1406533659755011</v>
+        <v>-0.7381645980166439</v>
       </c>
     </row>
     <row r="99">
@@ -3022,19 +3022,19 @@
         </is>
       </c>
       <c r="C99">
-        <v>1.009305175056198</v>
+        <v>1.635219893215939</v>
       </c>
       <c r="D99">
-        <v>1.276115534187383</v>
+        <v>1.166565195005742</v>
       </c>
       <c r="E99">
-        <v>-0.2025233296237564</v>
+        <v>-0.251973269100949</v>
       </c>
       <c r="F99">
-        <v>0.0512696830886087</v>
+        <v>-0.4275032603491461</v>
       </c>
       <c r="G99">
-        <v>0.2703774252599733</v>
+        <v>-0.05695657462752957</v>
       </c>
     </row>
     <row r="100">
@@ -3049,19 +3049,19 @@
         </is>
       </c>
       <c r="C100">
-        <v>0.1367163615411768</v>
+        <v>0.6179723193932795</v>
       </c>
       <c r="D100">
-        <v>1.3238343799334</v>
+        <v>1.335862999168059</v>
       </c>
       <c r="E100">
-        <v>0.1572231219028959</v>
+        <v>0.1455340978196162</v>
       </c>
       <c r="F100">
-        <v>0.1814963926863884</v>
+        <v>-0.3028005121457926</v>
       </c>
       <c r="G100">
-        <v>-0.06529777993933691</v>
+        <v>0.1049380427968892</v>
       </c>
     </row>
     <row r="101">
@@ -3076,19 +3076,19 @@
         </is>
       </c>
       <c r="C101">
-        <v>1.004868971741891</v>
+        <v>1.159494390965403</v>
       </c>
       <c r="D101">
-        <v>-1.488225390892863</v>
+        <v>-1.56168509136938</v>
       </c>
       <c r="E101">
-        <v>0.1267352828913347</v>
+        <v>0.2347486804676212</v>
       </c>
       <c r="F101">
-        <v>0.7407415155937074</v>
+        <v>-0.6008918899473772</v>
       </c>
       <c r="G101">
-        <v>-0.1816675164894583</v>
+        <v>0.6118167187274236</v>
       </c>
     </row>
     <row r="102">
@@ -3103,19 +3103,19 @@
         </is>
       </c>
       <c r="C102">
-        <v>2.764313017376976</v>
+        <v>3.927652216637203</v>
       </c>
       <c r="D102">
-        <v>1.363948432184383</v>
+        <v>1.078263939772267</v>
       </c>
       <c r="E102">
-        <v>-0.4257967514197358</v>
+        <v>-0.5053077845445557</v>
       </c>
       <c r="F102">
-        <v>0.204368389669211</v>
+        <v>-0.7216397887957701</v>
       </c>
       <c r="G102">
-        <v>-0.01400761913076093</v>
+        <v>0.02414611825477575</v>
       </c>
     </row>
     <row r="103">
@@ -3130,19 +3130,19 @@
         </is>
       </c>
       <c r="C103">
-        <v>-0.5087714140610166</v>
+        <v>-1.159147976286181</v>
       </c>
       <c r="D103">
-        <v>-1.594481448034846</v>
+        <v>-1.597779214755981</v>
       </c>
       <c r="E103">
-        <v>-0.7895132503065229</v>
+        <v>-0.7076015993954403</v>
       </c>
       <c r="F103">
-        <v>-0.05812960522941107</v>
+        <v>-0.22352978106675</v>
       </c>
       <c r="G103">
-        <v>-0.07006020856004137</v>
+        <v>-0.09670402475406556</v>
       </c>
     </row>
     <row r="104">
@@ -3157,19 +3157,19 @@
         </is>
       </c>
       <c r="C104">
-        <v>1.379598761762736</v>
+        <v>2.275298614316885</v>
       </c>
       <c r="D104">
-        <v>-0.2935400518017238</v>
+        <v>-0.2909740039308974</v>
       </c>
       <c r="E104">
-        <v>1.123177686298596</v>
+        <v>1.226947509441179</v>
       </c>
       <c r="F104">
-        <v>0.2686921031360277</v>
+        <v>-0.2110324928559681</v>
       </c>
       <c r="G104">
-        <v>-0.2355295591782887</v>
+        <v>0.2106431158382072</v>
       </c>
     </row>
     <row r="105">
@@ -3184,19 +3184,19 @@
         </is>
       </c>
       <c r="C105">
-        <v>-0.2165011323841212</v>
+        <v>-0.7336695322654238</v>
       </c>
       <c r="D105">
-        <v>-0.3132693576233153</v>
+        <v>-0.3791687156354721</v>
       </c>
       <c r="E105">
-        <v>-0.6292010679917693</v>
+        <v>-0.7169134293277174</v>
       </c>
       <c r="F105">
-        <v>-0.6592695267029259</v>
+        <v>0.3703960754468226</v>
       </c>
       <c r="G105">
-        <v>0.221749392959666</v>
+        <v>-0.5789767243871993</v>
       </c>
     </row>
     <row r="106">
@@ -3211,19 +3211,19 @@
         </is>
       </c>
       <c r="C106">
-        <v>-2.155117117570998</v>
+        <v>-3.738535773507726</v>
       </c>
       <c r="D106">
-        <v>-1.059200427339337</v>
+        <v>-1.008603701931471</v>
       </c>
       <c r="E106">
-        <v>-1.290988626194469</v>
+        <v>-1.350433410540777</v>
       </c>
       <c r="F106">
-        <v>0.8634370148858768</v>
+        <v>0.1520082337267959</v>
       </c>
       <c r="G106">
-        <v>0.1765802823489862</v>
+        <v>0.9515112556827708</v>
       </c>
     </row>
     <row r="107">
@@ -3238,19 +3238,19 @@
         </is>
       </c>
       <c r="C107">
-        <v>0.5581011579811478</v>
+        <v>0.6218962530787988</v>
       </c>
       <c r="D107">
-        <v>1.503763092568728</v>
+        <v>1.389965221340515</v>
       </c>
       <c r="E107">
-        <v>-0.791989086801595</v>
+        <v>-0.9830261048827444</v>
       </c>
       <c r="F107">
-        <v>-0.05135279649343313</v>
+        <v>0.7559818185400591</v>
       </c>
       <c r="G107">
-        <v>0.1852244493097013</v>
+        <v>0.1465933695133943</v>
       </c>
     </row>
     <row r="108">
@@ -3265,19 +3265,19 @@
         </is>
       </c>
       <c r="C108">
-        <v>1.350769212799546</v>
+        <v>1.850278032570236</v>
       </c>
       <c r="D108">
-        <v>0.2081325440397148</v>
+        <v>0.07727184371704048</v>
       </c>
       <c r="E108">
-        <v>-0.1291953681347499</v>
+        <v>-0.1429576046639812</v>
       </c>
       <c r="F108">
-        <v>-0.0168940246004872</v>
+        <v>-0.3011179928396412</v>
       </c>
       <c r="G108">
-        <v>-0.1283421373169</v>
+        <v>-0.09617956436292063</v>
       </c>
     </row>
     <row r="109">
@@ -3292,19 +3292,19 @@
         </is>
       </c>
       <c r="C109">
-        <v>3.07995742707377</v>
+        <v>4.149102861662582</v>
       </c>
       <c r="D109">
-        <v>1.949360503257368</v>
+        <v>1.581996510879243</v>
       </c>
       <c r="E109">
-        <v>-1.078363214546839</v>
+        <v>-1.267990350844383</v>
       </c>
       <c r="F109">
-        <v>0.1732126121323299</v>
+        <v>-0.2229748320282698</v>
       </c>
       <c r="G109">
-        <v>0.1309595508377981</v>
+        <v>0.1257260389208001</v>
       </c>
     </row>
     <row r="110">
@@ -3319,19 +3319,19 @@
         </is>
       </c>
       <c r="C110">
-        <v>-2.722560154132829</v>
+        <v>-3.880700381670974</v>
       </c>
       <c r="D110">
-        <v>0.5752747169622118</v>
+        <v>0.7095746406979796</v>
       </c>
       <c r="E110">
-        <v>-1.345050324794683</v>
+        <v>-1.38258903456348</v>
       </c>
       <c r="F110">
-        <v>-0.4142801188265118</v>
+        <v>0.1116368649974766</v>
       </c>
       <c r="G110">
-        <v>-0.01450089418288265</v>
+        <v>-0.3788735812984954</v>
       </c>
     </row>
     <row r="111">
@@ -3346,19 +3346,19 @@
         </is>
       </c>
       <c r="C111">
-        <v>0.6600466295955367</v>
+        <v>1.272345915491485</v>
       </c>
       <c r="D111">
-        <v>0.6196069414900999</v>
+        <v>0.6296342989449679</v>
       </c>
       <c r="E111">
-        <v>1.055226745978905</v>
+        <v>1.053682604247153</v>
       </c>
       <c r="F111">
-        <v>0.8427323602078718</v>
+        <v>-0.2098112720040417</v>
       </c>
       <c r="G111">
-        <v>-0.09989706149189553</v>
+        <v>0.7935781765437613</v>
       </c>
     </row>
     <row r="112">
@@ -3373,19 +3373,19 @@
         </is>
       </c>
       <c r="C112">
-        <v>3.160758353949882</v>
+        <v>4.391311432571693</v>
       </c>
       <c r="D112">
-        <v>-0.1711048009799861</v>
+        <v>-0.4146252407228338</v>
       </c>
       <c r="E112">
-        <v>0.5094599009276419</v>
+        <v>0.5196693056674656</v>
       </c>
       <c r="F112">
-        <v>-0.151988306519739</v>
+        <v>-0.4732247776225486</v>
       </c>
       <c r="G112">
-        <v>-0.05837003313149804</v>
+        <v>-0.2888491356561148</v>
       </c>
     </row>
     <row r="113">
@@ -3400,19 +3400,19 @@
         </is>
       </c>
       <c r="C113">
-        <v>-0.5215846957571713</v>
+        <v>-0.9621809133406313</v>
       </c>
       <c r="D113">
-        <v>-0.399390430560085</v>
+        <v>-0.417099384825635</v>
       </c>
       <c r="E113">
-        <v>-0.7324887258054692</v>
+        <v>-0.7258635827898903</v>
       </c>
       <c r="F113">
-        <v>-0.3731795283021782</v>
+        <v>-0.07534042866195659</v>
       </c>
       <c r="G113">
-        <v>-0.07080912061083514</v>
+        <v>-0.3957365234083445</v>
       </c>
     </row>
     <row r="114">
@@ -3427,19 +3427,19 @@
         </is>
       </c>
       <c r="C114">
-        <v>-2.962776196931117</v>
+        <v>-4.178296933073032</v>
       </c>
       <c r="D114">
-        <v>-0.2849790629476541</v>
+        <v>-0.08696329460464811</v>
       </c>
       <c r="E114">
-        <v>-0.8289901858238603</v>
+        <v>-0.7835304057991161</v>
       </c>
       <c r="F114">
-        <v>-0.2227994763780034</v>
+        <v>0.02467283927057484</v>
       </c>
       <c r="G114">
-        <v>0.1127718614670426</v>
+        <v>-0.2084207721927002</v>
       </c>
     </row>
     <row r="115">
@@ -3454,19 +3454,19 @@
         </is>
       </c>
       <c r="C115">
-        <v>-0.8279085207129887</v>
+        <v>-0.6658901709920813</v>
       </c>
       <c r="D115">
-        <v>0.8076829161138082</v>
+        <v>0.931998621059324</v>
       </c>
       <c r="E115">
-        <v>0.4060395417676167</v>
+        <v>0.457166685686248</v>
       </c>
       <c r="F115">
-        <v>0.5031548386232529</v>
+        <v>-0.3163485870516001</v>
       </c>
       <c r="G115">
-        <v>-0.01110007055404521</v>
+        <v>0.4337327613896206</v>
       </c>
     </row>
     <row r="116">
@@ -3481,19 +3481,19 @@
         </is>
       </c>
       <c r="C116">
-        <v>-0.706577181812413</v>
+        <v>-1.061533701979905</v>
       </c>
       <c r="D116">
-        <v>0.7944007497574752</v>
+        <v>0.8011877717595373</v>
       </c>
       <c r="E116">
-        <v>-0.6860686267146576</v>
+        <v>-0.7752189153499678</v>
       </c>
       <c r="F116">
-        <v>-0.2521206876748739</v>
+        <v>0.321890410773492</v>
       </c>
       <c r="G116">
-        <v>-0.02346527229411917</v>
+        <v>-0.1688487708634836</v>
       </c>
     </row>
     <row r="117">
@@ -3508,19 +3508,19 @@
         </is>
       </c>
       <c r="C117">
-        <v>-2.330926970631769</v>
+        <v>-2.954369438276726</v>
       </c>
       <c r="D117">
-        <v>0.3575490389108458</v>
+        <v>0.5919826793644207</v>
       </c>
       <c r="E117">
-        <v>-0.0862381113936137</v>
+        <v>-0.05076027849290055</v>
       </c>
       <c r="F117">
-        <v>-0.6107220141402399</v>
+        <v>0.7080756263354642</v>
       </c>
       <c r="G117">
-        <v>0.02481165898085299</v>
+        <v>-0.4464192109296695</v>
       </c>
     </row>
     <row r="118">
@@ -3535,19 +3535,19 @@
         </is>
       </c>
       <c r="C118">
-        <v>2.535728723532479</v>
+        <v>2.963107659313874</v>
       </c>
       <c r="D118">
-        <v>0.8561328640013834</v>
+        <v>0.5304696967069292</v>
       </c>
       <c r="E118">
-        <v>-0.7912678596903487</v>
+        <v>-1.032545854434041</v>
       </c>
       <c r="F118">
-        <v>0.101229758116166</v>
+        <v>0.5917545118144041</v>
       </c>
       <c r="G118">
-        <v>0.1613837846509327</v>
+        <v>0.2558197729915586</v>
       </c>
     </row>
     <row r="119">
@@ -3562,19 +3562,19 @@
         </is>
       </c>
       <c r="C119">
-        <v>-0.3795954339276689</v>
+        <v>-0.6121449645564653</v>
       </c>
       <c r="D119">
-        <v>-0.03861113444944195</v>
+        <v>-0.04155139807497718</v>
       </c>
       <c r="E119">
-        <v>-0.8152614104281863</v>
+        <v>-0.7903105254966969</v>
       </c>
       <c r="F119">
-        <v>-0.3015246399042431</v>
+        <v>-0.3379368491090963</v>
       </c>
       <c r="G119">
-        <v>-0.00355953639740095</v>
+        <v>-0.3734743300762487</v>
       </c>
     </row>
     <row r="120">
@@ -3589,19 +3589,19 @@
         </is>
       </c>
       <c r="C120">
-        <v>2.649002635117879</v>
+        <v>3.483204026568258</v>
       </c>
       <c r="D120">
-        <v>1.08834145902653</v>
+        <v>0.8353819411386422</v>
       </c>
       <c r="E120">
-        <v>0.09441982104314617</v>
+        <v>-0.1060470143563892</v>
       </c>
       <c r="F120">
-        <v>-0.02213229402703127</v>
+        <v>0.798171374433889</v>
       </c>
       <c r="G120">
-        <v>0.1095495792758815</v>
+        <v>0.1655871088623988</v>
       </c>
     </row>
     <row r="121">
@@ -3616,19 +3616,19 @@
         </is>
       </c>
       <c r="C121">
-        <v>-4.303200073939087</v>
+        <v>-5.229433177824988</v>
       </c>
       <c r="D121">
-        <v>0.04116990319698477</v>
+        <v>0.5139023523349905</v>
       </c>
       <c r="E121">
-        <v>1.359700196399688</v>
+        <v>1.503678014998345</v>
       </c>
       <c r="F121">
-        <v>-0.1887825817073567</v>
+        <v>0.03564608024239556</v>
       </c>
       <c r="G121">
-        <v>0.177803766429488</v>
+        <v>-0.2058349448053436</v>
       </c>
     </row>
     <row r="122">
@@ -3643,19 +3643,19 @@
         </is>
       </c>
       <c r="C122">
-        <v>-0.941428016342206</v>
+        <v>-0.764003908331258</v>
       </c>
       <c r="D122">
-        <v>0.5526379906451673</v>
+        <v>0.7528356577560068</v>
       </c>
       <c r="E122">
-        <v>1.083305507621273</v>
+        <v>1.13005100540495</v>
       </c>
       <c r="F122">
-        <v>-0.1248283962460986</v>
+        <v>0.2573954703418805</v>
       </c>
       <c r="G122">
-        <v>-0.133784575704458</v>
+        <v>-0.06998695218385811</v>
       </c>
     </row>
     <row r="123">
@@ -3670,19 +3670,19 @@
         </is>
       </c>
       <c r="C123">
-        <v>-0.4910190445850966</v>
+        <v>-1.143335527897648</v>
       </c>
       <c r="D123">
-        <v>-0.495262012792087</v>
+        <v>-0.5212964708172999</v>
       </c>
       <c r="E123">
-        <v>-0.411398458127453</v>
+        <v>-0.4994044384099701</v>
       </c>
       <c r="F123">
-        <v>-0.3904868742829362</v>
+        <v>0.4604526172224903</v>
       </c>
       <c r="G123">
-        <v>0.01386892132536104</v>
+        <v>-0.2807902210214892</v>
       </c>
     </row>
     <row r="124">
@@ -3697,19 +3697,19 @@
         </is>
       </c>
       <c r="C124">
-        <v>0.5864444800012237</v>
+        <v>1.038333745631256</v>
       </c>
       <c r="D124">
-        <v>-0.1399607547196105</v>
+        <v>-0.1103708348718692</v>
       </c>
       <c r="E124">
-        <v>0.6819033288196421</v>
+        <v>0.7248645991442926</v>
       </c>
       <c r="F124">
-        <v>-0.8861799591207351</v>
+        <v>0.3870931194971197</v>
       </c>
       <c r="G124">
-        <v>-0.09853606370684297</v>
+        <v>-0.8226062516766237</v>
       </c>
     </row>
     <row r="125">
@@ -3724,19 +3724,19 @@
         </is>
       </c>
       <c r="C125">
-        <v>-2.268921947371267</v>
+        <v>-2.81151165484927</v>
       </c>
       <c r="D125">
-        <v>-0.3163671156993469</v>
+        <v>-0.1201088212769386</v>
       </c>
       <c r="E125">
-        <v>-0.5396935904020463</v>
+        <v>-0.3410612914180324</v>
       </c>
       <c r="F125">
-        <v>0.114074878588167</v>
+        <v>-1.309368432541559</v>
       </c>
       <c r="G125">
-        <v>-0.41893776871865</v>
+        <v>-0.1972014579789563</v>
       </c>
     </row>
     <row r="126">
@@ -3751,19 +3751,19 @@
         </is>
       </c>
       <c r="C126">
-        <v>-3.154676979078838</v>
+        <v>-4.338295233778021</v>
       </c>
       <c r="D126">
-        <v>0.3424759759414758</v>
+        <v>0.545600961314387</v>
       </c>
       <c r="E126">
-        <v>-1.11971483509866</v>
+        <v>-1.091672766034065</v>
       </c>
       <c r="F126">
-        <v>-0.1722604718368709</v>
+        <v>-0.135698952755243</v>
       </c>
       <c r="G126">
-        <v>0.03131350033066337</v>
+        <v>-0.1907596443844014</v>
       </c>
     </row>
   </sheetData>
